--- a/comparativo_redutores_motores_potencia.xlsx
+++ b/comparativo_redutores_motores_potencia.xlsx
@@ -5,17 +5,18 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andre.santiago\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andre.santiago\Documents\MANUT REDUT INPASA 2026\ESCOPO EQUIPAMENTOS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A34E52D9-660D-4DF6-9D92-214D5F7DD54A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{99133F09-992C-42D9-A056-766A1AB45BB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-1875" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-27975" yWindow="1080" windowWidth="15375" windowHeight="7785" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Comparativo" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="425" uniqueCount="237">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="468" uniqueCount="262">
   <si>
     <t>TIPO</t>
   </si>
@@ -736,13 +737,88 @@
   </si>
   <si>
     <t>REDUTOR VENTILAÇÃO FORÇADA - TREMONHA DE ELOS COM TALISCAS TETD/100.1 (ME631511)</t>
+  </si>
+  <si>
+    <t>ME</t>
+  </si>
+  <si>
+    <t>601010</t>
+  </si>
+  <si>
+    <t>Moto Bomba Auxiliar</t>
+  </si>
+  <si>
+    <t>600</t>
+  </si>
+  <si>
+    <t>601086</t>
+  </si>
+  <si>
+    <t>Motor da bomba de óleo turbobomba caldeira 2</t>
+  </si>
+  <si>
+    <t>601108</t>
+  </si>
+  <si>
+    <t>Unidade Hidráulica Moega 1</t>
+  </si>
+  <si>
+    <t>7,5</t>
+  </si>
+  <si>
+    <t>601109</t>
+  </si>
+  <si>
+    <t>Unidade Hidráulica Moega 2</t>
+  </si>
+  <si>
+    <t>601207</t>
+  </si>
+  <si>
+    <t>Motor Unidade Hidraulica da Grelha - 24 Vcc 01</t>
+  </si>
+  <si>
+    <t>601208</t>
+  </si>
+  <si>
+    <t>Motor Unidade Hidraulica da Grelha - 24 Vcc 02</t>
+  </si>
+  <si>
+    <t>601209</t>
+  </si>
+  <si>
+    <t>Motor Unidade Hidraulica da Grelha - 24 Vcc 03</t>
+  </si>
+  <si>
+    <t>601218</t>
+  </si>
+  <si>
+    <t>Jato Vapor Balão</t>
+  </si>
+  <si>
+    <t>0,33</t>
+  </si>
+  <si>
+    <t>601523</t>
+  </si>
+  <si>
+    <t>Motor da bomba de lubrificação 1</t>
+  </si>
+  <si>
+    <t>601524</t>
+  </si>
+  <si>
+    <t>Motor da bomba de lubrificação 2</t>
+  </si>
+  <si>
+    <t>Motor transportadora redler tard/2000 - (trr631506)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -755,6 +831,11 @@
     </font>
     <font>
       <sz val="10"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF111827"/>
       <name val="Carlito"/>
     </font>
   </fonts>
@@ -783,7 +864,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -793,6 +874,15 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -820,9 +910,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="TabelaComparativoTags" displayName="TabelaComparativoTags" ref="A1:D112">
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D112">
-    <sortCondition ref="B1:B112"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="TabelaComparativoTags" displayName="TabelaComparativoTags" ref="A1:D123">
+  <autoFilter ref="A1:D123" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D123">
+    <sortCondition ref="B1:B123"/>
   </sortState>
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="TIPO"/>
@@ -983,7 +1074,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D112"/>
+  <dimension ref="A1:D123"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -1007,31 +1098,31 @@
       </c>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>54</v>
+      <c r="A2" t="s">
+        <v>237</v>
+      </c>
+      <c r="B2">
+        <v>601506</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>261</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>226</v>
       </c>
     </row>
     <row r="3" spans="1:4">
-      <c r="A3" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>54</v>
+      <c r="A3" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>239</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>240</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1039,10 +1130,10 @@
         <v>11</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>54</v>
@@ -1053,10 +1144,10 @@
         <v>11</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>54</v>
@@ -1067,10 +1158,10 @@
         <v>11</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>54</v>
@@ -1081,10 +1172,10 @@
         <v>11</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>54</v>
@@ -1095,10 +1186,10 @@
         <v>11</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>54</v>
@@ -1109,10 +1200,10 @@
         <v>11</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>54</v>
@@ -1123,10 +1214,10 @@
         <v>11</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>54</v>
@@ -1137,13 +1228,13 @@
         <v>11</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>140</v>
+        <v>79</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>141</v>
+        <v>80</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -1151,13 +1242,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>142</v>
+        <v>81</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>143</v>
+        <v>82</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -1165,10 +1256,10 @@
         <v>11</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>40</v>
@@ -1179,24 +1270,24 @@
         <v>11</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="25.5">
+    <row r="15" spans="1:4">
       <c r="A15" s="3" t="s">
         <v>11</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>40</v>
@@ -1207,24 +1298,24 @@
         <v>11</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>38</v>
+        <v>146</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>39</v>
+        <v>147</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="17" spans="1:4">
+    <row r="17" spans="1:4" ht="25.5">
       <c r="A17" s="3" t="s">
         <v>11</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>41</v>
+        <v>148</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>42</v>
+        <v>149</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>40</v>
@@ -1235,10 +1326,10 @@
         <v>11</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>40</v>
@@ -1249,10 +1340,10 @@
         <v>11</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>150</v>
+        <v>41</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>151</v>
+        <v>42</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>40</v>
@@ -1263,10 +1354,10 @@
         <v>11</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>152</v>
+        <v>43</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>153</v>
+        <v>44</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>40</v>
@@ -1277,10 +1368,10 @@
         <v>11</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>40</v>
@@ -1291,10 +1382,10 @@
         <v>11</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>40</v>
@@ -1305,10 +1396,10 @@
         <v>11</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="D23" s="3" t="s">
         <v>40</v>
@@ -1319,10 +1410,10 @@
         <v>11</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>40</v>
@@ -1333,10 +1424,10 @@
         <v>11</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="D25" s="3" t="s">
         <v>40</v>
@@ -1347,10 +1438,10 @@
         <v>11</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="D26" s="3" t="s">
         <v>40</v>
@@ -1361,13 +1452,13 @@
         <v>11</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>85</v>
+        <v>162</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>86</v>
+        <v>163</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>87</v>
+        <v>40</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -1375,66 +1466,66 @@
         <v>11</v>
       </c>
       <c r="B28" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4">
+      <c r="A29" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4">
+      <c r="A30" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B30" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="C28" s="2" t="s">
+      <c r="C30" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="D28" s="3" t="s">
+      <c r="D30" s="3" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="29" spans="1:4" ht="25.5">
-      <c r="A29" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B29" s="3" t="s">
+    <row r="31" spans="1:4" ht="25.5">
+      <c r="A31" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B31" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C29" s="2" t="s">
+      <c r="C31" s="2" t="s">
         <v>23</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" ht="25.5">
-      <c r="A30" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="D30" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4">
-      <c r="A31" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>136</v>
       </c>
       <c r="D31" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="32" spans="1:4">
+    <row r="32" spans="1:4" ht="25.5">
       <c r="A32" s="3" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>8</v>
+        <v>133</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>9</v>
+        <v>134</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>10</v>
@@ -1445,10 +1536,10 @@
         <v>11</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>8</v>
+        <v>135</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D33" s="3" t="s">
         <v>10</v>
@@ -1456,13 +1547,13 @@
     </row>
     <row r="34" spans="1:4">
       <c r="A34" s="3" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D34" s="3" t="s">
         <v>10</v>
@@ -1473,10 +1564,10 @@
         <v>11</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>138</v>
+        <v>8</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="D35" s="3" t="s">
         <v>10</v>
@@ -1487,13 +1578,13 @@
         <v>11</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>166</v>
+        <v>12</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>167</v>
+        <v>13</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -1501,13 +1592,13 @@
         <v>11</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>180</v>
+        <v>138</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>181</v>
+        <v>139</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -1515,10 +1606,10 @@
         <v>11</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>182</v>
+        <v>166</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>183</v>
+        <v>167</v>
       </c>
       <c r="D38" s="3" t="s">
         <v>26</v>
@@ -1529,10 +1620,10 @@
         <v>11</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="D39" s="3" t="s">
         <v>26</v>
@@ -1543,10 +1634,10 @@
         <v>11</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="D40" s="3" t="s">
         <v>26</v>
@@ -1557,10 +1648,10 @@
         <v>11</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="D41" s="3" t="s">
         <v>26</v>
@@ -1571,10 +1662,10 @@
         <v>11</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>26</v>
@@ -1585,10 +1676,10 @@
         <v>11</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>168</v>
+        <v>188</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="D43" s="3" t="s">
         <v>26</v>
@@ -1599,13 +1690,13 @@
         <v>11</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>170</v>
+        <v>190</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>171</v>
+        <v>191</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>7</v>
+        <v>26</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -1613,13 +1704,13 @@
         <v>11</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>7</v>
+        <v>26</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -1627,13 +1718,13 @@
         <v>11</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>88</v>
+        <v>170</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>89</v>
+        <v>171</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -1641,13 +1732,13 @@
         <v>11</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>90</v>
+        <v>172</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>91</v>
+        <v>173</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -1655,10 +1746,10 @@
         <v>11</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="D48" s="3" t="s">
         <v>16</v>
@@ -1669,10 +1760,10 @@
         <v>11</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>121</v>
+        <v>90</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>122</v>
+        <v>91</v>
       </c>
       <c r="D49" s="3" t="s">
         <v>16</v>
@@ -1683,10 +1774,10 @@
         <v>11</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D50" s="3" t="s">
         <v>16</v>
@@ -1697,10 +1788,10 @@
         <v>11</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D51" s="3" t="s">
         <v>16</v>
@@ -1711,10 +1802,10 @@
         <v>11</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>16</v>
@@ -1725,10 +1816,10 @@
         <v>11</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D53" s="3" t="s">
         <v>16</v>
@@ -1739,10 +1830,10 @@
         <v>11</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D54" s="3" t="s">
         <v>16</v>
@@ -1753,10 +1844,10 @@
         <v>11</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D55" s="3" t="s">
         <v>16</v>
@@ -1767,10 +1858,10 @@
         <v>11</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>83</v>
+        <v>98</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>84</v>
+        <v>99</v>
       </c>
       <c r="D56" s="3" t="s">
         <v>16</v>
@@ -1781,10 +1872,10 @@
         <v>11</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>14</v>
+        <v>127</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>15</v>
+        <v>128</v>
       </c>
       <c r="D57" s="3" t="s">
         <v>16</v>
@@ -1795,10 +1886,10 @@
         <v>11</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>31</v>
+        <v>83</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>32</v>
+        <v>84</v>
       </c>
       <c r="D58" s="3" t="s">
         <v>16</v>
@@ -1809,10 +1900,10 @@
         <v>11</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="D59" s="3" t="s">
         <v>16</v>
@@ -1820,16 +1911,16 @@
     </row>
     <row r="60" spans="1:4">
       <c r="A60" s="3" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -1837,69 +1928,69 @@
         <v>11</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>51</v>
+        <v>34</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
     </row>
     <row r="62" spans="1:4">
-      <c r="A62" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B62" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="C62" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="D62" s="3" t="s">
-        <v>7</v>
+      <c r="A62" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="B62" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="C62" s="5" t="s">
+        <v>242</v>
+      </c>
+      <c r="D62" s="4" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="63" spans="1:4">
-      <c r="A63" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B63" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="C63" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="D63" s="3" t="s">
-        <v>7</v>
+      <c r="A63" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="B63" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="C63" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="D63" s="4" t="s">
+        <v>245</v>
       </c>
     </row>
     <row r="64" spans="1:4">
-      <c r="A64" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B64" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="C64" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="D64" s="3" t="s">
-        <v>7</v>
+      <c r="A64" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="B64" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="C64" s="5" t="s">
+        <v>247</v>
+      </c>
+      <c r="D64" s="4" t="s">
+        <v>245</v>
       </c>
     </row>
     <row r="65" spans="1:4">
       <c r="A65" s="3" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -1907,13 +1998,13 @@
         <v>11</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -1921,13 +2012,13 @@
         <v>11</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>17</v>
+        <v>174</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>18</v>
+        <v>175</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -1935,13 +2026,13 @@
         <v>11</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>100</v>
+        <v>176</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>101</v>
+        <v>177</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>37</v>
+        <v>7</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -1949,13 +2040,13 @@
         <v>11</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>102</v>
+        <v>178</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>103</v>
+        <v>179</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>37</v>
+        <v>7</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -1963,13 +2054,13 @@
         <v>11</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>104</v>
+        <v>19</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>105</v>
+        <v>20</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>37</v>
+        <v>10</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -1977,13 +2068,13 @@
         <v>11</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>106</v>
+        <v>21</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>107</v>
+        <v>20</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>37</v>
+        <v>10</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -1991,83 +2082,83 @@
         <v>11</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>108</v>
+        <v>17</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>109</v>
+        <v>18</v>
       </c>
       <c r="D72" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4">
+      <c r="A73" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="B73" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="C73" s="5" t="s">
+        <v>249</v>
+      </c>
+      <c r="D73" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4">
+      <c r="A74" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="B74" s="4" t="s">
+        <v>250</v>
+      </c>
+      <c r="C74" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="D74" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4">
+      <c r="A75" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="B75" s="4" t="s">
+        <v>252</v>
+      </c>
+      <c r="C75" s="5" t="s">
+        <v>253</v>
+      </c>
+      <c r="D75" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4">
+      <c r="A76" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B76" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="D76" s="3" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="73" spans="1:4">
-      <c r="A73" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B73" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="C73" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="D73" s="3" t="s">
+    <row r="77" spans="1:4">
+      <c r="A77" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B77" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="D77" s="3" t="s">
         <v>37</v>
-      </c>
-    </row>
-    <row r="74" spans="1:4">
-      <c r="A74" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B74" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="C74" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="D74" s="3" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="75" spans="1:4">
-      <c r="A75" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B75" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="C75" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="D75" s="3" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="76" spans="1:4" ht="25.5">
-      <c r="A76" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B76" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="C76" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="D76" s="3" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="77" spans="1:4" ht="25.5">
-      <c r="A77" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B77" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="C77" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="D77" s="3" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -2075,27 +2166,27 @@
         <v>11</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="79" spans="1:4" ht="25.5">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4">
       <c r="A79" s="3" t="s">
         <v>11</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>131</v>
+        <v>106</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>132</v>
+        <v>107</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>16</v>
+        <v>37</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -2103,13 +2194,13 @@
         <v>11</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>24</v>
+        <v>108</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>25</v>
+        <v>109</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -2117,13 +2208,13 @@
         <v>11</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -2131,13 +2222,13 @@
         <v>11</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>29</v>
+        <v>49</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -2145,107 +2236,111 @@
         <v>11</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>110</v>
+        <v>47</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>111</v>
+        <v>48</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="84" spans="1:4" ht="25.5">
-      <c r="A84" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B84" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="C84" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="D84" s="3" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="85" spans="1:4">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4">
+      <c r="A84" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="B84" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="C84" s="5" t="s">
+        <v>255</v>
+      </c>
+      <c r="D84" s="4" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" ht="25.5">
       <c r="A85" s="3" t="s">
         <v>11</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="D85" s="3"/>
+        <v>61</v>
+      </c>
+      <c r="D85" s="3" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="86" spans="1:4" ht="25.5">
       <c r="A86" s="3" t="s">
         <v>11</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>55</v>
+        <v>117</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>56</v>
+        <v>118</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="87" spans="1:4" ht="25.5">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4">
       <c r="A87" s="3" t="s">
         <v>11</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="88" spans="1:4">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" ht="25.5">
       <c r="A88" s="3" t="s">
         <v>11</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>45</v>
+        <v>131</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D88" s="3"/>
-    </row>
-    <row r="89" spans="1:4" ht="25.5">
+        <v>132</v>
+      </c>
+      <c r="D88" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4">
       <c r="A89" s="3" t="s">
         <v>11</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>52</v>
+        <v>24</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="90" spans="1:4" ht="25.5">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4">
       <c r="A90" s="3" t="s">
         <v>11</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>57</v>
+        <v>27</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>58</v>
+        <v>28</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>59</v>
+        <v>26</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -2253,133 +2348,149 @@
         <v>11</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>206</v>
+        <v>29</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="D91" s="3"/>
+        <v>30</v>
+      </c>
+      <c r="D91" s="3" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="92" spans="1:4">
       <c r="A92" s="3" t="s">
         <v>11</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>208</v>
+        <v>110</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="D92" s="3"/>
-    </row>
-    <row r="93" spans="1:4">
+        <v>111</v>
+      </c>
+      <c r="D92" s="3" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" ht="25.5">
       <c r="A93" s="3" t="s">
         <v>11</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>204</v>
+        <v>129</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="D93" s="3"/>
+        <v>130</v>
+      </c>
+      <c r="D93" s="3" t="s">
+        <v>112</v>
+      </c>
     </row>
     <row r="94" spans="1:4">
       <c r="A94" s="3" t="s">
         <v>11</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>216</v>
+        <v>63</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>217</v>
+        <v>64</v>
       </c>
       <c r="D94" s="3"/>
     </row>
-    <row r="95" spans="1:4">
+    <row r="95" spans="1:4" ht="25.5">
       <c r="A95" s="3" t="s">
         <v>11</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>231</v>
+        <v>55</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="D95" s="3"/>
-    </row>
-    <row r="96" spans="1:4">
+        <v>56</v>
+      </c>
+      <c r="D95" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" ht="25.5">
       <c r="A96" s="3" t="s">
         <v>11</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>220</v>
+        <v>115</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="D96" s="3"/>
+        <v>116</v>
+      </c>
+      <c r="D96" s="3" t="s">
+        <v>54</v>
+      </c>
     </row>
     <row r="97" spans="1:4">
       <c r="A97" s="3" t="s">
         <v>11</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>233</v>
+        <v>45</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>234</v>
+        <v>46</v>
       </c>
       <c r="D97" s="3"/>
     </row>
-    <row r="98" spans="1:4">
+    <row r="98" spans="1:4" ht="25.5">
       <c r="A98" s="3" t="s">
         <v>11</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>222</v>
+        <v>52</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="D98" s="3"/>
-    </row>
-    <row r="99" spans="1:4">
+        <v>53</v>
+      </c>
+      <c r="D98" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" ht="25.5">
       <c r="A99" s="3" t="s">
         <v>11</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>229</v>
+        <v>57</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="D99" s="3"/>
+        <v>58</v>
+      </c>
+      <c r="D99" s="3" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="100" spans="1:4">
-      <c r="A100" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B100" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="C100" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="D100" s="3"/>
+      <c r="A100" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="B100" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="C100" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="D100" s="4" t="s">
+        <v>40</v>
+      </c>
     </row>
     <row r="101" spans="1:4">
-      <c r="A101" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B101" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="C101" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="D101" s="3" t="s">
-        <v>226</v>
+      <c r="A101" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="B101" s="4" t="s">
+        <v>259</v>
+      </c>
+      <c r="C101" s="5" t="s">
+        <v>260</v>
+      </c>
+      <c r="D101" s="4" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -2387,22 +2498,22 @@
         <v>11</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="D102" s="3"/>
     </row>
-    <row r="103" spans="1:4" ht="25.5">
+    <row r="103" spans="1:4">
       <c r="A103" s="3" t="s">
         <v>11</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="D103" s="3"/>
     </row>
@@ -2411,10 +2522,10 @@
         <v>11</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>192</v>
+        <v>204</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>193</v>
+        <v>205</v>
       </c>
       <c r="D104" s="3"/>
     </row>
@@ -2423,34 +2534,34 @@
         <v>11</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>227</v>
+        <v>216</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>228</v>
+        <v>217</v>
       </c>
       <c r="D105" s="3"/>
     </row>
-    <row r="106" spans="1:4" ht="25.5">
+    <row r="106" spans="1:4">
       <c r="A106" s="3" t="s">
         <v>11</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>214</v>
+        <v>231</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>215</v>
+        <v>232</v>
       </c>
       <c r="D106" s="3"/>
     </row>
-    <row r="107" spans="1:4" ht="25.5">
+    <row r="107" spans="1:4">
       <c r="A107" s="3" t="s">
         <v>11</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>235</v>
+        <v>220</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>236</v>
+        <v>221</v>
       </c>
       <c r="D107" s="3"/>
     </row>
@@ -2459,10 +2570,10 @@
         <v>11</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>196</v>
+        <v>233</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>197</v>
+        <v>234</v>
       </c>
       <c r="D108" s="3"/>
     </row>
@@ -2471,10 +2582,10 @@
         <v>11</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>210</v>
+        <v>222</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>211</v>
+        <v>223</v>
       </c>
       <c r="D109" s="3"/>
     </row>
@@ -2483,10 +2594,10 @@
         <v>11</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>194</v>
+        <v>229</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>195</v>
+        <v>230</v>
       </c>
       <c r="D110" s="3"/>
     </row>
@@ -2495,10 +2606,10 @@
         <v>11</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>198</v>
+        <v>218</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>199</v>
+        <v>219</v>
       </c>
       <c r="D111" s="3"/>
     </row>
@@ -2507,15 +2618,149 @@
         <v>11</v>
       </c>
       <c r="B112" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="C112" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="D112" s="3" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4">
+      <c r="A113" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B113" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="C113" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="D113" s="3"/>
+    </row>
+    <row r="114" spans="1:4" ht="25.5">
+      <c r="A114" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B114" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="C114" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="D114" s="3"/>
+    </row>
+    <row r="115" spans="1:4">
+      <c r="A115" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B115" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="C115" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="D115" s="3"/>
+    </row>
+    <row r="116" spans="1:4">
+      <c r="A116" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B116" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="C116" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="D116" s="3"/>
+    </row>
+    <row r="117" spans="1:4" ht="25.5">
+      <c r="A117" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B117" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="C117" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="D117" s="3"/>
+    </row>
+    <row r="118" spans="1:4" ht="25.5">
+      <c r="A118" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B118" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="C118" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="D118" s="3"/>
+    </row>
+    <row r="119" spans="1:4">
+      <c r="A119" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B119" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="C119" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="D119" s="3"/>
+    </row>
+    <row r="120" spans="1:4">
+      <c r="A120" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B120" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="C120" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="D120" s="3"/>
+    </row>
+    <row r="121" spans="1:4">
+      <c r="A121" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B121" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="C121" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="D121" s="3"/>
+    </row>
+    <row r="122" spans="1:4">
+      <c r="A122" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B122" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="C122" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="D122" s="3"/>
+    </row>
+    <row r="123" spans="1:4">
+      <c r="A123" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B123" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="C112" s="2" t="s">
+      <c r="C123" s="2" t="s">
         <v>203</v>
       </c>
-      <c r="D112" s="3"/>
+      <c r="D123" s="3"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="D2:D112">
+  <conditionalFormatting sqref="H2:H3 L2:L3 P2:P3 T2:T3 X2:X3 AB2:AB3 AF2:AF3 AJ2:AJ3 AN2:AN3 AR2:AR3 AV2:AV3 AZ2:AZ3 BD2:BD3 BH2:BH3 BL2:BL3 BP2:BP3 BT2:BT3 BX2:BX3 CB2:CB3 CF2:CF3 CJ2:CJ3 CN2:CN3 CR2:CR3 CV2:CV3 CZ2:CZ3 DD2:DD3 DH2:DH3 DL2:DL3 DP2:DP3 DT2:DT3 DX2:DX3 EB2:EB3 EF2:EF3 EJ2:EJ3 EN2:EN3 ER2:ER3 EV2:EV3 EZ2:EZ3 FD2:FD3 FH2:FH3 FL2:FL3 FP2:FP3 FT2:FT3 FX2:FX3 GB2:GB3 GF2:GF3 GJ2:GJ3 GN2:GN3 GR2:GR3 GV2:GV3 GZ2:GZ3 HD2:HD3 HH2:HH3 HL2:HL3 HP2:HP3 HT2:HT3 HX2:HX3 IB2:IB3 IF2:IF3 IJ2:IJ3 IN2:IN3 IR2:IR3 IV2:IV3 IZ2:IZ3 JD2:JD3 JH2:JH3 JL2:JL3 JP2:JP3 JT2:JT3 JX2:JX3 KB2:KB3 KF2:KF3 KJ2:KJ3 KN2:KN3 KR2:KR3 KV2:KV3 KZ2:KZ3 LD2:LD3 LH2:LH3 LL2:LL3 LP2:LP3 LT2:LT3 LX2:LX3 MB2:MB3 MF2:MF3 MJ2:MJ3 MN2:MN3 MR2:MR3 MV2:MV3 MZ2:MZ3 ND2:ND3 NH2:NH3 NL2:NL3 NP2:NP3 NT2:NT3 NX2:NX3 OB2:OB3 OF2:OF3 OJ2:OJ3 ON2:ON3 OR2:OR3 OV2:OV3 OZ2:OZ3 PD2:PD3 PH2:PH3 PL2:PL3 PP2:PP3 PT2:PT3 PX2:PX3 QB2:QB3 QF2:QF3 QJ2:QJ3 QN2:QN3 QR2:QR3 QV2:QV3 QZ2:QZ3 RD2:RD3 RH2:RH3 RL2:RL3 RP2:RP3 RT2:RT3 RX2:RX3 SB2:SB3 SF2:SF3 SJ2:SJ3 SN2:SN3 SR2:SR3 SV2:SV3 SZ2:SZ3 TD2:TD3 TH2:TH3 TL2:TL3 TP2:TP3 TT2:TT3 TX2:TX3 UB2:UB3 UF2:UF3 UJ2:UJ3 UN2:UN3 UR2:UR3 UV2:UV3 UZ2:UZ3 VD2:VD3 VH2:VH3 VL2:VL3 VP2:VP3 VT2:VT3 VX2:VX3 WB2:WB3 WF2:WF3 WJ2:WJ3 WN2:WN3 WR2:WR3 WV2:WV3 WZ2:WZ3 XD2:XD3 XH2:XH3 XL2:XL3 XP2:XP3 XT2:XT3 XX2:XX3 YB2:YB3 YF2:YF3 YJ2:YJ3 YN2:YN3 YR2:YR3 YV2:YV3 YZ2:YZ3 ZD2:ZD3 ZH2:ZH3 ZL2:ZL3 ZP2:ZP3 ZT2:ZT3 ZX2:ZX3 AAB2:AAB3 AAF2:AAF3 AAJ2:AAJ3 AAN2:AAN3 AAR2:AAR3 AAV2:AAV3 AAZ2:AAZ3 ABD2:ABD3 ABH2:ABH3 ABL2:ABL3 ABP2:ABP3 ABT2:ABT3 ABX2:ABX3 ACB2:ACB3 ACF2:ACF3 ACJ2:ACJ3 ACN2:ACN3 ACR2:ACR3 ACV2:ACV3 ACZ2:ACZ3 ADD2:ADD3 ADH2:ADH3 ADL2:ADL3 ADP2:ADP3 ADT2:ADT3 ADX2:ADX3 AEB2:AEB3 AEF2:AEF3 AEJ2:AEJ3 AEN2:AEN3 AER2:AER3 AEV2:AEV3 AEZ2:AEZ3 AFD2:AFD3 AFH2:AFH3 AFL2:AFL3 AFP2:AFP3 AFT2:AFT3 AFX2:AFX3 AGB2:AGB3 AGF2:AGF3 AGJ2:AGJ3 AGN2:AGN3 AGR2:AGR3 AGV2:AGV3 AGZ2:AGZ3 AHD2:AHD3 AHH2:AHH3 AHL2:AHL3 AHP2:AHP3 AHT2:AHT3 AHX2:AHX3 AIB2:AIB3 AIF2:AIF3 AIJ2:AIJ3 AIN2:AIN3 AIR2:AIR3 AIV2:AIV3 AIZ2:AIZ3 AJD2:AJD3 AJH2:AJH3 AJL2:AJL3 AJP2:AJP3 AJT2:AJT3 AJX2:AJX3 AKB2:AKB3 AKF2:AKF3 AKJ2:AKJ3 AKN2:AKN3 AKR2:AKR3 AKV2:AKV3 AKZ2:AKZ3 ALD2:ALD3 ALH2:ALH3 ALL2:ALL3 ALP2:ALP3 ALT2:ALT3 ALX2:ALX3 AMB2:AMB3 AMF2:AMF3 AMJ2:AMJ3 AMN2:AMN3 AMR2:AMR3 AMV2:AMV3 AMZ2:AMZ3 AND2:AND3 ANH2:ANH3 ANL2:ANL3 ANP2:ANP3 ANT2:ANT3 ANX2:ANX3 AOB2:AOB3 AOF2:AOF3 AOJ2:AOJ3 AON2:AON3 AOR2:AOR3 AOV2:AOV3 AOZ2:AOZ3 APD2:APD3 APH2:APH3 APL2:APL3 APP2:APP3 APT2:APT3 APX2:APX3 AQB2:AQB3 AQF2:AQF3 AQJ2:AQJ3 AQN2:AQN3 AQR2:AQR3 AQV2:AQV3 AQZ2:AQZ3 ARD2:ARD3 ARH2:ARH3 ARL2:ARL3 ARP2:ARP3 ART2:ART3 ARX2:ARX3 ASB2:ASB3 ASF2:ASF3 ASJ2:ASJ3 ASN2:ASN3 ASR2:ASR3 ASV2:ASV3 ASZ2:ASZ3 ATD2:ATD3 ATH2:ATH3 ATL2:ATL3 ATP2:ATP3 ATT2:ATT3 ATX2:ATX3 AUB2:AUB3 AUF2:AUF3 AUJ2:AUJ3 AUN2:AUN3 AUR2:AUR3 AUV2:AUV3 AUZ2:AUZ3 AVD2:AVD3 AVH2:AVH3 AVL2:AVL3 AVP2:AVP3 AVT2:AVT3 AVX2:AVX3 AWB2:AWB3 AWF2:AWF3 AWJ2:AWJ3 AWN2:AWN3 AWR2:AWR3 AWV2:AWV3 AWZ2:AWZ3 AXD2:AXD3 AXH2:AXH3 AXL2:AXL3 AXP2:AXP3 AXT2:AXT3 AXX2:AXX3 AYB2:AYB3 AYF2:AYF3 AYJ2:AYJ3 AYN2:AYN3 AYR2:AYR3 AYV2:AYV3 AYZ2:AYZ3 AZD2:AZD3 AZH2:AZH3 AZL2:AZL3 AZP2:AZP3 AZT2:AZT3 AZX2:AZX3 BAB2:BAB3 BAF2:BAF3 BAJ2:BAJ3 BAN2:BAN3 BAR2:BAR3 BAV2:BAV3 BAZ2:BAZ3 BBD2:BBD3 BBH2:BBH3 BBL2:BBL3 BBP2:BBP3 BBT2:BBT3 BBX2:BBX3 BCB2:BCB3 BCF2:BCF3 BCJ2:BCJ3 BCN2:BCN3 BCR2:BCR3 BCV2:BCV3 BCZ2:BCZ3 BDD2:BDD3 BDH2:BDH3 BDL2:BDL3 BDP2:BDP3 BDT2:BDT3 BDX2:BDX3 BEB2:BEB3 BEF2:BEF3 BEJ2:BEJ3 BEN2:BEN3 BER2:BER3 BEV2:BEV3 BEZ2:BEZ3 BFD2:BFD3 BFH2:BFH3 BFL2:BFL3 BFP2:BFP3 BFT2:BFT3 BFX2:BFX3 BGB2:BGB3 BGF2:BGF3 BGJ2:BGJ3 BGN2:BGN3 BGR2:BGR3 BGV2:BGV3 BGZ2:BGZ3 BHD2:BHD3 BHH2:BHH3 BHL2:BHL3 BHP2:BHP3 BHT2:BHT3 BHX2:BHX3 BIB2:BIB3 BIF2:BIF3 BIJ2:BIJ3 BIN2:BIN3 BIR2:BIR3 BIV2:BIV3 BIZ2:BIZ3 BJD2:BJD3 BJH2:BJH3 BJL2:BJL3 BJP2:BJP3 BJT2:BJT3 BJX2:BJX3 BKB2:BKB3 BKF2:BKF3 BKJ2:BKJ3 BKN2:BKN3 BKR2:BKR3 BKV2:BKV3 BKZ2:BKZ3 BLD2:BLD3 BLH2:BLH3 BLL2:BLL3 BLP2:BLP3 BLT2:BLT3 BLX2:BLX3 BMB2:BMB3 BMF2:BMF3 BMJ2:BMJ3 BMN2:BMN3 BMR2:BMR3 BMV2:BMV3 BMZ2:BMZ3 BND2:BND3 BNH2:BNH3 BNL2:BNL3 BNP2:BNP3 BNT2:BNT3 BNX2:BNX3 BOB2:BOB3 BOF2:BOF3 BOJ2:BOJ3 BON2:BON3 BOR2:BOR3 BOV2:BOV3 BOZ2:BOZ3 BPD2:BPD3 BPH2:BPH3 BPL2:BPL3 BPP2:BPP3 BPT2:BPT3 BPX2:BPX3 BQB2:BQB3 BQF2:BQF3 BQJ2:BQJ3 BQN2:BQN3 BQR2:BQR3 BQV2:BQV3 BQZ2:BQZ3 BRD2:BRD3 BRH2:BRH3 BRL2:BRL3 BRP2:BRP3 BRT2:BRT3 BRX2:BRX3 BSB2:BSB3 BSF2:BSF3 BSJ2:BSJ3 BSN2:BSN3 BSR2:BSR3 BSV2:BSV3 BSZ2:BSZ3 BTD2:BTD3 BTH2:BTH3 BTL2:BTL3 BTP2:BTP3 BTT2:BTT3 BTX2:BTX3 BUB2:BUB3 BUF2:BUF3 BUJ2:BUJ3 BUN2:BUN3 BUR2:BUR3 BUV2:BUV3 BUZ2:BUZ3 BVD2:BVD3 BVH2:BVH3 BVL2:BVL3 BVP2:BVP3 BVT2:BVT3 BVX2:BVX3 BWB2:BWB3 BWF2:BWF3 BWJ2:BWJ3 BWN2:BWN3 BWR2:BWR3 BWV2:BWV3 BWZ2:BWZ3 BXD2:BXD3 BXH2:BXH3 BXL2:BXL3 BXP2:BXP3 BXT2:BXT3 BXX2:BXX3 BYB2:BYB3 BYF2:BYF3 BYJ2:BYJ3 BYN2:BYN3 BYR2:BYR3 BYV2:BYV3 BYZ2:BYZ3 BZD2:BZD3 BZH2:BZH3 BZL2:BZL3 BZP2:BZP3 BZT2:BZT3 BZX2:BZX3 CAB2:CAB3 CAF2:CAF3 CAJ2:CAJ3 CAN2:CAN3 CAR2:CAR3 CAV2:CAV3 CAZ2:CAZ3 CBD2:CBD3 CBH2:CBH3 CBL2:CBL3 CBP2:CBP3 CBT2:CBT3 CBX2:CBX3 CCB2:CCB3 CCF2:CCF3 CCJ2:CCJ3 CCN2:CCN3 CCR2:CCR3 CCV2:CCV3 CCZ2:CCZ3 CDD2:CDD3 CDH2:CDH3 CDL2:CDL3 CDP2:CDP3 CDT2:CDT3 CDX2:CDX3 CEB2:CEB3 CEF2:CEF3 CEJ2:CEJ3 CEN2:CEN3 CER2:CER3 CEV2:CEV3 CEZ2:CEZ3 CFD2:CFD3 CFH2:CFH3 CFL2:CFL3 CFP2:CFP3 CFT2:CFT3 CFX2:CFX3 CGB2:CGB3 CGF2:CGF3 CGJ2:CGJ3 CGN2:CGN3 CGR2:CGR3 CGV2:CGV3 CGZ2:CGZ3 CHD2:CHD3 CHH2:CHH3 CHL2:CHL3 CHP2:CHP3 CHT2:CHT3 CHX2:CHX3 CIB2:CIB3 CIF2:CIF3 CIJ2:CIJ3 CIN2:CIN3 CIR2:CIR3 CIV2:CIV3 CIZ2:CIZ3 CJD2:CJD3 CJH2:CJH3 CJL2:CJL3 CJP2:CJP3 CJT2:CJT3 CJX2:CJX3 CKB2:CKB3 CKF2:CKF3 CKJ2:CKJ3 CKN2:CKN3 CKR2:CKR3 CKV2:CKV3 CKZ2:CKZ3 CLD2:CLD3 CLH2:CLH3 CLL2:CLL3 CLP2:CLP3 CLT2:CLT3 CLX2:CLX3 CMB2:CMB3 CMF2:CMF3 CMJ2:CMJ3 CMN2:CMN3 CMR2:CMR3 CMV2:CMV3 CMZ2:CMZ3 CND2:CND3 CNH2:CNH3 CNL2:CNL3 CNP2:CNP3 CNT2:CNT3 CNX2:CNX3 COB2:COB3 COF2:COF3 COJ2:COJ3 CON2:CON3 COR2:COR3 COV2:COV3 COZ2:COZ3 CPD2:CPD3 CPH2:CPH3 CPL2:CPL3 CPP2:CPP3 CPT2:CPT3 CPX2:CPX3 CQB2:CQB3 CQF2:CQF3 CQJ2:CQJ3 CQN2:CQN3 CQR2:CQR3 CQV2:CQV3 CQZ2:CQZ3 CRD2:CRD3 CRH2:CRH3 CRL2:CRL3 CRP2:CRP3 CRT2:CRT3 CRX2:CRX3 CSB2:CSB3 CSF2:CSF3 CSJ2:CSJ3 CSN2:CSN3 CSR2:CSR3 CSV2:CSV3 CSZ2:CSZ3 CTD2:CTD3 CTH2:CTH3 CTL2:CTL3 CTP2:CTP3 CTT2:CTT3 CTX2:CTX3 CUB2:CUB3 CUF2:CUF3 CUJ2:CUJ3 CUN2:CUN3 CUR2:CUR3 CUV2:CUV3 CUZ2:CUZ3 CVD2:CVD3 CVH2:CVH3 CVL2:CVL3 CVP2:CVP3 CVT2:CVT3 CVX2:CVX3 CWB2:CWB3 CWF2:CWF3 CWJ2:CWJ3 CWN2:CWN3 CWR2:CWR3 CWV2:CWV3 CWZ2:CWZ3 CXD2:CXD3 CXH2:CXH3 CXL2:CXL3 CXP2:CXP3 CXT2:CXT3 CXX2:CXX3 CYB2:CYB3 CYF2:CYF3 CYJ2:CYJ3 CYN2:CYN3 CYR2:CYR3 CYV2:CYV3 CYZ2:CYZ3 CZD2:CZD3 CZH2:CZH3 CZL2:CZL3 CZP2:CZP3 CZT2:CZT3 CZX2:CZX3 DAB2:DAB3 DAF2:DAF3 DAJ2:DAJ3 DAN2:DAN3 DAR2:DAR3 DAV2:DAV3 DAZ2:DAZ3 DBD2:DBD3 DBH2:DBH3 DBL2:DBL3 DBP2:DBP3 DBT2:DBT3 DBX2:DBX3 DCB2:DCB3 DCF2:DCF3 DCJ2:DCJ3 DCN2:DCN3 DCR2:DCR3 DCV2:DCV3 DCZ2:DCZ3 DDD2:DDD3 DDH2:DDH3 DDL2:DDL3 DDP2:DDP3 DDT2:DDT3 DDX2:DDX3 DEB2:DEB3 DEF2:DEF3 DEJ2:DEJ3 DEN2:DEN3 DER2:DER3 DEV2:DEV3 DEZ2:DEZ3 DFD2:DFD3 DFH2:DFH3 DFL2:DFL3 DFP2:DFP3 DFT2:DFT3 DFX2:DFX3 DGB2:DGB3 DGF2:DGF3 DGJ2:DGJ3 DGN2:DGN3 DGR2:DGR3 DGV2:DGV3 DGZ2:DGZ3 DHD2:DHD3 DHH2:DHH3 DHL2:DHL3 DHP2:DHP3 DHT2:DHT3 DHX2:DHX3 DIB2:DIB3 DIF2:DIF3 DIJ2:DIJ3 DIN2:DIN3 DIR2:DIR3 DIV2:DIV3 DIZ2:DIZ3 DJD2:DJD3 DJH2:DJH3 DJL2:DJL3 DJP2:DJP3 DJT2:DJT3 DJX2:DJX3 DKB2:DKB3 DKF2:DKF3 DKJ2:DKJ3 DKN2:DKN3 DKR2:DKR3 DKV2:DKV3 DKZ2:DKZ3 DLD2:DLD3 DLH2:DLH3 DLL2:DLL3 DLP2:DLP3 DLT2:DLT3 DLX2:DLX3 DMB2:DMB3 DMF2:DMF3 DMJ2:DMJ3 DMN2:DMN3 DMR2:DMR3 DMV2:DMV3 DMZ2:DMZ3 DND2:DND3 DNH2:DNH3 DNL2:DNL3 DNP2:DNP3 DNT2:DNT3 DNX2:DNX3 DOB2:DOB3 DOF2:DOF3 DOJ2:DOJ3 DON2:DON3 DOR2:DOR3 DOV2:DOV3 DOZ2:DOZ3 DPD2:DPD3 DPH2:DPH3 DPL2:DPL3 DPP2:DPP3 DPT2:DPT3 DPX2:DPX3 DQB2:DQB3 DQF2:DQF3 DQJ2:DQJ3 DQN2:DQN3 DQR2:DQR3 DQV2:DQV3 DQZ2:DQZ3 DRD2:DRD3 DRH2:DRH3 DRL2:DRL3 DRP2:DRP3 DRT2:DRT3 DRX2:DRX3 DSB2:DSB3 DSF2:DSF3 DSJ2:DSJ3 DSN2:DSN3 DSR2:DSR3 DSV2:DSV3 DSZ2:DSZ3 DTD2:DTD3 DTH2:DTH3 DTL2:DTL3 DTP2:DTP3 DTT2:DTT3 DTX2:DTX3 DUB2:DUB3 DUF2:DUF3 DUJ2:DUJ3 DUN2:DUN3 DUR2:DUR3 DUV2:DUV3 DUZ2:DUZ3 DVD2:DVD3 DVH2:DVH3 DVL2:DVL3 DVP2:DVP3 DVT2:DVT3 DVX2:DVX3 DWB2:DWB3 DWF2:DWF3 DWJ2:DWJ3 DWN2:DWN3 DWR2:DWR3 DWV2:DWV3 DWZ2:DWZ3 DXD2:DXD3 DXH2:DXH3 DXL2:DXL3 DXP2:DXP3 DXT2:DXT3 DXX2:DXX3 DYB2:DYB3 DYF2:DYF3 DYJ2:DYJ3 DYN2:DYN3 DYR2:DYR3 DYV2:DYV3 DYZ2:DYZ3 DZD2:DZD3 DZH2:DZH3 DZL2:DZL3 DZP2:DZP3 DZT2:DZT3 DZX2:DZX3 EAB2:EAB3 EAF2:EAF3 EAJ2:EAJ3 EAN2:EAN3 EAR2:EAR3 EAV2:EAV3 EAZ2:EAZ3 EBD2:EBD3 EBH2:EBH3 EBL2:EBL3 EBP2:EBP3 EBT2:EBT3 EBX2:EBX3 ECB2:ECB3 ECF2:ECF3 ECJ2:ECJ3 ECN2:ECN3 ECR2:ECR3 ECV2:ECV3 ECZ2:ECZ3 EDD2:EDD3 EDH2:EDH3 EDL2:EDL3 EDP2:EDP3 EDT2:EDT3 EDX2:EDX3 EEB2:EEB3 EEF2:EEF3 EEJ2:EEJ3 EEN2:EEN3 EER2:EER3 EEV2:EEV3 EEZ2:EEZ3 EFD2:EFD3 EFH2:EFH3 EFL2:EFL3 EFP2:EFP3 EFT2:EFT3 EFX2:EFX3 EGB2:EGB3 EGF2:EGF3 EGJ2:EGJ3 EGN2:EGN3 EGR2:EGR3 EGV2:EGV3 EGZ2:EGZ3 EHD2:EHD3 EHH2:EHH3 EHL2:EHL3 EHP2:EHP3 EHT2:EHT3 EHX2:EHX3 EIB2:EIB3 EIF2:EIF3 EIJ2:EIJ3 EIN2:EIN3 EIR2:EIR3 EIV2:EIV3 EIZ2:EIZ3 EJD2:EJD3 EJH2:EJH3 EJL2:EJL3 EJP2:EJP3 EJT2:EJT3 EJX2:EJX3 EKB2:EKB3 EKF2:EKF3 EKJ2:EKJ3 EKN2:EKN3 EKR2:EKR3 EKV2:EKV3 EKZ2:EKZ3 ELD2:ELD3 ELH2:ELH3 ELL2:ELL3 ELP2:ELP3 ELT2:ELT3 ELX2:ELX3 EMB2:EMB3 EMF2:EMF3 EMJ2:EMJ3 EMN2:EMN3 EMR2:EMR3 EMV2:EMV3 EMZ2:EMZ3 END2:END3 ENH2:ENH3 ENL2:ENL3 ENP2:ENP3 ENT2:ENT3 ENX2:ENX3 EOB2:EOB3 EOF2:EOF3 EOJ2:EOJ3 EON2:EON3 EOR2:EOR3 EOV2:EOV3 EOZ2:EOZ3 EPD2:EPD3 EPH2:EPH3 EPL2:EPL3 EPP2:EPP3 EPT2:EPT3 EPX2:EPX3 EQB2:EQB3 EQF2:EQF3 EQJ2:EQJ3 EQN2:EQN3 EQR2:EQR3 EQV2:EQV3 EQZ2:EQZ3 ERD2:ERD3 ERH2:ERH3 ERL2:ERL3 ERP2:ERP3 ERT2:ERT3 ERX2:ERX3 ESB2:ESB3 ESF2:ESF3 ESJ2:ESJ3 ESN2:ESN3 ESR2:ESR3 ESV2:ESV3 ESZ2:ESZ3 ETD2:ETD3 ETH2:ETH3 ETL2:ETL3 ETP2:ETP3 ETT2:ETT3 ETX2:ETX3 EUB2:EUB3 EUF2:EUF3 EUJ2:EUJ3 EUN2:EUN3 EUR2:EUR3 EUV2:EUV3 EUZ2:EUZ3 EVD2:EVD3 EVH2:EVH3 EVL2:EVL3 EVP2:EVP3 EVT2:EVT3 EVX2:EVX3 EWB2:EWB3 EWF2:EWF3 EWJ2:EWJ3 EWN2:EWN3 EWR2:EWR3 EWV2:EWV3 EWZ2:EWZ3 EXD2:EXD3 EXH2:EXH3 EXL2:EXL3 EXP2:EXP3 EXT2:EXT3 EXX2:EXX3 EYB2:EYB3 EYF2:EYF3 EYJ2:EYJ3 EYN2:EYN3 EYR2:EYR3 EYV2:EYV3 EYZ2:EYZ3 EZD2:EZD3 EZH2:EZH3 EZL2:EZL3 EZP2:EZP3 EZT2:EZT3 EZX2:EZX3 FAB2:FAB3 FAF2:FAF3 FAJ2:FAJ3 FAN2:FAN3 FAR2:FAR3 FAV2:FAV3 FAZ2:FAZ3 FBD2:FBD3 FBH2:FBH3 FBL2:FBL3 FBP2:FBP3 FBT2:FBT3 FBX2:FBX3 FCB2:FCB3 FCF2:FCF3 FCJ2:FCJ3 FCN2:FCN3 FCR2:FCR3 FCV2:FCV3 FCZ2:FCZ3 FDD2:FDD3 FDH2:FDH3 FDL2:FDL3 FDP2:FDP3 FDT2:FDT3 FDX2:FDX3 FEB2:FEB3 FEF2:FEF3 FEJ2:FEJ3 FEN2:FEN3 FER2:FER3 FEV2:FEV3 FEZ2:FEZ3 FFD2:FFD3 FFH2:FFH3 FFL2:FFL3 FFP2:FFP3 FFT2:FFT3 FFX2:FFX3 FGB2:FGB3 FGF2:FGF3 FGJ2:FGJ3 FGN2:FGN3 FGR2:FGR3 FGV2:FGV3 FGZ2:FGZ3 FHD2:FHD3 FHH2:FHH3 FHL2:FHL3 FHP2:FHP3 FHT2:FHT3 FHX2:FHX3 FIB2:FIB3 FIF2:FIF3 FIJ2:FIJ3 FIN2:FIN3 FIR2:FIR3 FIV2:FIV3 FIZ2:FIZ3 FJD2:FJD3 FJH2:FJH3 FJL2:FJL3 FJP2:FJP3 FJT2:FJT3 FJX2:FJX3 FKB2:FKB3 FKF2:FKF3 FKJ2:FKJ3 FKN2:FKN3 FKR2:FKR3 FKV2:FKV3 FKZ2:FKZ3 FLD2:FLD3 FLH2:FLH3 FLL2:FLL3 FLP2:FLP3 FLT2:FLT3 FLX2:FLX3 FMB2:FMB3 FMF2:FMF3 FMJ2:FMJ3 FMN2:FMN3 FMR2:FMR3 FMV2:FMV3 FMZ2:FMZ3 FND2:FND3 FNH2:FNH3 FNL2:FNL3 FNP2:FNP3 FNT2:FNT3 FNX2:FNX3 FOB2:FOB3 FOF2:FOF3 FOJ2:FOJ3 FON2:FON3 FOR2:FOR3 FOV2:FOV3 FOZ2:FOZ3 FPD2:FPD3 FPH2:FPH3 FPL2:FPL3 FPP2:FPP3 FPT2:FPT3 FPX2:FPX3 FQB2:FQB3 FQF2:FQF3 FQJ2:FQJ3 FQN2:FQN3 FQR2:FQR3 FQV2:FQV3 FQZ2:FQZ3 FRD2:FRD3 FRH2:FRH3 FRL2:FRL3 FRP2:FRP3 FRT2:FRT3 FRX2:FRX3 FSB2:FSB3 FSF2:FSF3 FSJ2:FSJ3 FSN2:FSN3 FSR2:FSR3 FSV2:FSV3 FSZ2:FSZ3 FTD2:FTD3 FTH2:FTH3 FTL2:FTL3 FTP2:FTP3 FTT2:FTT3 FTX2:FTX3 FUB2:FUB3 FUF2:FUF3 FUJ2:FUJ3 FUN2:FUN3 FUR2:FUR3 FUV2:FUV3 FUZ2:FUZ3 FVD2:FVD3 FVH2:FVH3 FVL2:FVL3 FVP2:FVP3 FVT2:FVT3 FVX2:FVX3 FWB2:FWB3 FWF2:FWF3 FWJ2:FWJ3 FWN2:FWN3 FWR2:FWR3 FWV2:FWV3 FWZ2:FWZ3 FXD2:FXD3 FXH2:FXH3 FXL2:FXL3 FXP2:FXP3 FXT2:FXT3 FXX2:FXX3 FYB2:FYB3 FYF2:FYF3 FYJ2:FYJ3 FYN2:FYN3 FYR2:FYR3 FYV2:FYV3 FYZ2:FYZ3 FZD2:FZD3 FZH2:FZH3 FZL2:FZL3 FZP2:FZP3 FZT2:FZT3 FZX2:FZX3 GAB2:GAB3 GAF2:GAF3 GAJ2:GAJ3 GAN2:GAN3 GAR2:GAR3 GAV2:GAV3 GAZ2:GAZ3 GBD2:GBD3 GBH2:GBH3 GBL2:GBL3 GBP2:GBP3 GBT2:GBT3 GBX2:GBX3 GCB2:GCB3 GCF2:GCF3 GCJ2:GCJ3 GCN2:GCN3 GCR2:GCR3 GCV2:GCV3 GCZ2:GCZ3 GDD2:GDD3 GDH2:GDH3 GDL2:GDL3 GDP2:GDP3 GDT2:GDT3 GDX2:GDX3 GEB2:GEB3 GEF2:GEF3 GEJ2:GEJ3 GEN2:GEN3 GER2:GER3 GEV2:GEV3 GEZ2:GEZ3 GFD2:GFD3 GFH2:GFH3 GFL2:GFL3 GFP2:GFP3 GFT2:GFT3 GFX2:GFX3 GGB2:GGB3 GGF2:GGF3 GGJ2:GGJ3 GGN2:GGN3 GGR2:GGR3 GGV2:GGV3 GGZ2:GGZ3 GHD2:GHD3 GHH2:GHH3 GHL2:GHL3 GHP2:GHP3 GHT2:GHT3 GHX2:GHX3 GIB2:GIB3 GIF2:GIF3 GIJ2:GIJ3 GIN2:GIN3 GIR2:GIR3 GIV2:GIV3 GIZ2:GIZ3 GJD2:GJD3 GJH2:GJH3 GJL2:GJL3 GJP2:GJP3 GJT2:GJT3 GJX2:GJX3 GKB2:GKB3 GKF2:GKF3 GKJ2:GKJ3 GKN2:GKN3 GKR2:GKR3 GKV2:GKV3 GKZ2:GKZ3 GLD2:GLD3 GLH2:GLH3 GLL2:GLL3 GLP2:GLP3 GLT2:GLT3 GLX2:GLX3 GMB2:GMB3 GMF2:GMF3 GMJ2:GMJ3 GMN2:GMN3 GMR2:GMR3 GMV2:GMV3 GMZ2:GMZ3 GND2:GND3 GNH2:GNH3 GNL2:GNL3 GNP2:GNP3 GNT2:GNT3 GNX2:GNX3 GOB2:GOB3 GOF2:GOF3 GOJ2:GOJ3 GON2:GON3 GOR2:GOR3 GOV2:GOV3 GOZ2:GOZ3 GPD2:GPD3 GPH2:GPH3 GPL2:GPL3 GPP2:GPP3 GPT2:GPT3 GPX2:GPX3 GQB2:GQB3 GQF2:GQF3 GQJ2:GQJ3 GQN2:GQN3 GQR2:GQR3 GQV2:GQV3 GQZ2:GQZ3 GRD2:GRD3 GRH2:GRH3 GRL2:GRL3 GRP2:GRP3 GRT2:GRT3 GRX2:GRX3 GSB2:GSB3 GSF2:GSF3 GSJ2:GSJ3 GSN2:GSN3 GSR2:GSR3 GSV2:GSV3 GSZ2:GSZ3 GTD2:GTD3 GTH2:GTH3 GTL2:GTL3 GTP2:GTP3 GTT2:GTT3 GTX2:GTX3 GUB2:GUB3 GUF2:GUF3 GUJ2:GUJ3 GUN2:GUN3 GUR2:GUR3 GUV2:GUV3 GUZ2:GUZ3 GVD2:GVD3 GVH2:GVH3 GVL2:GVL3 GVP2:GVP3 GVT2:GVT3 GVX2:GVX3 GWB2:GWB3 GWF2:GWF3 GWJ2:GWJ3 GWN2:GWN3 GWR2:GWR3 GWV2:GWV3 GWZ2:GWZ3 GXD2:GXD3 GXH2:GXH3 GXL2:GXL3 GXP2:GXP3 GXT2:GXT3 GXX2:GXX3 GYB2:GYB3 GYF2:GYF3 GYJ2:GYJ3 GYN2:GYN3 GYR2:GYR3 GYV2:GYV3 GYZ2:GYZ3 GZD2:GZD3 GZH2:GZH3 GZL2:GZL3 GZP2:GZP3 GZT2:GZT3 GZX2:GZX3 HAB2:HAB3 HAF2:HAF3 HAJ2:HAJ3 HAN2:HAN3 HAR2:HAR3 HAV2:HAV3 HAZ2:HAZ3 HBD2:HBD3 HBH2:HBH3 HBL2:HBL3 HBP2:HBP3 HBT2:HBT3 HBX2:HBX3 HCB2:HCB3 HCF2:HCF3 HCJ2:HCJ3 HCN2:HCN3 HCR2:HCR3 HCV2:HCV3 HCZ2:HCZ3 HDD2:HDD3 HDH2:HDH3 HDL2:HDL3 HDP2:HDP3 HDT2:HDT3 HDX2:HDX3 HEB2:HEB3 HEF2:HEF3 HEJ2:HEJ3 HEN2:HEN3 HER2:HER3 HEV2:HEV3 HEZ2:HEZ3 HFD2:HFD3 HFH2:HFH3 HFL2:HFL3 HFP2:HFP3 HFT2:HFT3 HFX2:HFX3 HGB2:HGB3 HGF2:HGF3 HGJ2:HGJ3 HGN2:HGN3 HGR2:HGR3 HGV2:HGV3 HGZ2:HGZ3 HHD2:HHD3 HHH2:HHH3 HHL2:HHL3 HHP2:HHP3 HHT2:HHT3 HHX2:HHX3 HIB2:HIB3 HIF2:HIF3 HIJ2:HIJ3 HIN2:HIN3 HIR2:HIR3 HIV2:HIV3 HIZ2:HIZ3 HJD2:HJD3 HJH2:HJH3 HJL2:HJL3 HJP2:HJP3 HJT2:HJT3 HJX2:HJX3 HKB2:HKB3 HKF2:HKF3 HKJ2:HKJ3 HKN2:HKN3 HKR2:HKR3 HKV2:HKV3 HKZ2:HKZ3 HLD2:HLD3 HLH2:HLH3 HLL2:HLL3 HLP2:HLP3 HLT2:HLT3 HLX2:HLX3 HMB2:HMB3 HMF2:HMF3 HMJ2:HMJ3 HMN2:HMN3 HMR2:HMR3 HMV2:HMV3 HMZ2:HMZ3 HND2:HND3 HNH2:HNH3 HNL2:HNL3 HNP2:HNP3 HNT2:HNT3 HNX2:HNX3 HOB2:HOB3 HOF2:HOF3 HOJ2:HOJ3 HON2:HON3 HOR2:HOR3 HOV2:HOV3 HOZ2:HOZ3 HPD2:HPD3 HPH2:HPH3 HPL2:HPL3 HPP2:HPP3 HPT2:HPT3 HPX2:HPX3 HQB2:HQB3 HQF2:HQF3 HQJ2:HQJ3 HQN2:HQN3 HQR2:HQR3 HQV2:HQV3 HQZ2:HQZ3 HRD2:HRD3 HRH2:HRH3 HRL2:HRL3 HRP2:HRP3 HRT2:HRT3 HRX2:HRX3 HSB2:HSB3 HSF2:HSF3 HSJ2:HSJ3 HSN2:HSN3 HSR2:HSR3 HSV2:HSV3 HSZ2:HSZ3 HTD2:HTD3 HTH2:HTH3 HTL2:HTL3 HTP2:HTP3 HTT2:HTT3 HTX2:HTX3 HUB2:HUB3 HUF2:HUF3 HUJ2:HUJ3 HUN2:HUN3 HUR2:HUR3 HUV2:HUV3 HUZ2:HUZ3 HVD2:HVD3 HVH2:HVH3 HVL2:HVL3 HVP2:HVP3 HVT2:HVT3 HVX2:HVX3 HWB2:HWB3 HWF2:HWF3 HWJ2:HWJ3 HWN2:HWN3 HWR2:HWR3 HWV2:HWV3 HWZ2:HWZ3 HXD2:HXD3 HXH2:HXH3 HXL2:HXL3 HXP2:HXP3 HXT2:HXT3 HXX2:HXX3 HYB2:HYB3 HYF2:HYF3 HYJ2:HYJ3 HYN2:HYN3 HYR2:HYR3 HYV2:HYV3 HYZ2:HYZ3 HZD2:HZD3 HZH2:HZH3 HZL2:HZL3 HZP2:HZP3 HZT2:HZT3 HZX2:HZX3 IAB2:IAB3 IAF2:IAF3 IAJ2:IAJ3 IAN2:IAN3 IAR2:IAR3 IAV2:IAV3 IAZ2:IAZ3 IBD2:IBD3 IBH2:IBH3 IBL2:IBL3 IBP2:IBP3 IBT2:IBT3 IBX2:IBX3 ICB2:ICB3 ICF2:ICF3 ICJ2:ICJ3 ICN2:ICN3 ICR2:ICR3 ICV2:ICV3 ICZ2:ICZ3 IDD2:IDD3 IDH2:IDH3 IDL2:IDL3 IDP2:IDP3 IDT2:IDT3 IDX2:IDX3 IEB2:IEB3 IEF2:IEF3 IEJ2:IEJ3 IEN2:IEN3 IER2:IER3 IEV2:IEV3 IEZ2:IEZ3 IFD2:IFD3 IFH2:IFH3 IFL2:IFL3 IFP2:IFP3 IFT2:IFT3 IFX2:IFX3 IGB2:IGB3 IGF2:IGF3 IGJ2:IGJ3 IGN2:IGN3 IGR2:IGR3 IGV2:IGV3 IGZ2:IGZ3 IHD2:IHD3 IHH2:IHH3 IHL2:IHL3 IHP2:IHP3 IHT2:IHT3 IHX2:IHX3 IIB2:IIB3 IIF2:IIF3 IIJ2:IIJ3 IIN2:IIN3 IIR2:IIR3 IIV2:IIV3 IIZ2:IIZ3 IJD2:IJD3 IJH2:IJH3 IJL2:IJL3 IJP2:IJP3 IJT2:IJT3 IJX2:IJX3 IKB2:IKB3 IKF2:IKF3 IKJ2:IKJ3 IKN2:IKN3 IKR2:IKR3 IKV2:IKV3 IKZ2:IKZ3 ILD2:ILD3 ILH2:ILH3 ILL2:ILL3 ILP2:ILP3 ILT2:ILT3 ILX2:ILX3 IMB2:IMB3 IMF2:IMF3 IMJ2:IMJ3 IMN2:IMN3 IMR2:IMR3 IMV2:IMV3 IMZ2:IMZ3 IND2:IND3 INH2:INH3 INL2:INL3 INP2:INP3 INT2:INT3 INX2:INX3 IOB2:IOB3 IOF2:IOF3 IOJ2:IOJ3 ION2:ION3 IOR2:IOR3 IOV2:IOV3 IOZ2:IOZ3 IPD2:IPD3 IPH2:IPH3 IPL2:IPL3 IPP2:IPP3 IPT2:IPT3 IPX2:IPX3 IQB2:IQB3 IQF2:IQF3 IQJ2:IQJ3 IQN2:IQN3 IQR2:IQR3 IQV2:IQV3 IQZ2:IQZ3 IRD2:IRD3 IRH2:IRH3 IRL2:IRL3 IRP2:IRP3 IRT2:IRT3 IRX2:IRX3 ISB2:ISB3 ISF2:ISF3 ISJ2:ISJ3 ISN2:ISN3 ISR2:ISR3 ISV2:ISV3 ISZ2:ISZ3 ITD2:ITD3 ITH2:ITH3 ITL2:ITL3 ITP2:ITP3 ITT2:ITT3 ITX2:ITX3 IUB2:IUB3 IUF2:IUF3 IUJ2:IUJ3 IUN2:IUN3 IUR2:IUR3 IUV2:IUV3 IUZ2:IUZ3 IVD2:IVD3 IVH2:IVH3 IVL2:IVL3 IVP2:IVP3 IVT2:IVT3 IVX2:IVX3 IWB2:IWB3 IWF2:IWF3 IWJ2:IWJ3 IWN2:IWN3 IWR2:IWR3 IWV2:IWV3 IWZ2:IWZ3 IXD2:IXD3 IXH2:IXH3 IXL2:IXL3 IXP2:IXP3 IXT2:IXT3 IXX2:IXX3 IYB2:IYB3 IYF2:IYF3 IYJ2:IYJ3 IYN2:IYN3 IYR2:IYR3 IYV2:IYV3 IYZ2:IYZ3 IZD2:IZD3 IZH2:IZH3 IZL2:IZL3 IZP2:IZP3 IZT2:IZT3 IZX2:IZX3 JAB2:JAB3 JAF2:JAF3 JAJ2:JAJ3 JAN2:JAN3 JAR2:JAR3 JAV2:JAV3 JAZ2:JAZ3 JBD2:JBD3 JBH2:JBH3 JBL2:JBL3 JBP2:JBP3 JBT2:JBT3 JBX2:JBX3 JCB2:JCB3 JCF2:JCF3 JCJ2:JCJ3 JCN2:JCN3 JCR2:JCR3 JCV2:JCV3 JCZ2:JCZ3 JDD2:JDD3 JDH2:JDH3 JDL2:JDL3 JDP2:JDP3 JDT2:JDT3 JDX2:JDX3 JEB2:JEB3 JEF2:JEF3 JEJ2:JEJ3 JEN2:JEN3 JER2:JER3 JEV2:JEV3 JEZ2:JEZ3 JFD2:JFD3 JFH2:JFH3 JFL2:JFL3 JFP2:JFP3 JFT2:JFT3 JFX2:JFX3 JGB2:JGB3 JGF2:JGF3 JGJ2:JGJ3 JGN2:JGN3 JGR2:JGR3 JGV2:JGV3 JGZ2:JGZ3 JHD2:JHD3 JHH2:JHH3 JHL2:JHL3 JHP2:JHP3 JHT2:JHT3 JHX2:JHX3 JIB2:JIB3 JIF2:JIF3 JIJ2:JIJ3 JIN2:JIN3 JIR2:JIR3 JIV2:JIV3 JIZ2:JIZ3 JJD2:JJD3 JJH2:JJH3 JJL2:JJL3 JJP2:JJP3 JJT2:JJT3 JJX2:JJX3 JKB2:JKB3 JKF2:JKF3 JKJ2:JKJ3 JKN2:JKN3 JKR2:JKR3 JKV2:JKV3 JKZ2:JKZ3 JLD2:JLD3 JLH2:JLH3 JLL2:JLL3 JLP2:JLP3 JLT2:JLT3 JLX2:JLX3 JMB2:JMB3 JMF2:JMF3 JMJ2:JMJ3 JMN2:JMN3 JMR2:JMR3 JMV2:JMV3 JMZ2:JMZ3 JND2:JND3 JNH2:JNH3 JNL2:JNL3 JNP2:JNP3 JNT2:JNT3 JNX2:JNX3 JOB2:JOB3 JOF2:JOF3 JOJ2:JOJ3 JON2:JON3 JOR2:JOR3 JOV2:JOV3 JOZ2:JOZ3 JPD2:JPD3 JPH2:JPH3 JPL2:JPL3 JPP2:JPP3 JPT2:JPT3 JPX2:JPX3 JQB2:JQB3 JQF2:JQF3 JQJ2:JQJ3 JQN2:JQN3 JQR2:JQR3 JQV2:JQV3 JQZ2:JQZ3 JRD2:JRD3 JRH2:JRH3 JRL2:JRL3 JRP2:JRP3 JRT2:JRT3 JRX2:JRX3 JSB2:JSB3 JSF2:JSF3 JSJ2:JSJ3 JSN2:JSN3 JSR2:JSR3 JSV2:JSV3 JSZ2:JSZ3 JTD2:JTD3 JTH2:JTH3 JTL2:JTL3 JTP2:JTP3 JTT2:JTT3 JTX2:JTX3 JUB2:JUB3 JUF2:JUF3 JUJ2:JUJ3 JUN2:JUN3 JUR2:JUR3 JUV2:JUV3 JUZ2:JUZ3 JVD2:JVD3 JVH2:JVH3 JVL2:JVL3 JVP2:JVP3 JVT2:JVT3 JVX2:JVX3 JWB2:JWB3 JWF2:JWF3 JWJ2:JWJ3 JWN2:JWN3 JWR2:JWR3 JWV2:JWV3 JWZ2:JWZ3 JXD2:JXD3 JXH2:JXH3 JXL2:JXL3 JXP2:JXP3 JXT2:JXT3 JXX2:JXX3 JYB2:JYB3 JYF2:JYF3 JYJ2:JYJ3 JYN2:JYN3 JYR2:JYR3 JYV2:JYV3 JYZ2:JYZ3 JZD2:JZD3 JZH2:JZH3 JZL2:JZL3 JZP2:JZP3 JZT2:JZT3 JZX2:JZX3 KAB2:KAB3 KAF2:KAF3 KAJ2:KAJ3 KAN2:KAN3 KAR2:KAR3 KAV2:KAV3 KAZ2:KAZ3 KBD2:KBD3 KBH2:KBH3 KBL2:KBL3 KBP2:KBP3 KBT2:KBT3 KBX2:KBX3 KCB2:KCB3 KCF2:KCF3 KCJ2:KCJ3 KCN2:KCN3 KCR2:KCR3 KCV2:KCV3 KCZ2:KCZ3 KDD2:KDD3 KDH2:KDH3 KDL2:KDL3 KDP2:KDP3 KDT2:KDT3 KDX2:KDX3 KEB2:KEB3 KEF2:KEF3 KEJ2:KEJ3 KEN2:KEN3 KER2:KER3 KEV2:KEV3 KEZ2:KEZ3 KFD2:KFD3 KFH2:KFH3 KFL2:KFL3 KFP2:KFP3 KFT2:KFT3 KFX2:KFX3 KGB2:KGB3 KGF2:KGF3 KGJ2:KGJ3 KGN2:KGN3 KGR2:KGR3 KGV2:KGV3 KGZ2:KGZ3 KHD2:KHD3 KHH2:KHH3 KHL2:KHL3 KHP2:KHP3 KHT2:KHT3 KHX2:KHX3 KIB2:KIB3 KIF2:KIF3 KIJ2:KIJ3 KIN2:KIN3 KIR2:KIR3 KIV2:KIV3 KIZ2:KIZ3 KJD2:KJD3 KJH2:KJH3 KJL2:KJL3 KJP2:KJP3 KJT2:KJT3 KJX2:KJX3 KKB2:KKB3 KKF2:KKF3 KKJ2:KKJ3 KKN2:KKN3 KKR2:KKR3 KKV2:KKV3 KKZ2:KKZ3 KLD2:KLD3 KLH2:KLH3 KLL2:KLL3 KLP2:KLP3 KLT2:KLT3 KLX2:KLX3 KMB2:KMB3 KMF2:KMF3 KMJ2:KMJ3 KMN2:KMN3 KMR2:KMR3 KMV2:KMV3 KMZ2:KMZ3 KND2:KND3 KNH2:KNH3 KNL2:KNL3 KNP2:KNP3 KNT2:KNT3 KNX2:KNX3 KOB2:KOB3 KOF2:KOF3 KOJ2:KOJ3 KON2:KON3 KOR2:KOR3 KOV2:KOV3 KOZ2:KOZ3 KPD2:KPD3 KPH2:KPH3 KPL2:KPL3 KPP2:KPP3 KPT2:KPT3 KPX2:KPX3 KQB2:KQB3 KQF2:KQF3 KQJ2:KQJ3 KQN2:KQN3 KQR2:KQR3 KQV2:KQV3 KQZ2:KQZ3 KRD2:KRD3 KRH2:KRH3 KRL2:KRL3 KRP2:KRP3 KRT2:KRT3 KRX2:KRX3 KSB2:KSB3 KSF2:KSF3 KSJ2:KSJ3 KSN2:KSN3 KSR2:KSR3 KSV2:KSV3 KSZ2:KSZ3 KTD2:KTD3 KTH2:KTH3 KTL2:KTL3 KTP2:KTP3 KTT2:KTT3 KTX2:KTX3 KUB2:KUB3 KUF2:KUF3 KUJ2:KUJ3 KUN2:KUN3 KUR2:KUR3 KUV2:KUV3 KUZ2:KUZ3 KVD2:KVD3 KVH2:KVH3 KVL2:KVL3 KVP2:KVP3 KVT2:KVT3 KVX2:KVX3 KWB2:KWB3 KWF2:KWF3 KWJ2:KWJ3 KWN2:KWN3 KWR2:KWR3 KWV2:KWV3 KWZ2:KWZ3 KXD2:KXD3 KXH2:KXH3 KXL2:KXL3 KXP2:KXP3 KXT2:KXT3 KXX2:KXX3 KYB2:KYB3 KYF2:KYF3 KYJ2:KYJ3 KYN2:KYN3 KYR2:KYR3 KYV2:KYV3 KYZ2:KYZ3 KZD2:KZD3 KZH2:KZH3 KZL2:KZL3 KZP2:KZP3 KZT2:KZT3 KZX2:KZX3 LAB2:LAB3 LAF2:LAF3 LAJ2:LAJ3 LAN2:LAN3 LAR2:LAR3 LAV2:LAV3 LAZ2:LAZ3 LBD2:LBD3 LBH2:LBH3 LBL2:LBL3 LBP2:LBP3 LBT2:LBT3 LBX2:LBX3 LCB2:LCB3 LCF2:LCF3 LCJ2:LCJ3 LCN2:LCN3 LCR2:LCR3 LCV2:LCV3 LCZ2:LCZ3 LDD2:LDD3 LDH2:LDH3 LDL2:LDL3 LDP2:LDP3 LDT2:LDT3 LDX2:LDX3 LEB2:LEB3 LEF2:LEF3 LEJ2:LEJ3 LEN2:LEN3 LER2:LER3 LEV2:LEV3 LEZ2:LEZ3 LFD2:LFD3 LFH2:LFH3 LFL2:LFL3 LFP2:LFP3 LFT2:LFT3 LFX2:LFX3 LGB2:LGB3 LGF2:LGF3 LGJ2:LGJ3 LGN2:LGN3 LGR2:LGR3 LGV2:LGV3 LGZ2:LGZ3 LHD2:LHD3 LHH2:LHH3 LHL2:LHL3 LHP2:LHP3 LHT2:LHT3 LHX2:LHX3 LIB2:LIB3 LIF2:LIF3 LIJ2:LIJ3 LIN2:LIN3 LIR2:LIR3 LIV2:LIV3 LIZ2:LIZ3 LJD2:LJD3 LJH2:LJH3 LJL2:LJL3 LJP2:LJP3 LJT2:LJT3 LJX2:LJX3 LKB2:LKB3 LKF2:LKF3 LKJ2:LKJ3 LKN2:LKN3 LKR2:LKR3 LKV2:LKV3 LKZ2:LKZ3 LLD2:LLD3 LLH2:LLH3 LLL2:LLL3 LLP2:LLP3 LLT2:LLT3 LLX2:LLX3 LMB2:LMB3 LMF2:LMF3 LMJ2:LMJ3 LMN2:LMN3 LMR2:LMR3 LMV2:LMV3 LMZ2:LMZ3 LND2:LND3 LNH2:LNH3 LNL2:LNL3 LNP2:LNP3 LNT2:LNT3 LNX2:LNX3 LOB2:LOB3 LOF2:LOF3 LOJ2:LOJ3 LON2:LON3 LOR2:LOR3 LOV2:LOV3 LOZ2:LOZ3 LPD2:LPD3 LPH2:LPH3 LPL2:LPL3 LPP2:LPP3 LPT2:LPT3 LPX2:LPX3 LQB2:LQB3 LQF2:LQF3 LQJ2:LQJ3 LQN2:LQN3 LQR2:LQR3 LQV2:LQV3 LQZ2:LQZ3 LRD2:LRD3 LRH2:LRH3 LRL2:LRL3 LRP2:LRP3 LRT2:LRT3 LRX2:LRX3 LSB2:LSB3 LSF2:LSF3 LSJ2:LSJ3 LSN2:LSN3 LSR2:LSR3 LSV2:LSV3 LSZ2:LSZ3 LTD2:LTD3 LTH2:LTH3 LTL2:LTL3 LTP2:LTP3 LTT2:LTT3 LTX2:LTX3 LUB2:LUB3 LUF2:LUF3 LUJ2:LUJ3 LUN2:LUN3 LUR2:LUR3 LUV2:LUV3 LUZ2:LUZ3 LVD2:LVD3 LVH2:LVH3 LVL2:LVL3 LVP2:LVP3 LVT2:LVT3 LVX2:LVX3 LWB2:LWB3 LWF2:LWF3 LWJ2:LWJ3 LWN2:LWN3 LWR2:LWR3 LWV2:LWV3 LWZ2:LWZ3 LXD2:LXD3 LXH2:LXH3 LXL2:LXL3 LXP2:LXP3 LXT2:LXT3 LXX2:LXX3 LYB2:LYB3 LYF2:LYF3 LYJ2:LYJ3 LYN2:LYN3 LYR2:LYR3 LYV2:LYV3 LYZ2:LYZ3 LZD2:LZD3 LZH2:LZH3 LZL2:LZL3 LZP2:LZP3 LZT2:LZT3 LZX2:LZX3 MAB2:MAB3 MAF2:MAF3 MAJ2:MAJ3 MAN2:MAN3 MAR2:MAR3 MAV2:MAV3 MAZ2:MAZ3 MBD2:MBD3 MBH2:MBH3 MBL2:MBL3 MBP2:MBP3 MBT2:MBT3 MBX2:MBX3 MCB2:MCB3 MCF2:MCF3 MCJ2:MCJ3 MCN2:MCN3 MCR2:MCR3 MCV2:MCV3 MCZ2:MCZ3 MDD2:MDD3 MDH2:MDH3 MDL2:MDL3 MDP2:MDP3 MDT2:MDT3 MDX2:MDX3 MEB2:MEB3 MEF2:MEF3 MEJ2:MEJ3 MEN2:MEN3 MER2:MER3 MEV2:MEV3 MEZ2:MEZ3 MFD2:MFD3 MFH2:MFH3 MFL2:MFL3 MFP2:MFP3 MFT2:MFT3 MFX2:MFX3 MGB2:MGB3 MGF2:MGF3 MGJ2:MGJ3 MGN2:MGN3 MGR2:MGR3 MGV2:MGV3 MGZ2:MGZ3 MHD2:MHD3 MHH2:MHH3 MHL2:MHL3 MHP2:MHP3 MHT2:MHT3 MHX2:MHX3 MIB2:MIB3 MIF2:MIF3 MIJ2:MIJ3 MIN2:MIN3 MIR2:MIR3 MIV2:MIV3 MIZ2:MIZ3 MJD2:MJD3 MJH2:MJH3 MJL2:MJL3 MJP2:MJP3 MJT2:MJT3 MJX2:MJX3 MKB2:MKB3 MKF2:MKF3 MKJ2:MKJ3 MKN2:MKN3 MKR2:MKR3 MKV2:MKV3 MKZ2:MKZ3 MLD2:MLD3 MLH2:MLH3 MLL2:MLL3 MLP2:MLP3 MLT2:MLT3 MLX2:MLX3 MMB2:MMB3 MMF2:MMF3 MMJ2:MMJ3 MMN2:MMN3 MMR2:MMR3 MMV2:MMV3 MMZ2:MMZ3 MND2:MND3 MNH2:MNH3 MNL2:MNL3 MNP2:MNP3 MNT2:MNT3 MNX2:MNX3 MOB2:MOB3 MOF2:MOF3 MOJ2:MOJ3 MON2:MON3 MOR2:MOR3 MOV2:MOV3 MOZ2:MOZ3 MPD2:MPD3 MPH2:MPH3 MPL2:MPL3 MPP2:MPP3 MPT2:MPT3 MPX2:MPX3 MQB2:MQB3 MQF2:MQF3 MQJ2:MQJ3 MQN2:MQN3 MQR2:MQR3 MQV2:MQV3 MQZ2:MQZ3 MRD2:MRD3 MRH2:MRH3 MRL2:MRL3 MRP2:MRP3 MRT2:MRT3 MRX2:MRX3 MSB2:MSB3 MSF2:MSF3 MSJ2:MSJ3 MSN2:MSN3 MSR2:MSR3 MSV2:MSV3 MSZ2:MSZ3 MTD2:MTD3 MTH2:MTH3 MTL2:MTL3 MTP2:MTP3 MTT2:MTT3 MTX2:MTX3 MUB2:MUB3 MUF2:MUF3 MUJ2:MUJ3 MUN2:MUN3 MUR2:MUR3 MUV2:MUV3 MUZ2:MUZ3 MVD2:MVD3 MVH2:MVH3 MVL2:MVL3 MVP2:MVP3 MVT2:MVT3 MVX2:MVX3 MWB2:MWB3 MWF2:MWF3 MWJ2:MWJ3 MWN2:MWN3 MWR2:MWR3 MWV2:MWV3 MWZ2:MWZ3 MXD2:MXD3 MXH2:MXH3 MXL2:MXL3 MXP2:MXP3 MXT2:MXT3 MXX2:MXX3 MYB2:MYB3 MYF2:MYF3 MYJ2:MYJ3 MYN2:MYN3 MYR2:MYR3 MYV2:MYV3 MYZ2:MYZ3 MZD2:MZD3 MZH2:MZH3 MZL2:MZL3 MZP2:MZP3 MZT2:MZT3 MZX2:MZX3 NAB2:NAB3 NAF2:NAF3 NAJ2:NAJ3 NAN2:NAN3 NAR2:NAR3 NAV2:NAV3 NAZ2:NAZ3 NBD2:NBD3 NBH2:NBH3 NBL2:NBL3 NBP2:NBP3 NBT2:NBT3 NBX2:NBX3 NCB2:NCB3 NCF2:NCF3 NCJ2:NCJ3 NCN2:NCN3 NCR2:NCR3 NCV2:NCV3 NCZ2:NCZ3 NDD2:NDD3 NDH2:NDH3 NDL2:NDL3 NDP2:NDP3 NDT2:NDT3 NDX2:NDX3 NEB2:NEB3 NEF2:NEF3 NEJ2:NEJ3 NEN2:NEN3 NER2:NER3 NEV2:NEV3 NEZ2:NEZ3 NFD2:NFD3 NFH2:NFH3 NFL2:NFL3 NFP2:NFP3 NFT2:NFT3 NFX2:NFX3 NGB2:NGB3 NGF2:NGF3 NGJ2:NGJ3 NGN2:NGN3 NGR2:NGR3 NGV2:NGV3 NGZ2:NGZ3 NHD2:NHD3 NHH2:NHH3 NHL2:NHL3 NHP2:NHP3 NHT2:NHT3 NHX2:NHX3 NIB2:NIB3 NIF2:NIF3 NIJ2:NIJ3 NIN2:NIN3 NIR2:NIR3 NIV2:NIV3 NIZ2:NIZ3 NJD2:NJD3 NJH2:NJH3 NJL2:NJL3 NJP2:NJP3 NJT2:NJT3 NJX2:NJX3 NKB2:NKB3 NKF2:NKF3 NKJ2:NKJ3 NKN2:NKN3 NKR2:NKR3 NKV2:NKV3 NKZ2:NKZ3 NLD2:NLD3 NLH2:NLH3 NLL2:NLL3 NLP2:NLP3 NLT2:NLT3 NLX2:NLX3 NMB2:NMB3 NMF2:NMF3 NMJ2:NMJ3 NMN2:NMN3 NMR2:NMR3 NMV2:NMV3 NMZ2:NMZ3 NND2:NND3 NNH2:NNH3 NNL2:NNL3 NNP2:NNP3 NNT2:NNT3 NNX2:NNX3 NOB2:NOB3 NOF2:NOF3 NOJ2:NOJ3 NON2:NON3 NOR2:NOR3 NOV2:NOV3 NOZ2:NOZ3 NPD2:NPD3 NPH2:NPH3 NPL2:NPL3 NPP2:NPP3 NPT2:NPT3 NPX2:NPX3 NQB2:NQB3 NQF2:NQF3 NQJ2:NQJ3 NQN2:NQN3 NQR2:NQR3 NQV2:NQV3 NQZ2:NQZ3 NRD2:NRD3 NRH2:NRH3 NRL2:NRL3 NRP2:NRP3 NRT2:NRT3 NRX2:NRX3 NSB2:NSB3 NSF2:NSF3 NSJ2:NSJ3 NSN2:NSN3 NSR2:NSR3 NSV2:NSV3 NSZ2:NSZ3 NTD2:NTD3 NTH2:NTH3 NTL2:NTL3 NTP2:NTP3 NTT2:NTT3 NTX2:NTX3 NUB2:NUB3 NUF2:NUF3 NUJ2:NUJ3 NUN2:NUN3 NUR2:NUR3 NUV2:NUV3 NUZ2:NUZ3 NVD2:NVD3 NVH2:NVH3 NVL2:NVL3 NVP2:NVP3 NVT2:NVT3 NVX2:NVX3 NWB2:NWB3 NWF2:NWF3 NWJ2:NWJ3 NWN2:NWN3 NWR2:NWR3 NWV2:NWV3 NWZ2:NWZ3 NXD2:NXD3 NXH2:NXH3 NXL2:NXL3 NXP2:NXP3 NXT2:NXT3 NXX2:NXX3 NYB2:NYB3 NYF2:NYF3 NYJ2:NYJ3 NYN2:NYN3 NYR2:NYR3 NYV2:NYV3 NYZ2:NYZ3 NZD2:NZD3 NZH2:NZH3 NZL2:NZL3 NZP2:NZP3 NZT2:NZT3 NZX2:NZX3 OAB2:OAB3 OAF2:OAF3 OAJ2:OAJ3 OAN2:OAN3 OAR2:OAR3 OAV2:OAV3 OAZ2:OAZ3 OBD2:OBD3 OBH2:OBH3 OBL2:OBL3 OBP2:OBP3 OBT2:OBT3 OBX2:OBX3 OCB2:OCB3 OCF2:OCF3 OCJ2:OCJ3 OCN2:OCN3 OCR2:OCR3 OCV2:OCV3 OCZ2:OCZ3 ODD2:ODD3 ODH2:ODH3 ODL2:ODL3 ODP2:ODP3 ODT2:ODT3 ODX2:ODX3 OEB2:OEB3 OEF2:OEF3 OEJ2:OEJ3 OEN2:OEN3 OER2:OER3 OEV2:OEV3 OEZ2:OEZ3 OFD2:OFD3 OFH2:OFH3 OFL2:OFL3 OFP2:OFP3 OFT2:OFT3 OFX2:OFX3 OGB2:OGB3 OGF2:OGF3 OGJ2:OGJ3 OGN2:OGN3 OGR2:OGR3 OGV2:OGV3 OGZ2:OGZ3 OHD2:OHD3 OHH2:OHH3 OHL2:OHL3 OHP2:OHP3 OHT2:OHT3 OHX2:OHX3 OIB2:OIB3 OIF2:OIF3 OIJ2:OIJ3 OIN2:OIN3 OIR2:OIR3 OIV2:OIV3 OIZ2:OIZ3 OJD2:OJD3 OJH2:OJH3 OJL2:OJL3 OJP2:OJP3 OJT2:OJT3 OJX2:OJX3 OKB2:OKB3 OKF2:OKF3 OKJ2:OKJ3 OKN2:OKN3 OKR2:OKR3 OKV2:OKV3 OKZ2:OKZ3 OLD2:OLD3 OLH2:OLH3 OLL2:OLL3 OLP2:OLP3 OLT2:OLT3 OLX2:OLX3 OMB2:OMB3 OMF2:OMF3 OMJ2:OMJ3 OMN2:OMN3 OMR2:OMR3 OMV2:OMV3 OMZ2:OMZ3 OND2:OND3 ONH2:ONH3 ONL2:ONL3 ONP2:ONP3 ONT2:ONT3 ONX2:ONX3 OOB2:OOB3 OOF2:OOF3 OOJ2:OOJ3 OON2:OON3 OOR2:OOR3 OOV2:OOV3 OOZ2:OOZ3 OPD2:OPD3 OPH2:OPH3 OPL2:OPL3 OPP2:OPP3 OPT2:OPT3 OPX2:OPX3 OQB2:OQB3 OQF2:OQF3 OQJ2:OQJ3 OQN2:OQN3 OQR2:OQR3 OQV2:OQV3 OQZ2:OQZ3 ORD2:ORD3 ORH2:ORH3 ORL2:ORL3 ORP2:ORP3 ORT2:ORT3 ORX2:ORX3 OSB2:OSB3 OSF2:OSF3 OSJ2:OSJ3 OSN2:OSN3 OSR2:OSR3 OSV2:OSV3 OSZ2:OSZ3 OTD2:OTD3 OTH2:OTH3 OTL2:OTL3 OTP2:OTP3 OTT2:OTT3 OTX2:OTX3 OUB2:OUB3 OUF2:OUF3 OUJ2:OUJ3 OUN2:OUN3 OUR2:OUR3 OUV2:OUV3 OUZ2:OUZ3 OVD2:OVD3 OVH2:OVH3 OVL2:OVL3 OVP2:OVP3 OVT2:OVT3 OVX2:OVX3 OWB2:OWB3 OWF2:OWF3 OWJ2:OWJ3 OWN2:OWN3 OWR2:OWR3 OWV2:OWV3 OWZ2:OWZ3 OXD2:OXD3 OXH2:OXH3 OXL2:OXL3 OXP2:OXP3 OXT2:OXT3 OXX2:OXX3 OYB2:OYB3 OYF2:OYF3 OYJ2:OYJ3 OYN2:OYN3 OYR2:OYR3 OYV2:OYV3 OYZ2:OYZ3 OZD2:OZD3 OZH2:OZH3 OZL2:OZL3 OZP2:OZP3 OZT2:OZT3 OZX2:OZX3 PAB2:PAB3 PAF2:PAF3 PAJ2:PAJ3 PAN2:PAN3 PAR2:PAR3 PAV2:PAV3 PAZ2:PAZ3 PBD2:PBD3 PBH2:PBH3 PBL2:PBL3 PBP2:PBP3 PBT2:PBT3 PBX2:PBX3 PCB2:PCB3 PCF2:PCF3 PCJ2:PCJ3 PCN2:PCN3 PCR2:PCR3 PCV2:PCV3 PCZ2:PCZ3 PDD2:PDD3 PDH2:PDH3 PDL2:PDL3 PDP2:PDP3 PDT2:PDT3 PDX2:PDX3 PEB2:PEB3 PEF2:PEF3 PEJ2:PEJ3 PEN2:PEN3 PER2:PER3 PEV2:PEV3 PEZ2:PEZ3 PFD2:PFD3 PFH2:PFH3 PFL2:PFL3 PFP2:PFP3 PFT2:PFT3 PFX2:PFX3 PGB2:PGB3 PGF2:PGF3 PGJ2:PGJ3 PGN2:PGN3 PGR2:PGR3 PGV2:PGV3 PGZ2:PGZ3 PHD2:PHD3 PHH2:PHH3 PHL2:PHL3 PHP2:PHP3 PHT2:PHT3 PHX2:PHX3 PIB2:PIB3 PIF2:PIF3 PIJ2:PIJ3 PIN2:PIN3 PIR2:PIR3 PIV2:PIV3 PIZ2:PIZ3 PJD2:PJD3 PJH2:PJH3 PJL2:PJL3 PJP2:PJP3 PJT2:PJT3 PJX2:PJX3 PKB2:PKB3 PKF2:PKF3 PKJ2:PKJ3 PKN2:PKN3 PKR2:PKR3 PKV2:PKV3 PKZ2:PKZ3 PLD2:PLD3 PLH2:PLH3 PLL2:PLL3 PLP2:PLP3 PLT2:PLT3 PLX2:PLX3 PMB2:PMB3 PMF2:PMF3 PMJ2:PMJ3 PMN2:PMN3 PMR2:PMR3 PMV2:PMV3 PMZ2:PMZ3 PND2:PND3 PNH2:PNH3 PNL2:PNL3 PNP2:PNP3 PNT2:PNT3 PNX2:PNX3 POB2:POB3 POF2:POF3 POJ2:POJ3 PON2:PON3 POR2:POR3 POV2:POV3 POZ2:POZ3 PPD2:PPD3 PPH2:PPH3 PPL2:PPL3 PPP2:PPP3 PPT2:PPT3 PPX2:PPX3 PQB2:PQB3 PQF2:PQF3 PQJ2:PQJ3 PQN2:PQN3 PQR2:PQR3 PQV2:PQV3 PQZ2:PQZ3 PRD2:PRD3 PRH2:PRH3 PRL2:PRL3 PRP2:PRP3 PRT2:PRT3 PRX2:PRX3 PSB2:PSB3 PSF2:PSF3 PSJ2:PSJ3 PSN2:PSN3 PSR2:PSR3 PSV2:PSV3 PSZ2:PSZ3 PTD2:PTD3 PTH2:PTH3 PTL2:PTL3 PTP2:PTP3 PTT2:PTT3 PTX2:PTX3 PUB2:PUB3 PUF2:PUF3 PUJ2:PUJ3 PUN2:PUN3 PUR2:PUR3 PUV2:PUV3 PUZ2:PUZ3 PVD2:PVD3 PVH2:PVH3 PVL2:PVL3 PVP2:PVP3 PVT2:PVT3 PVX2:PVX3 PWB2:PWB3 PWF2:PWF3 PWJ2:PWJ3 PWN2:PWN3 PWR2:PWR3 PWV2:PWV3 PWZ2:PWZ3 PXD2:PXD3 PXH2:PXH3 PXL2:PXL3 PXP2:PXP3 PXT2:PXT3 PXX2:PXX3 PYB2:PYB3 PYF2:PYF3 PYJ2:PYJ3 PYN2:PYN3 PYR2:PYR3 PYV2:PYV3 PYZ2:PYZ3 PZD2:PZD3 PZH2:PZH3 PZL2:PZL3 PZP2:PZP3 PZT2:PZT3 PZX2:PZX3 QAB2:QAB3 QAF2:QAF3 QAJ2:QAJ3 QAN2:QAN3 QAR2:QAR3 QAV2:QAV3 QAZ2:QAZ3 QBD2:QBD3 QBH2:QBH3 QBL2:QBL3 QBP2:QBP3 QBT2:QBT3 QBX2:QBX3 QCB2:QCB3 QCF2:QCF3 QCJ2:QCJ3 QCN2:QCN3 QCR2:QCR3 QCV2:QCV3 QCZ2:QCZ3 QDD2:QDD3 QDH2:QDH3 QDL2:QDL3 QDP2:QDP3 QDT2:QDT3 QDX2:QDX3 QEB2:QEB3 QEF2:QEF3 QEJ2:QEJ3 QEN2:QEN3 QER2:QER3 QEV2:QEV3 QEZ2:QEZ3 QFD2:QFD3 QFH2:QFH3 QFL2:QFL3 QFP2:QFP3 QFT2:QFT3 QFX2:QFX3 QGB2:QGB3 QGF2:QGF3 QGJ2:QGJ3 QGN2:QGN3 QGR2:QGR3 QGV2:QGV3 QGZ2:QGZ3 QHD2:QHD3 QHH2:QHH3 QHL2:QHL3 QHP2:QHP3 QHT2:QHT3 QHX2:QHX3 QIB2:QIB3 QIF2:QIF3 QIJ2:QIJ3 QIN2:QIN3 QIR2:QIR3 QIV2:QIV3 QIZ2:QIZ3 QJD2:QJD3 QJH2:QJH3 QJL2:QJL3 QJP2:QJP3 QJT2:QJT3 QJX2:QJX3 QKB2:QKB3 QKF2:QKF3 QKJ2:QKJ3 QKN2:QKN3 QKR2:QKR3 QKV2:QKV3 QKZ2:QKZ3 QLD2:QLD3 QLH2:QLH3 QLL2:QLL3 QLP2:QLP3 QLT2:QLT3 QLX2:QLX3 QMB2:QMB3 QMF2:QMF3 QMJ2:QMJ3 QMN2:QMN3 QMR2:QMR3 QMV2:QMV3 QMZ2:QMZ3 QND2:QND3 QNH2:QNH3 QNL2:QNL3 QNP2:QNP3 QNT2:QNT3 QNX2:QNX3 QOB2:QOB3 QOF2:QOF3 QOJ2:QOJ3 QON2:QON3 QOR2:QOR3 QOV2:QOV3 QOZ2:QOZ3 QPD2:QPD3 QPH2:QPH3 QPL2:QPL3 QPP2:QPP3 QPT2:QPT3 QPX2:QPX3 QQB2:QQB3 QQF2:QQF3 QQJ2:QQJ3 QQN2:QQN3 QQR2:QQR3 QQV2:QQV3 QQZ2:QQZ3 QRD2:QRD3 QRH2:QRH3 QRL2:QRL3 QRP2:QRP3 QRT2:QRT3 QRX2:QRX3 QSB2:QSB3 QSF2:QSF3 QSJ2:QSJ3 QSN2:QSN3 QSR2:QSR3 QSV2:QSV3 QSZ2:QSZ3 QTD2:QTD3 QTH2:QTH3 QTL2:QTL3 QTP2:QTP3 QTT2:QTT3 QTX2:QTX3 QUB2:QUB3 QUF2:QUF3 QUJ2:QUJ3 QUN2:QUN3 QUR2:QUR3 QUV2:QUV3 QUZ2:QUZ3 QVD2:QVD3 QVH2:QVH3 QVL2:QVL3 QVP2:QVP3 QVT2:QVT3 QVX2:QVX3 QWB2:QWB3 QWF2:QWF3 QWJ2:QWJ3 QWN2:QWN3 QWR2:QWR3 QWV2:QWV3 QWZ2:QWZ3 QXD2:QXD3 QXH2:QXH3 QXL2:QXL3 QXP2:QXP3 QXT2:QXT3 QXX2:QXX3 QYB2:QYB3 QYF2:QYF3 QYJ2:QYJ3 QYN2:QYN3 QYR2:QYR3 QYV2:QYV3 QYZ2:QYZ3 QZD2:QZD3 QZH2:QZH3 QZL2:QZL3 QZP2:QZP3 QZT2:QZT3 QZX2:QZX3 RAB2:RAB3 RAF2:RAF3 RAJ2:RAJ3 RAN2:RAN3 RAR2:RAR3 RAV2:RAV3 RAZ2:RAZ3 RBD2:RBD3 RBH2:RBH3 RBL2:RBL3 RBP2:RBP3 RBT2:RBT3 RBX2:RBX3 RCB2:RCB3 RCF2:RCF3 RCJ2:RCJ3 RCN2:RCN3 RCR2:RCR3 RCV2:RCV3 RCZ2:RCZ3 RDD2:RDD3 RDH2:RDH3 RDL2:RDL3 RDP2:RDP3 RDT2:RDT3 RDX2:RDX3 REB2:REB3 REF2:REF3 REJ2:REJ3 REN2:REN3 RER2:RER3 REV2:REV3 REZ2:REZ3 RFD2:RFD3 RFH2:RFH3 RFL2:RFL3 RFP2:RFP3 RFT2:RFT3 RFX2:RFX3 RGB2:RGB3 RGF2:RGF3 RGJ2:RGJ3 RGN2:RGN3 RGR2:RGR3 RGV2:RGV3 RGZ2:RGZ3 RHD2:RHD3 RHH2:RHH3 RHL2:RHL3 RHP2:RHP3 RHT2:RHT3 RHX2:RHX3 RIB2:RIB3 RIF2:RIF3 RIJ2:RIJ3 RIN2:RIN3 RIR2:RIR3 RIV2:RIV3 RIZ2:RIZ3 RJD2:RJD3 RJH2:RJH3 RJL2:RJL3 RJP2:RJP3 RJT2:RJT3 RJX2:RJX3 RKB2:RKB3 RKF2:RKF3 RKJ2:RKJ3 RKN2:RKN3 RKR2:RKR3 RKV2:RKV3 RKZ2:RKZ3 RLD2:RLD3 RLH2:RLH3 RLL2:RLL3 RLP2:RLP3 RLT2:RLT3 RLX2:RLX3 RMB2:RMB3 RMF2:RMF3 RMJ2:RMJ3 RMN2:RMN3 RMR2:RMR3 RMV2:RMV3 RMZ2:RMZ3 RND2:RND3 RNH2:RNH3 RNL2:RNL3 RNP2:RNP3 RNT2:RNT3 RNX2:RNX3 ROB2:ROB3 ROF2:ROF3 ROJ2:ROJ3 RON2:RON3 ROR2:ROR3 ROV2:ROV3 ROZ2:ROZ3 RPD2:RPD3 RPH2:RPH3 RPL2:RPL3 RPP2:RPP3 RPT2:RPT3 RPX2:RPX3 RQB2:RQB3 RQF2:RQF3 RQJ2:RQJ3 RQN2:RQN3 RQR2:RQR3 RQV2:RQV3 RQZ2:RQZ3 RRD2:RRD3 RRH2:RRH3 RRL2:RRL3 RRP2:RRP3 RRT2:RRT3 RRX2:RRX3 RSB2:RSB3 RSF2:RSF3 RSJ2:RSJ3 RSN2:RSN3 RSR2:RSR3 RSV2:RSV3 RSZ2:RSZ3 RTD2:RTD3 RTH2:RTH3 RTL2:RTL3 RTP2:RTP3 RTT2:RTT3 RTX2:RTX3 RUB2:RUB3 RUF2:RUF3 RUJ2:RUJ3 RUN2:RUN3 RUR2:RUR3 RUV2:RUV3 RUZ2:RUZ3 RVD2:RVD3 RVH2:RVH3 RVL2:RVL3 RVP2:RVP3 RVT2:RVT3 RVX2:RVX3 RWB2:RWB3 RWF2:RWF3 RWJ2:RWJ3 RWN2:RWN3 RWR2:RWR3 RWV2:RWV3 RWZ2:RWZ3 RXD2:RXD3 RXH2:RXH3 RXL2:RXL3 RXP2:RXP3 RXT2:RXT3 RXX2:RXX3 RYB2:RYB3 RYF2:RYF3 RYJ2:RYJ3 RYN2:RYN3 RYR2:RYR3 RYV2:RYV3 RYZ2:RYZ3 RZD2:RZD3 RZH2:RZH3 RZL2:RZL3 RZP2:RZP3 RZT2:RZT3 RZX2:RZX3 SAB2:SAB3 SAF2:SAF3 SAJ2:SAJ3 SAN2:SAN3 SAR2:SAR3 SAV2:SAV3 SAZ2:SAZ3 SBD2:SBD3 SBH2:SBH3 SBL2:SBL3 SBP2:SBP3 SBT2:SBT3 SBX2:SBX3 SCB2:SCB3 SCF2:SCF3 SCJ2:SCJ3 SCN2:SCN3 SCR2:SCR3 SCV2:SCV3 SCZ2:SCZ3 SDD2:SDD3 SDH2:SDH3 SDL2:SDL3 SDP2:SDP3 SDT2:SDT3 SDX2:SDX3 SEB2:SEB3 SEF2:SEF3 SEJ2:SEJ3 SEN2:SEN3 SER2:SER3 SEV2:SEV3 SEZ2:SEZ3 SFD2:SFD3 SFH2:SFH3 SFL2:SFL3 SFP2:SFP3 SFT2:SFT3 SFX2:SFX3 SGB2:SGB3 SGF2:SGF3 SGJ2:SGJ3 SGN2:SGN3 SGR2:SGR3 SGV2:SGV3 SGZ2:SGZ3 SHD2:SHD3 SHH2:SHH3 SHL2:SHL3 SHP2:SHP3 SHT2:SHT3 SHX2:SHX3 SIB2:SIB3 SIF2:SIF3 SIJ2:SIJ3 SIN2:SIN3 SIR2:SIR3 SIV2:SIV3 SIZ2:SIZ3 SJD2:SJD3 SJH2:SJH3 SJL2:SJL3 SJP2:SJP3 SJT2:SJT3 SJX2:SJX3 SKB2:SKB3 SKF2:SKF3 SKJ2:SKJ3 SKN2:SKN3 SKR2:SKR3 SKV2:SKV3 SKZ2:SKZ3 SLD2:SLD3 SLH2:SLH3 SLL2:SLL3 SLP2:SLP3 SLT2:SLT3 SLX2:SLX3 SMB2:SMB3 SMF2:SMF3 SMJ2:SMJ3 SMN2:SMN3 SMR2:SMR3 SMV2:SMV3 SMZ2:SMZ3 SND2:SND3 SNH2:SNH3 SNL2:SNL3 SNP2:SNP3 SNT2:SNT3 SNX2:SNX3 SOB2:SOB3 SOF2:SOF3 SOJ2:SOJ3 SON2:SON3 SOR2:SOR3 SOV2:SOV3 SOZ2:SOZ3 SPD2:SPD3 SPH2:SPH3 SPL2:SPL3 SPP2:SPP3 SPT2:SPT3 SPX2:SPX3 SQB2:SQB3 SQF2:SQF3 SQJ2:SQJ3 SQN2:SQN3 SQR2:SQR3 SQV2:SQV3 SQZ2:SQZ3 SRD2:SRD3 SRH2:SRH3 SRL2:SRL3 SRP2:SRP3 SRT2:SRT3 SRX2:SRX3 SSB2:SSB3 SSF2:SSF3 SSJ2:SSJ3 SSN2:SSN3 SSR2:SSR3 SSV2:SSV3 SSZ2:SSZ3 STD2:STD3 STH2:STH3 STL2:STL3 STP2:STP3 STT2:STT3 STX2:STX3 SUB2:SUB3 SUF2:SUF3 SUJ2:SUJ3 SUN2:SUN3 SUR2:SUR3 SUV2:SUV3 SUZ2:SUZ3 SVD2:SVD3 SVH2:SVH3 SVL2:SVL3 SVP2:SVP3 SVT2:SVT3 SVX2:SVX3 SWB2:SWB3 SWF2:SWF3 SWJ2:SWJ3 SWN2:SWN3 SWR2:SWR3 SWV2:SWV3 SWZ2:SWZ3 SXD2:SXD3 SXH2:SXH3 SXL2:SXL3 SXP2:SXP3 SXT2:SXT3 SXX2:SXX3 SYB2:SYB3 SYF2:SYF3 SYJ2:SYJ3 SYN2:SYN3 SYR2:SYR3 SYV2:SYV3 SYZ2:SYZ3 SZD2:SZD3 SZH2:SZH3 SZL2:SZL3 SZP2:SZP3 SZT2:SZT3 SZX2:SZX3 TAB2:TAB3 TAF2:TAF3 TAJ2:TAJ3 TAN2:TAN3 TAR2:TAR3 TAV2:TAV3 TAZ2:TAZ3 TBD2:TBD3 TBH2:TBH3 TBL2:TBL3 TBP2:TBP3 TBT2:TBT3 TBX2:TBX3 TCB2:TCB3 TCF2:TCF3 TCJ2:TCJ3 TCN2:TCN3 TCR2:TCR3 TCV2:TCV3 TCZ2:TCZ3 TDD2:TDD3 TDH2:TDH3 TDL2:TDL3 TDP2:TDP3 TDT2:TDT3 TDX2:TDX3 TEB2:TEB3 TEF2:TEF3 TEJ2:TEJ3 TEN2:TEN3 TER2:TER3 TEV2:TEV3 TEZ2:TEZ3 TFD2:TFD3 TFH2:TFH3 TFL2:TFL3 TFP2:TFP3 TFT2:TFT3 TFX2:TFX3 TGB2:TGB3 TGF2:TGF3 TGJ2:TGJ3 TGN2:TGN3 TGR2:TGR3 TGV2:TGV3 TGZ2:TGZ3 THD2:THD3 THH2:THH3 THL2:THL3 THP2:THP3 THT2:THT3 THX2:THX3 TIB2:TIB3 TIF2:TIF3 TIJ2:TIJ3 TIN2:TIN3 TIR2:TIR3 TIV2:TIV3 TIZ2:TIZ3 TJD2:TJD3 TJH2:TJH3 TJL2:TJL3 TJP2:TJP3 TJT2:TJT3 TJX2:TJX3 TKB2:TKB3 TKF2:TKF3 TKJ2:TKJ3 TKN2:TKN3 TKR2:TKR3 TKV2:TKV3 TKZ2:TKZ3 TLD2:TLD3 TLH2:TLH3 TLL2:TLL3 TLP2:TLP3 TLT2:TLT3 TLX2:TLX3 TMB2:TMB3 TMF2:TMF3 TMJ2:TMJ3 TMN2:TMN3 TMR2:TMR3 TMV2:TMV3 TMZ2:TMZ3 TND2:TND3 TNH2:TNH3 TNL2:TNL3 TNP2:TNP3 TNT2:TNT3 TNX2:TNX3 TOB2:TOB3 TOF2:TOF3 TOJ2:TOJ3 TON2:TON3 TOR2:TOR3 TOV2:TOV3 TOZ2:TOZ3 TPD2:TPD3 TPH2:TPH3 TPL2:TPL3 TPP2:TPP3 TPT2:TPT3 TPX2:TPX3 TQB2:TQB3 TQF2:TQF3 TQJ2:TQJ3 TQN2:TQN3 TQR2:TQR3 TQV2:TQV3 TQZ2:TQZ3 TRD2:TRD3 TRH2:TRH3 TRL2:TRL3 TRP2:TRP3 TRT2:TRT3 TRX2:TRX3 TSB2:TSB3 TSF2:TSF3 TSJ2:TSJ3 TSN2:TSN3 TSR2:TSR3 TSV2:TSV3 TSZ2:TSZ3 TTD2:TTD3 TTH2:TTH3 TTL2:TTL3 TTP2:TTP3 TTT2:TTT3 TTX2:TTX3 TUB2:TUB3 TUF2:TUF3 TUJ2:TUJ3 TUN2:TUN3 TUR2:TUR3 TUV2:TUV3 TUZ2:TUZ3 TVD2:TVD3 TVH2:TVH3 TVL2:TVL3 TVP2:TVP3 TVT2:TVT3 TVX2:TVX3 TWB2:TWB3 TWF2:TWF3 TWJ2:TWJ3 TWN2:TWN3 TWR2:TWR3 TWV2:TWV3 TWZ2:TWZ3 TXD2:TXD3 TXH2:TXH3 TXL2:TXL3 TXP2:TXP3 TXT2:TXT3 TXX2:TXX3 TYB2:TYB3 TYF2:TYF3 TYJ2:TYJ3 TYN2:TYN3 TYR2:TYR3 TYV2:TYV3 TYZ2:TYZ3 TZD2:TZD3 TZH2:TZH3 TZL2:TZL3 TZP2:TZP3 TZT2:TZT3 TZX2:TZX3 UAB2:UAB3 UAF2:UAF3 UAJ2:UAJ3 UAN2:UAN3 UAR2:UAR3 UAV2:UAV3 UAZ2:UAZ3 UBD2:UBD3 UBH2:UBH3 UBL2:UBL3 UBP2:UBP3 UBT2:UBT3 UBX2:UBX3 UCB2:UCB3 UCF2:UCF3 UCJ2:UCJ3 UCN2:UCN3 UCR2:UCR3 UCV2:UCV3 UCZ2:UCZ3 UDD2:UDD3 UDH2:UDH3 UDL2:UDL3 UDP2:UDP3 UDT2:UDT3 UDX2:UDX3 UEB2:UEB3 UEF2:UEF3 UEJ2:UEJ3 UEN2:UEN3 UER2:UER3 UEV2:UEV3 UEZ2:UEZ3 UFD2:UFD3 UFH2:UFH3 UFL2:UFL3 UFP2:UFP3 UFT2:UFT3 UFX2:UFX3 UGB2:UGB3 UGF2:UGF3 UGJ2:UGJ3 UGN2:UGN3 UGR2:UGR3 UGV2:UGV3 UGZ2:UGZ3 UHD2:UHD3 UHH2:UHH3 UHL2:UHL3 UHP2:UHP3 UHT2:UHT3 UHX2:UHX3 UIB2:UIB3 UIF2:UIF3 UIJ2:UIJ3 UIN2:UIN3 UIR2:UIR3 UIV2:UIV3 UIZ2:UIZ3 UJD2:UJD3 UJH2:UJH3 UJL2:UJL3 UJP2:UJP3 UJT2:UJT3 UJX2:UJX3 UKB2:UKB3 UKF2:UKF3 UKJ2:UKJ3 UKN2:UKN3 UKR2:UKR3 UKV2:UKV3 UKZ2:UKZ3 ULD2:ULD3 ULH2:ULH3 ULL2:ULL3 ULP2:ULP3 ULT2:ULT3 ULX2:ULX3 UMB2:UMB3 UMF2:UMF3 UMJ2:UMJ3 UMN2:UMN3 UMR2:UMR3 UMV2:UMV3 UMZ2:UMZ3 UND2:UND3 UNH2:UNH3 UNL2:UNL3 UNP2:UNP3 UNT2:UNT3 UNX2:UNX3 UOB2:UOB3 UOF2:UOF3 UOJ2:UOJ3 UON2:UON3 UOR2:UOR3 UOV2:UOV3 UOZ2:UOZ3 UPD2:UPD3 UPH2:UPH3 UPL2:UPL3 UPP2:UPP3 UPT2:UPT3 UPX2:UPX3 UQB2:UQB3 UQF2:UQF3 UQJ2:UQJ3 UQN2:UQN3 UQR2:UQR3 UQV2:UQV3 UQZ2:UQZ3 URD2:URD3 URH2:URH3 URL2:URL3 URP2:URP3 URT2:URT3 URX2:URX3 USB2:USB3 USF2:USF3 USJ2:USJ3 USN2:USN3 USR2:USR3 USV2:USV3 USZ2:USZ3 UTD2:UTD3 UTH2:UTH3 UTL2:UTL3 UTP2:UTP3 UTT2:UTT3 UTX2:UTX3 UUB2:UUB3 UUF2:UUF3 UUJ2:UUJ3 UUN2:UUN3 UUR2:UUR3 UUV2:UUV3 UUZ2:UUZ3 UVD2:UVD3 UVH2:UVH3 UVL2:UVL3 UVP2:UVP3 UVT2:UVT3 UVX2:UVX3 UWB2:UWB3 UWF2:UWF3 UWJ2:UWJ3 UWN2:UWN3 UWR2:UWR3 UWV2:UWV3 UWZ2:UWZ3 UXD2:UXD3 UXH2:UXH3 UXL2:UXL3 UXP2:UXP3 UXT2:UXT3 UXX2:UXX3 UYB2:UYB3 UYF2:UYF3 UYJ2:UYJ3 UYN2:UYN3 UYR2:UYR3 UYV2:UYV3 UYZ2:UYZ3 UZD2:UZD3 UZH2:UZH3 UZL2:UZL3 UZP2:UZP3 UZT2:UZT3 UZX2:UZX3 VAB2:VAB3 VAF2:VAF3 VAJ2:VAJ3 VAN2:VAN3 VAR2:VAR3 VAV2:VAV3 VAZ2:VAZ3 VBD2:VBD3 VBH2:VBH3 VBL2:VBL3 VBP2:VBP3 VBT2:VBT3 VBX2:VBX3 VCB2:VCB3 VCF2:VCF3 VCJ2:VCJ3 VCN2:VCN3 VCR2:VCR3 VCV2:VCV3 VCZ2:VCZ3 VDD2:VDD3 VDH2:VDH3 VDL2:VDL3 VDP2:VDP3 VDT2:VDT3 VDX2:VDX3 VEB2:VEB3 VEF2:VEF3 VEJ2:VEJ3 VEN2:VEN3 VER2:VER3 VEV2:VEV3 VEZ2:VEZ3 VFD2:VFD3 VFH2:VFH3 VFL2:VFL3 VFP2:VFP3 VFT2:VFT3 VFX2:VFX3 VGB2:VGB3 VGF2:VGF3 VGJ2:VGJ3 VGN2:VGN3 VGR2:VGR3 VGV2:VGV3 VGZ2:VGZ3 VHD2:VHD3 VHH2:VHH3 VHL2:VHL3 VHP2:VHP3 VHT2:VHT3 VHX2:VHX3 VIB2:VIB3 VIF2:VIF3 VIJ2:VIJ3 VIN2:VIN3 VIR2:VIR3 VIV2:VIV3 VIZ2:VIZ3 VJD2:VJD3 VJH2:VJH3 VJL2:VJL3 VJP2:VJP3 VJT2:VJT3 VJX2:VJX3 VKB2:VKB3 VKF2:VKF3 VKJ2:VKJ3 VKN2:VKN3 VKR2:VKR3 VKV2:VKV3 VKZ2:VKZ3 VLD2:VLD3 VLH2:VLH3 VLL2:VLL3 VLP2:VLP3 VLT2:VLT3 VLX2:VLX3 VMB2:VMB3 VMF2:VMF3 VMJ2:VMJ3 VMN2:VMN3 VMR2:VMR3 VMV2:VMV3 VMZ2:VMZ3 VND2:VND3 VNH2:VNH3 VNL2:VNL3 VNP2:VNP3 VNT2:VNT3 VNX2:VNX3 VOB2:VOB3 VOF2:VOF3 VOJ2:VOJ3 VON2:VON3 VOR2:VOR3 VOV2:VOV3 VOZ2:VOZ3 VPD2:VPD3 VPH2:VPH3 VPL2:VPL3 VPP2:VPP3 VPT2:VPT3 VPX2:VPX3 VQB2:VQB3 VQF2:VQF3 VQJ2:VQJ3 VQN2:VQN3 VQR2:VQR3 VQV2:VQV3 VQZ2:VQZ3 VRD2:VRD3 VRH2:VRH3 VRL2:VRL3 VRP2:VRP3 VRT2:VRT3 VRX2:VRX3 VSB2:VSB3 VSF2:VSF3 VSJ2:VSJ3 VSN2:VSN3 VSR2:VSR3 VSV2:VSV3 VSZ2:VSZ3 VTD2:VTD3 VTH2:VTH3 VTL2:VTL3 VTP2:VTP3 VTT2:VTT3 VTX2:VTX3 VUB2:VUB3 VUF2:VUF3 VUJ2:VUJ3 VUN2:VUN3 VUR2:VUR3 VUV2:VUV3 VUZ2:VUZ3 VVD2:VVD3 VVH2:VVH3 VVL2:VVL3 VVP2:VVP3 VVT2:VVT3 VVX2:VVX3 VWB2:VWB3 VWF2:VWF3 VWJ2:VWJ3 VWN2:VWN3 VWR2:VWR3 VWV2:VWV3 VWZ2:VWZ3 VXD2:VXD3 VXH2:VXH3 VXL2:VXL3 VXP2:VXP3 VXT2:VXT3 VXX2:VXX3 VYB2:VYB3 VYF2:VYF3 VYJ2:VYJ3 VYN2:VYN3 VYR2:VYR3 VYV2:VYV3 VYZ2:VYZ3 VZD2:VZD3 VZH2:VZH3 VZL2:VZL3 VZP2:VZP3 VZT2:VZT3 VZX2:VZX3 WAB2:WAB3 WAF2:WAF3 WAJ2:WAJ3 WAN2:WAN3 WAR2:WAR3 WAV2:WAV3 WAZ2:WAZ3 WBD2:WBD3 WBH2:WBH3 WBL2:WBL3 WBP2:WBP3 WBT2:WBT3 WBX2:WBX3 WCB2:WCB3 WCF2:WCF3 WCJ2:WCJ3 WCN2:WCN3 WCR2:WCR3 WCV2:WCV3 WCZ2:WCZ3 WDD2:WDD3 WDH2:WDH3 WDL2:WDL3 WDP2:WDP3 WDT2:WDT3 WDX2:WDX3 WEB2:WEB3 WEF2:WEF3 WEJ2:WEJ3 WEN2:WEN3 WER2:WER3 WEV2:WEV3 WEZ2:WEZ3 WFD2:WFD3 WFH2:WFH3 WFL2:WFL3 WFP2:WFP3 WFT2:WFT3 WFX2:WFX3 WGB2:WGB3 WGF2:WGF3 WGJ2:WGJ3 WGN2:WGN3 WGR2:WGR3 WGV2:WGV3 WGZ2:WGZ3 WHD2:WHD3 WHH2:WHH3 WHL2:WHL3 WHP2:WHP3 WHT2:WHT3 WHX2:WHX3 WIB2:WIB3 WIF2:WIF3 WIJ2:WIJ3 WIN2:WIN3 WIR2:WIR3 WIV2:WIV3 WIZ2:WIZ3 WJD2:WJD3 WJH2:WJH3 WJL2:WJL3 WJP2:WJP3 WJT2:WJT3 WJX2:WJX3 WKB2:WKB3 WKF2:WKF3 WKJ2:WKJ3 WKN2:WKN3 WKR2:WKR3 WKV2:WKV3 WKZ2:WKZ3 WLD2:WLD3 WLH2:WLH3 WLL2:WLL3 WLP2:WLP3 WLT2:WLT3 WLX2:WLX3 WMB2:WMB3 WMF2:WMF3 WMJ2:WMJ3 WMN2:WMN3 WMR2:WMR3 WMV2:WMV3 WMZ2:WMZ3 WND2:WND3 WNH2:WNH3 WNL2:WNL3 WNP2:WNP3 WNT2:WNT3 WNX2:WNX3 WOB2:WOB3 WOF2:WOF3 WOJ2:WOJ3 WON2:WON3 WOR2:WOR3 WOV2:WOV3 WOZ2:WOZ3 WPD2:WPD3 WPH2:WPH3 WPL2:WPL3 WPP2:WPP3 WPT2:WPT3 WPX2:WPX3 WQB2:WQB3 WQF2:WQF3 WQJ2:WQJ3 WQN2:WQN3 WQR2:WQR3 WQV2:WQV3 WQZ2:WQZ3 WRD2:WRD3 WRH2:WRH3 WRL2:WRL3 WRP2:WRP3 WRT2:WRT3 WRX2:WRX3 WSB2:WSB3 WSF2:WSF3 WSJ2:WSJ3 WSN2:WSN3 WSR2:WSR3 WSV2:WSV3 WSZ2:WSZ3 WTD2:WTD3 WTH2:WTH3 WTL2:WTL3 WTP2:WTP3 WTT2:WTT3 WTX2:WTX3 WUB2:WUB3 WUF2:WUF3 WUJ2:WUJ3 WUN2:WUN3 WUR2:WUR3 WUV2:WUV3 WUZ2:WUZ3 WVD2:WVD3 WVH2:WVH3 WVL2:WVL3 WVP2:WVP3 WVT2:WVT3 WVX2:WVX3 WWB2:WWB3 WWF2:WWF3 WWJ2:WWJ3 WWN2:WWN3 WWR2:WWR3 WWV2:WWV3 WWZ2:WWZ3 WXD2:WXD3 WXH2:WXH3 WXL2:WXL3 WXP2:WXP3 WXT2:WXT3 WXX2:WXX3 WYB2:WYB3 WYF2:WYF3 WYJ2:WYJ3 WYN2:WYN3 WYR2:WYR3 WYV2:WYV3 WYZ2:WYZ3 WZD2:WZD3 WZH2:WZH3 WZL2:WZL3 WZP2:WZP3 WZT2:WZT3 WZX2:WZX3 XAB2:XAB3 XAF2:XAF3 XAJ2:XAJ3 XAN2:XAN3 XAR2:XAR3 XAV2:XAV3 XAZ2:XAZ3 XBD2:XBD3 XBH2:XBH3 XBL2:XBL3 XBP2:XBP3 XBT2:XBT3 XBX2:XBX3 XCB2:XCB3 XCF2:XCF3 XCJ2:XCJ3 XCN2:XCN3 XCR2:XCR3 XCV2:XCV3 XCZ2:XCZ3 XDD2:XDD3 XDH2:XDH3 XDL2:XDL3 XDP2:XDP3 XDT2:XDT3 XDX2:XDX3 XEB2:XEB3 XEF2:XEF3 XEJ2:XEJ3 XEN2:XEN3 XER2:XER3 XEV2:XEV3 XEZ2:XEZ3 XFD2:XFD3 D2:D123">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>D2=""</formula>
     </cfRule>

--- a/comparativo_redutores_motores_potencia.xlsx
+++ b/comparativo_redutores_motores_potencia.xlsx
@@ -8,15 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andre.santiago\Documents\MANUT REDUT INPASA 2026\ESCOPO EQUIPAMENTOS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{99133F09-992C-42D9-A056-766A1AB45BB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{703A706F-7A92-45DB-BEBB-5C55DBA9EDFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-27975" yWindow="1080" windowWidth="15375" windowHeight="7785" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-1875" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Comparativo" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
@@ -26,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="468" uniqueCount="262">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="423" uniqueCount="239">
   <si>
     <t>TIPO</t>
   </si>
@@ -193,12 +192,6 @@
     <t>5</t>
   </si>
   <si>
-    <t>601248</t>
-  </si>
-  <si>
-    <t>REDUTOR DO MOTOR TRANSPORTADOR DE CINZAS PARA O ELEVADOR C-601015</t>
-  </si>
-  <si>
     <t>601252</t>
   </si>
   <si>
@@ -208,12 +201,6 @@
     <t>4</t>
   </si>
   <si>
-    <t>601240</t>
-  </si>
-  <si>
-    <t>REDUTOR DO MOTROR TRANSPORTADOR DE CORRENTE ALIMENTAÇÃO - C-601012</t>
-  </si>
-  <si>
     <t>10</t>
   </si>
   <si>
@@ -283,12 +270,6 @@
     <t>REDUTOR ELEVADOR DE CANECA 1</t>
   </si>
   <si>
-    <t>601047</t>
-  </si>
-  <si>
-    <t>REDUTOR ESPARGIDOR</t>
-  </si>
-  <si>
     <t>0,5</t>
   </si>
   <si>
@@ -304,30 +285,6 @@
     <t>REDUTOR ESTEIRA TRANSPORTADORA DE CINZAS 02</t>
   </si>
   <si>
-    <t>601078</t>
-  </si>
-  <si>
-    <t>REDUTOR ESTEIRA TRANSPORTADORA DE CINZAS 03</t>
-  </si>
-  <si>
-    <t>601079</t>
-  </si>
-  <si>
-    <t>REDUTOR ESTEIRA TRANSPORTADORA DE CINZAS 04</t>
-  </si>
-  <si>
-    <t>601080</t>
-  </si>
-  <si>
-    <t>REDUTOR ESTEIRA TRANSPORTADORA DE CINZAS 05</t>
-  </si>
-  <si>
-    <t>601081</t>
-  </si>
-  <si>
-    <t>REDUTOR ESTEIRA TRANSPORTADORA DE CINZAS 06</t>
-  </si>
-  <si>
     <t>601210</t>
   </si>
   <si>
@@ -358,21 +315,9 @@
     <t>REDUTOR MOTOR DA VALVULA DUPLA COMPORTA (CINZAS)</t>
   </si>
   <si>
-    <t>601245</t>
-  </si>
-  <si>
-    <t>REDUTOR MOTOR TRANSP. CORRENTE RETIRADA CINZAS C601014</t>
-  </si>
-  <si>
     <t>6</t>
   </si>
   <si>
-    <t>601241</t>
-  </si>
-  <si>
-    <t>REDUTOR MOTOR TRANSPORTADOR CORRENTE ALIMENTAÇÃO C601013</t>
-  </si>
-  <si>
     <t>601248-B</t>
   </si>
   <si>
@@ -628,12 +573,6 @@
     <t>REDUTOR DA TRANSP. DE CORREIA TCD/48" 26 (ME631517)</t>
   </si>
   <si>
-    <t>631507</t>
-  </si>
-  <si>
-    <t>REDUTOR DO MOTOR TREMONHA DE ELOS COM TALISCAS TETD/100</t>
-  </si>
-  <si>
     <t>631546</t>
   </si>
   <si>
@@ -709,12 +648,6 @@
     <t>75</t>
   </si>
   <si>
-    <t>631510</t>
-  </si>
-  <si>
-    <t>REDUTOR TREMONHA DE ELOS COM TALISCAS TETD/100.1 (ME631510)</t>
-  </si>
-  <si>
     <t>631110</t>
   </si>
   <si>
@@ -809,9 +742,6 @@
   </si>
   <si>
     <t>Motor da bomba de lubrificação 2</t>
-  </si>
-  <si>
-    <t>Motor transportadora redler tard/2000 - (trr631506)</t>
   </si>
 </sst>
 </file>
@@ -839,7 +769,7 @@
       <name val="Carlito"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -849,6 +779,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF1F4E78"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -881,8 +817,8 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -910,10 +846,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="TabelaComparativoTags" displayName="TabelaComparativoTags" ref="A1:D123">
-  <autoFilter ref="A1:D123" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D123">
-    <sortCondition ref="B1:B123"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="TabelaComparativoTags" displayName="TabelaComparativoTags" ref="A1:D111">
+  <autoFilter ref="A1:D111" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D111">
+    <sortCondition ref="B1:B111"/>
   </sortState>
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="TIPO"/>
@@ -1074,7 +1010,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D123"/>
+  <dimension ref="A1:D111"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -1098,31 +1034,31 @@
       </c>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" t="s">
-        <v>237</v>
-      </c>
-      <c r="B2">
-        <v>601506</v>
-      </c>
-      <c r="C2" s="6" t="s">
-        <v>261</v>
-      </c>
-      <c r="D2" s="6" t="s">
-        <v>226</v>
+      <c r="A2" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>216</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="3" spans="1:4">
-      <c r="A3" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>238</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>239</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>240</v>
+      <c r="A3" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1130,10 +1066,10 @@
         <v>11</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>54</v>
@@ -1144,10 +1080,10 @@
         <v>11</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>54</v>
@@ -1158,10 +1094,10 @@
         <v>11</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>54</v>
@@ -1172,10 +1108,10 @@
         <v>11</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>54</v>
@@ -1186,10 +1122,10 @@
         <v>11</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>54</v>
@@ -1200,10 +1136,10 @@
         <v>11</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>54</v>
@@ -1214,10 +1150,10 @@
         <v>11</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>54</v>
@@ -1228,10 +1164,10 @@
         <v>11</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>54</v>
@@ -1242,13 +1178,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>81</v>
+        <v>122</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>82</v>
+        <v>123</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -1256,10 +1192,10 @@
         <v>11</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>140</v>
+        <v>124</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>141</v>
+        <v>125</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>40</v>
@@ -1270,10 +1206,10 @@
         <v>11</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>142</v>
+        <v>126</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>143</v>
+        <v>127</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>40</v>
@@ -1284,38 +1220,38 @@
         <v>11</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>144</v>
+        <v>128</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>145</v>
+        <v>129</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="16" spans="1:4">
+    <row r="16" spans="1:4" ht="25.5">
       <c r="A16" s="3" t="s">
         <v>11</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>146</v>
+        <v>130</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>147</v>
+        <v>131</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="25.5">
+    <row r="17" spans="1:4">
       <c r="A17" s="3" t="s">
         <v>11</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>148</v>
+        <v>38</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>149</v>
+        <v>39</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>40</v>
@@ -1326,10 +1262,10 @@
         <v>11</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>40</v>
@@ -1340,10 +1276,10 @@
         <v>11</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>40</v>
@@ -1354,10 +1290,10 @@
         <v>11</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>43</v>
+        <v>132</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>44</v>
+        <v>133</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>40</v>
@@ -1368,10 +1304,10 @@
         <v>11</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>150</v>
+        <v>134</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>151</v>
+        <v>135</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>40</v>
@@ -1382,10 +1318,10 @@
         <v>11</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>152</v>
+        <v>136</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>153</v>
+        <v>137</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>40</v>
@@ -1396,10 +1332,10 @@
         <v>11</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>154</v>
+        <v>138</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>155</v>
+        <v>139</v>
       </c>
       <c r="D23" s="3" t="s">
         <v>40</v>
@@ -1410,10 +1346,10 @@
         <v>11</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>156</v>
+        <v>140</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>157</v>
+        <v>141</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>40</v>
@@ -1424,10 +1360,10 @@
         <v>11</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>158</v>
+        <v>142</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>159</v>
+        <v>143</v>
       </c>
       <c r="D25" s="3" t="s">
         <v>40</v>
@@ -1438,10 +1374,10 @@
         <v>11</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>160</v>
+        <v>144</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>161</v>
+        <v>145</v>
       </c>
       <c r="D26" s="3" t="s">
         <v>40</v>
@@ -1452,10 +1388,10 @@
         <v>11</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>162</v>
+        <v>146</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>163</v>
+        <v>147</v>
       </c>
       <c r="D27" s="3" t="s">
         <v>40</v>
@@ -1465,67 +1401,67 @@
       <c r="A28" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B28" s="3" t="s">
-        <v>164</v>
+      <c r="B28" s="6" t="s">
+        <v>101</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>165</v>
+        <v>102</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" ht="25.5">
       <c r="A29" s="3" t="s">
         <v>11</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>85</v>
+        <v>22</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>86</v>
+        <v>23</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" ht="25.5">
       <c r="A30" s="3" t="s">
         <v>11</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" ht="25.5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4">
       <c r="A31" s="3" t="s">
         <v>11</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>22</v>
+        <v>117</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>23</v>
+        <v>118</v>
       </c>
       <c r="D31" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="32" spans="1:4" ht="25.5">
+    <row r="32" spans="1:4">
       <c r="A32" s="3" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>133</v>
+        <v>8</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>134</v>
+        <v>9</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>10</v>
@@ -1536,10 +1472,10 @@
         <v>11</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>135</v>
+        <v>8</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>136</v>
+        <v>119</v>
       </c>
       <c r="D33" s="3" t="s">
         <v>10</v>
@@ -1547,13 +1483,13 @@
     </row>
     <row r="34" spans="1:4">
       <c r="A34" s="3" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D34" s="3" t="s">
         <v>10</v>
@@ -1564,10 +1500,10 @@
         <v>11</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>8</v>
+        <v>120</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>137</v>
+        <v>121</v>
       </c>
       <c r="D35" s="3" t="s">
         <v>10</v>
@@ -1578,13 +1514,13 @@
         <v>11</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>12</v>
+        <v>148</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>13</v>
+        <v>149</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>10</v>
+        <v>26</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -1592,13 +1528,13 @@
         <v>11</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>138</v>
+        <v>162</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>139</v>
+        <v>163</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>10</v>
+        <v>26</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -1606,10 +1542,10 @@
         <v>11</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="D38" s="3" t="s">
         <v>26</v>
@@ -1620,10 +1556,10 @@
         <v>11</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>180</v>
+        <v>166</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>181</v>
+        <v>167</v>
       </c>
       <c r="D39" s="3" t="s">
         <v>26</v>
@@ -1634,10 +1570,10 @@
         <v>11</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>182</v>
+        <v>168</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>183</v>
+        <v>169</v>
       </c>
       <c r="D40" s="3" t="s">
         <v>26</v>
@@ -1648,10 +1584,10 @@
         <v>11</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>184</v>
+        <v>170</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>185</v>
+        <v>171</v>
       </c>
       <c r="D41" s="3" t="s">
         <v>26</v>
@@ -1662,10 +1598,10 @@
         <v>11</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>186</v>
+        <v>172</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>26</v>
@@ -1676,10 +1612,10 @@
         <v>11</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>188</v>
+        <v>150</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>189</v>
+        <v>151</v>
       </c>
       <c r="D43" s="3" t="s">
         <v>26</v>
@@ -1690,13 +1626,13 @@
         <v>11</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>190</v>
+        <v>152</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>191</v>
+        <v>153</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>26</v>
+        <v>7</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -1704,13 +1640,13 @@
         <v>11</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>168</v>
+        <v>154</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>169</v>
+        <v>155</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>26</v>
+        <v>7</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -1718,13 +1654,13 @@
         <v>11</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>170</v>
+        <v>82</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>171</v>
+        <v>83</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -1732,24 +1668,24 @@
         <v>11</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>172</v>
+        <v>84</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>173</v>
+        <v>85</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
     </row>
     <row r="48" spans="1:4">
       <c r="A48" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B48" s="3" t="s">
-        <v>88</v>
+      <c r="B48" s="6" t="s">
+        <v>103</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>89</v>
+        <v>104</v>
       </c>
       <c r="D48" s="3" t="s">
         <v>16</v>
@@ -1759,11 +1695,11 @@
       <c r="A49" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B49" s="3" t="s">
-        <v>90</v>
+      <c r="B49" s="6" t="s">
+        <v>105</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>91</v>
+        <v>106</v>
       </c>
       <c r="D49" s="3" t="s">
         <v>16</v>
@@ -1773,11 +1709,11 @@
       <c r="A50" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B50" s="3" t="s">
-        <v>92</v>
+      <c r="B50" s="6" t="s">
+        <v>107</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>93</v>
+        <v>108</v>
       </c>
       <c r="D50" s="3" t="s">
         <v>16</v>
@@ -1787,11 +1723,11 @@
       <c r="A51" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B51" s="3" t="s">
-        <v>121</v>
+      <c r="B51" s="6" t="s">
+        <v>109</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>122</v>
+        <v>110</v>
       </c>
       <c r="D51" s="3" t="s">
         <v>16</v>
@@ -1802,10 +1738,10 @@
         <v>11</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>94</v>
+        <v>79</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>16</v>
@@ -1816,10 +1752,10 @@
         <v>11</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>123</v>
+        <v>14</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>124</v>
+        <v>15</v>
       </c>
       <c r="D53" s="3" t="s">
         <v>16</v>
@@ -1830,10 +1766,10 @@
         <v>11</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>96</v>
+        <v>31</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>97</v>
+        <v>32</v>
       </c>
       <c r="D54" s="3" t="s">
         <v>16</v>
@@ -1844,69 +1780,69 @@
         <v>11</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>125</v>
+        <v>33</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>126</v>
+        <v>34</v>
       </c>
       <c r="D55" s="3" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="56" spans="1:4">
-      <c r="A56" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B56" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="C56" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="D56" s="3" t="s">
-        <v>16</v>
+      <c r="A56" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="B56" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="C56" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="D56" s="4" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="57" spans="1:4">
-      <c r="A57" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B57" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="C57" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="D57" s="3" t="s">
-        <v>16</v>
+      <c r="A57" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="B57" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="C57" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="D57" s="4" t="s">
+        <v>223</v>
       </c>
     </row>
     <row r="58" spans="1:4">
-      <c r="A58" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B58" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="C58" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="D58" s="3" t="s">
-        <v>16</v>
+      <c r="A58" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="B58" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="C58" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="D58" s="4" t="s">
+        <v>223</v>
       </c>
     </row>
     <row r="59" spans="1:4">
       <c r="A59" s="3" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -1914,13 +1850,13 @@
         <v>11</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -1928,69 +1864,69 @@
         <v>11</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>33</v>
+        <v>156</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>34</v>
+        <v>157</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
     </row>
     <row r="62" spans="1:4">
-      <c r="A62" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="B62" s="4" t="s">
-        <v>241</v>
-      </c>
-      <c r="C62" s="5" t="s">
-        <v>242</v>
-      </c>
-      <c r="D62" s="4" t="s">
+      <c r="A62" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="D62" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4">
+      <c r="A63" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="D63" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4">
+      <c r="A64" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D64" s="3" t="s">
         <v>10</v>
-      </c>
-    </row>
-    <row r="63" spans="1:4">
-      <c r="A63" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="B63" s="4" t="s">
-        <v>243</v>
-      </c>
-      <c r="C63" s="5" t="s">
-        <v>244</v>
-      </c>
-      <c r="D63" s="4" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="64" spans="1:4">
-      <c r="A64" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="B64" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="C64" s="5" t="s">
-        <v>247</v>
-      </c>
-      <c r="D64" s="4" t="s">
-        <v>245</v>
       </c>
     </row>
     <row r="65" spans="1:4">
       <c r="A65" s="3" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -1998,55 +1934,55 @@
         <v>11</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>51</v>
+        <v>18</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="67" spans="1:4">
-      <c r="A67" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B67" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="C67" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="D67" s="3" t="s">
-        <v>7</v>
+      <c r="A67" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="B67" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="C67" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="D67" s="4" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="68" spans="1:4">
-      <c r="A68" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B68" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="C68" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="D68" s="3" t="s">
-        <v>7</v>
+      <c r="A68" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="B68" s="4" t="s">
+        <v>228</v>
+      </c>
+      <c r="C68" s="5" t="s">
+        <v>229</v>
+      </c>
+      <c r="D68" s="4" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="69" spans="1:4">
-      <c r="A69" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B69" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="C69" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="D69" s="3" t="s">
-        <v>7</v>
+      <c r="A69" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="B69" s="4" t="s">
+        <v>230</v>
+      </c>
+      <c r="C69" s="5" t="s">
+        <v>231</v>
+      </c>
+      <c r="D69" s="4" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2054,13 +1990,13 @@
         <v>11</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>19</v>
+        <v>86</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>20</v>
+        <v>87</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>10</v>
+        <v>37</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2068,13 +2004,13 @@
         <v>11</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>10</v>
+        <v>37</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2082,55 +2018,55 @@
         <v>11</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>17</v>
+        <v>90</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>18</v>
+        <v>91</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>10</v>
+        <v>37</v>
       </c>
     </row>
     <row r="73" spans="1:4">
-      <c r="A73" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="B73" s="4" t="s">
-        <v>248</v>
-      </c>
-      <c r="C73" s="5" t="s">
-        <v>249</v>
-      </c>
-      <c r="D73" s="4" t="s">
-        <v>10</v>
+      <c r="A73" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B73" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D73" s="3" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="74" spans="1:4">
-      <c r="A74" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="B74" s="4" t="s">
-        <v>250</v>
-      </c>
-      <c r="C74" s="5" t="s">
-        <v>251</v>
-      </c>
-      <c r="D74" s="4" t="s">
-        <v>10</v>
+      <c r="A74" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="D74" s="3" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="75" spans="1:4">
-      <c r="A75" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="B75" s="4" t="s">
-        <v>252</v>
-      </c>
-      <c r="C75" s="5" t="s">
-        <v>253</v>
-      </c>
-      <c r="D75" s="4" t="s">
-        <v>10</v>
+      <c r="A75" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B75" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D75" s="3" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2138,10 +2074,10 @@
         <v>11</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>100</v>
+        <v>49</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>101</v>
+        <v>50</v>
       </c>
       <c r="D76" s="3" t="s">
         <v>37</v>
@@ -2152,55 +2088,55 @@
         <v>11</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>102</v>
+        <v>47</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>103</v>
+        <v>48</v>
       </c>
       <c r="D77" s="3" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="78" spans="1:4">
-      <c r="A78" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B78" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="C78" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="D78" s="3" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="79" spans="1:4">
+      <c r="A78" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="B78" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="C78" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="D78" s="4" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" ht="25.5">
       <c r="A79" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B79" s="3" t="s">
-        <v>106</v>
+      <c r="B79" s="6" t="s">
+        <v>99</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="80" spans="1:4">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" ht="25.5">
       <c r="A80" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B80" s="3" t="s">
-        <v>108</v>
+      <c r="B80" s="6" t="s">
+        <v>113</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>37</v>
+        <v>16</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -2208,13 +2144,13 @@
         <v>11</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -2222,13 +2158,13 @@
         <v>11</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>49</v>
+        <v>27</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -2236,55 +2172,53 @@
         <v>11</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="84" spans="1:4">
-      <c r="A84" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="B84" s="4" t="s">
-        <v>254</v>
-      </c>
-      <c r="C84" s="5" t="s">
-        <v>255</v>
-      </c>
-      <c r="D84" s="4" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="85" spans="1:4" ht="25.5">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" ht="25.5">
+      <c r="A84" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B84" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="D84" s="3" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4">
       <c r="A85" s="3" t="s">
         <v>11</v>
       </c>
       <c r="B85" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C85" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="C85" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="D85" s="3" t="s">
-        <v>62</v>
-      </c>
+      <c r="D85" s="3"/>
     </row>
     <row r="86" spans="1:4" ht="25.5">
       <c r="A86" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B86" s="3" t="s">
-        <v>117</v>
+      <c r="B86" s="6" t="s">
+        <v>97</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>118</v>
+        <v>98</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -2292,69 +2226,67 @@
         <v>11</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>113</v>
+        <v>45</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="D87" s="3" t="s">
-        <v>16</v>
-      </c>
+        <v>46</v>
+      </c>
+      <c r="D87" s="3"/>
     </row>
     <row r="88" spans="1:4" ht="25.5">
       <c r="A88" s="3" t="s">
         <v>11</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>131</v>
+        <v>52</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>132</v>
+        <v>53</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="89" spans="1:4">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" ht="25.5">
       <c r="A89" s="3" t="s">
         <v>11</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>24</v>
+        <v>55</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>25</v>
+        <v>56</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>26</v>
+        <v>57</v>
       </c>
     </row>
     <row r="90" spans="1:4">
-      <c r="A90" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B90" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C90" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D90" s="3" t="s">
-        <v>26</v>
+      <c r="A90" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="B90" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="C90" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="D90" s="4" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="91" spans="1:4">
-      <c r="A91" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B91" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C91" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="D91" s="3" t="s">
-        <v>26</v>
+      <c r="A91" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="B91" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="C91" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="D91" s="4" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -2362,158 +2294,144 @@
         <v>11</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>110</v>
+        <v>186</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="D92" s="3" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="93" spans="1:4" ht="25.5">
+        <v>187</v>
+      </c>
+      <c r="D92" s="3"/>
+    </row>
+    <row r="93" spans="1:4">
       <c r="A93" s="3" t="s">
         <v>11</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>129</v>
+        <v>188</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="D93" s="3" t="s">
-        <v>112</v>
-      </c>
+        <v>189</v>
+      </c>
+      <c r="D93" s="3"/>
     </row>
     <row r="94" spans="1:4">
       <c r="A94" s="3" t="s">
         <v>11</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>63</v>
+        <v>184</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>64</v>
+        <v>185</v>
       </c>
       <c r="D94" s="3"/>
     </row>
-    <row r="95" spans="1:4" ht="25.5">
+    <row r="95" spans="1:4">
       <c r="A95" s="3" t="s">
         <v>11</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>55</v>
+        <v>196</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="D95" s="3" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="96" spans="1:4" ht="25.5">
+        <v>197</v>
+      </c>
+      <c r="D95" s="3"/>
+    </row>
+    <row r="96" spans="1:4">
       <c r="A96" s="3" t="s">
         <v>11</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>115</v>
+        <v>209</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="D96" s="3" t="s">
-        <v>54</v>
-      </c>
+        <v>210</v>
+      </c>
+      <c r="D96" s="3"/>
     </row>
     <row r="97" spans="1:4">
       <c r="A97" s="3" t="s">
         <v>11</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>45</v>
+        <v>200</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>46</v>
+        <v>201</v>
       </c>
       <c r="D97" s="3"/>
     </row>
-    <row r="98" spans="1:4" ht="25.5">
+    <row r="98" spans="1:4">
       <c r="A98" s="3" t="s">
         <v>11</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>52</v>
+        <v>211</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="D98" s="3" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="99" spans="1:4" ht="25.5">
+        <v>212</v>
+      </c>
+      <c r="D98" s="3"/>
+    </row>
+    <row r="99" spans="1:4">
       <c r="A99" s="3" t="s">
         <v>11</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>57</v>
+        <v>202</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="D99" s="3" t="s">
-        <v>59</v>
-      </c>
+        <v>203</v>
+      </c>
+      <c r="D99" s="3"/>
     </row>
     <row r="100" spans="1:4">
-      <c r="A100" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="B100" s="4" t="s">
-        <v>257</v>
-      </c>
-      <c r="C100" s="5" t="s">
-        <v>258</v>
-      </c>
-      <c r="D100" s="4" t="s">
-        <v>40</v>
-      </c>
+      <c r="A100" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B100" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="C100" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="D100" s="3"/>
     </row>
     <row r="101" spans="1:4">
-      <c r="A101" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="B101" s="4" t="s">
-        <v>259</v>
-      </c>
-      <c r="C101" s="5" t="s">
-        <v>260</v>
-      </c>
-      <c r="D101" s="4" t="s">
-        <v>40</v>
-      </c>
+      <c r="A101" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B101" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="C101" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="D101" s="3"/>
     </row>
     <row r="102" spans="1:4">
       <c r="A102" s="3" t="s">
         <v>11</v>
       </c>
       <c r="B102" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="C102" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="D102" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="C102" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="D102" s="3"/>
-    </row>
-    <row r="103" spans="1:4">
+    </row>
+    <row r="103" spans="1:4" ht="25.5">
       <c r="A103" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B103" s="3" t="s">
-        <v>208</v>
+      <c r="B103" s="6" t="s">
+        <v>192</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>209</v>
+        <v>193</v>
       </c>
       <c r="D103" s="3"/>
     </row>
@@ -2522,34 +2440,34 @@
         <v>11</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>204</v>
+        <v>174</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>205</v>
+        <v>175</v>
       </c>
       <c r="D104" s="3"/>
     </row>
-    <row r="105" spans="1:4">
+    <row r="105" spans="1:4" ht="25.5">
       <c r="A105" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B105" s="3" t="s">
-        <v>216</v>
+      <c r="B105" s="6" t="s">
+        <v>194</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>217</v>
+        <v>195</v>
       </c>
       <c r="D105" s="3"/>
     </row>
-    <row r="106" spans="1:4">
+    <row r="106" spans="1:4" ht="25.5">
       <c r="A106" s="3" t="s">
         <v>11</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>231</v>
+        <v>213</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>232</v>
+        <v>214</v>
       </c>
       <c r="D106" s="3"/>
     </row>
@@ -2558,10 +2476,10 @@
         <v>11</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>220</v>
+        <v>178</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>221</v>
+        <v>179</v>
       </c>
       <c r="D107" s="3"/>
     </row>
@@ -2570,10 +2488,10 @@
         <v>11</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>233</v>
+        <v>190</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>234</v>
+        <v>191</v>
       </c>
       <c r="D108" s="3"/>
     </row>
@@ -2582,10 +2500,10 @@
         <v>11</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>222</v>
+        <v>176</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>223</v>
+        <v>177</v>
       </c>
       <c r="D109" s="3"/>
     </row>
@@ -2594,10 +2512,10 @@
         <v>11</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>229</v>
+        <v>180</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>230</v>
+        <v>181</v>
       </c>
       <c r="D110" s="3"/>
     </row>
@@ -2606,161 +2524,15 @@
         <v>11</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>218</v>
+        <v>182</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>219</v>
+        <v>183</v>
       </c>
       <c r="D111" s="3"/>
     </row>
-    <row r="112" spans="1:4">
-      <c r="A112" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B112" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="C112" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="D112" s="3" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="113" spans="1:4">
-      <c r="A113" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B113" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="C113" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="D113" s="3"/>
-    </row>
-    <row r="114" spans="1:4" ht="25.5">
-      <c r="A114" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B114" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="C114" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="D114" s="3"/>
-    </row>
-    <row r="115" spans="1:4">
-      <c r="A115" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B115" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="C115" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="D115" s="3"/>
-    </row>
-    <row r="116" spans="1:4">
-      <c r="A116" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B116" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="C116" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="D116" s="3"/>
-    </row>
-    <row r="117" spans="1:4" ht="25.5">
-      <c r="A117" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B117" s="3" t="s">
-        <v>214</v>
-      </c>
-      <c r="C117" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="D117" s="3"/>
-    </row>
-    <row r="118" spans="1:4" ht="25.5">
-      <c r="A118" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B118" s="3" t="s">
-        <v>235</v>
-      </c>
-      <c r="C118" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="D118" s="3"/>
-    </row>
-    <row r="119" spans="1:4">
-      <c r="A119" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B119" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="C119" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="D119" s="3"/>
-    </row>
-    <row r="120" spans="1:4">
-      <c r="A120" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B120" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="C120" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="D120" s="3"/>
-    </row>
-    <row r="121" spans="1:4">
-      <c r="A121" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B121" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="C121" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="D121" s="3"/>
-    </row>
-    <row r="122" spans="1:4">
-      <c r="A122" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B122" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="C122" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="D122" s="3"/>
-    </row>
-    <row r="123" spans="1:4">
-      <c r="A123" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B123" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="C123" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="D123" s="3"/>
-    </row>
   </sheetData>
-  <conditionalFormatting sqref="H2:H3 L2:L3 P2:P3 T2:T3 X2:X3 AB2:AB3 AF2:AF3 AJ2:AJ3 AN2:AN3 AR2:AR3 AV2:AV3 AZ2:AZ3 BD2:BD3 BH2:BH3 BL2:BL3 BP2:BP3 BT2:BT3 BX2:BX3 CB2:CB3 CF2:CF3 CJ2:CJ3 CN2:CN3 CR2:CR3 CV2:CV3 CZ2:CZ3 DD2:DD3 DH2:DH3 DL2:DL3 DP2:DP3 DT2:DT3 DX2:DX3 EB2:EB3 EF2:EF3 EJ2:EJ3 EN2:EN3 ER2:ER3 EV2:EV3 EZ2:EZ3 FD2:FD3 FH2:FH3 FL2:FL3 FP2:FP3 FT2:FT3 FX2:FX3 GB2:GB3 GF2:GF3 GJ2:GJ3 GN2:GN3 GR2:GR3 GV2:GV3 GZ2:GZ3 HD2:HD3 HH2:HH3 HL2:HL3 HP2:HP3 HT2:HT3 HX2:HX3 IB2:IB3 IF2:IF3 IJ2:IJ3 IN2:IN3 IR2:IR3 IV2:IV3 IZ2:IZ3 JD2:JD3 JH2:JH3 JL2:JL3 JP2:JP3 JT2:JT3 JX2:JX3 KB2:KB3 KF2:KF3 KJ2:KJ3 KN2:KN3 KR2:KR3 KV2:KV3 KZ2:KZ3 LD2:LD3 LH2:LH3 LL2:LL3 LP2:LP3 LT2:LT3 LX2:LX3 MB2:MB3 MF2:MF3 MJ2:MJ3 MN2:MN3 MR2:MR3 MV2:MV3 MZ2:MZ3 ND2:ND3 NH2:NH3 NL2:NL3 NP2:NP3 NT2:NT3 NX2:NX3 OB2:OB3 OF2:OF3 OJ2:OJ3 ON2:ON3 OR2:OR3 OV2:OV3 OZ2:OZ3 PD2:PD3 PH2:PH3 PL2:PL3 PP2:PP3 PT2:PT3 PX2:PX3 QB2:QB3 QF2:QF3 QJ2:QJ3 QN2:QN3 QR2:QR3 QV2:QV3 QZ2:QZ3 RD2:RD3 RH2:RH3 RL2:RL3 RP2:RP3 RT2:RT3 RX2:RX3 SB2:SB3 SF2:SF3 SJ2:SJ3 SN2:SN3 SR2:SR3 SV2:SV3 SZ2:SZ3 TD2:TD3 TH2:TH3 TL2:TL3 TP2:TP3 TT2:TT3 TX2:TX3 UB2:UB3 UF2:UF3 UJ2:UJ3 UN2:UN3 UR2:UR3 UV2:UV3 UZ2:UZ3 VD2:VD3 VH2:VH3 VL2:VL3 VP2:VP3 VT2:VT3 VX2:VX3 WB2:WB3 WF2:WF3 WJ2:WJ3 WN2:WN3 WR2:WR3 WV2:WV3 WZ2:WZ3 XD2:XD3 XH2:XH3 XL2:XL3 XP2:XP3 XT2:XT3 XX2:XX3 YB2:YB3 YF2:YF3 YJ2:YJ3 YN2:YN3 YR2:YR3 YV2:YV3 YZ2:YZ3 ZD2:ZD3 ZH2:ZH3 ZL2:ZL3 ZP2:ZP3 ZT2:ZT3 ZX2:ZX3 AAB2:AAB3 AAF2:AAF3 AAJ2:AAJ3 AAN2:AAN3 AAR2:AAR3 AAV2:AAV3 AAZ2:AAZ3 ABD2:ABD3 ABH2:ABH3 ABL2:ABL3 ABP2:ABP3 ABT2:ABT3 ABX2:ABX3 ACB2:ACB3 ACF2:ACF3 ACJ2:ACJ3 ACN2:ACN3 ACR2:ACR3 ACV2:ACV3 ACZ2:ACZ3 ADD2:ADD3 ADH2:ADH3 ADL2:ADL3 ADP2:ADP3 ADT2:ADT3 ADX2:ADX3 AEB2:AEB3 AEF2:AEF3 AEJ2:AEJ3 AEN2:AEN3 AER2:AER3 AEV2:AEV3 AEZ2:AEZ3 AFD2:AFD3 AFH2:AFH3 AFL2:AFL3 AFP2:AFP3 AFT2:AFT3 AFX2:AFX3 AGB2:AGB3 AGF2:AGF3 AGJ2:AGJ3 AGN2:AGN3 AGR2:AGR3 AGV2:AGV3 AGZ2:AGZ3 AHD2:AHD3 AHH2:AHH3 AHL2:AHL3 AHP2:AHP3 AHT2:AHT3 AHX2:AHX3 AIB2:AIB3 AIF2:AIF3 AIJ2:AIJ3 AIN2:AIN3 AIR2:AIR3 AIV2:AIV3 AIZ2:AIZ3 AJD2:AJD3 AJH2:AJH3 AJL2:AJL3 AJP2:AJP3 AJT2:AJT3 AJX2:AJX3 AKB2:AKB3 AKF2:AKF3 AKJ2:AKJ3 AKN2:AKN3 AKR2:AKR3 AKV2:AKV3 AKZ2:AKZ3 ALD2:ALD3 ALH2:ALH3 ALL2:ALL3 ALP2:ALP3 ALT2:ALT3 ALX2:ALX3 AMB2:AMB3 AMF2:AMF3 AMJ2:AMJ3 AMN2:AMN3 AMR2:AMR3 AMV2:AMV3 AMZ2:AMZ3 AND2:AND3 ANH2:ANH3 ANL2:ANL3 ANP2:ANP3 ANT2:ANT3 ANX2:ANX3 AOB2:AOB3 AOF2:AOF3 AOJ2:AOJ3 AON2:AON3 AOR2:AOR3 AOV2:AOV3 AOZ2:AOZ3 APD2:APD3 APH2:APH3 APL2:APL3 APP2:APP3 APT2:APT3 APX2:APX3 AQB2:AQB3 AQF2:AQF3 AQJ2:AQJ3 AQN2:AQN3 AQR2:AQR3 AQV2:AQV3 AQZ2:AQZ3 ARD2:ARD3 ARH2:ARH3 ARL2:ARL3 ARP2:ARP3 ART2:ART3 ARX2:ARX3 ASB2:ASB3 ASF2:ASF3 ASJ2:ASJ3 ASN2:ASN3 ASR2:ASR3 ASV2:ASV3 ASZ2:ASZ3 ATD2:ATD3 ATH2:ATH3 ATL2:ATL3 ATP2:ATP3 ATT2:ATT3 ATX2:ATX3 AUB2:AUB3 AUF2:AUF3 AUJ2:AUJ3 AUN2:AUN3 AUR2:AUR3 AUV2:AUV3 AUZ2:AUZ3 AVD2:AVD3 AVH2:AVH3 AVL2:AVL3 AVP2:AVP3 AVT2:AVT3 AVX2:AVX3 AWB2:AWB3 AWF2:AWF3 AWJ2:AWJ3 AWN2:AWN3 AWR2:AWR3 AWV2:AWV3 AWZ2:AWZ3 AXD2:AXD3 AXH2:AXH3 AXL2:AXL3 AXP2:AXP3 AXT2:AXT3 AXX2:AXX3 AYB2:AYB3 AYF2:AYF3 AYJ2:AYJ3 AYN2:AYN3 AYR2:AYR3 AYV2:AYV3 AYZ2:AYZ3 AZD2:AZD3 AZH2:AZH3 AZL2:AZL3 AZP2:AZP3 AZT2:AZT3 AZX2:AZX3 BAB2:BAB3 BAF2:BAF3 BAJ2:BAJ3 BAN2:BAN3 BAR2:BAR3 BAV2:BAV3 BAZ2:BAZ3 BBD2:BBD3 BBH2:BBH3 BBL2:BBL3 BBP2:BBP3 BBT2:BBT3 BBX2:BBX3 BCB2:BCB3 BCF2:BCF3 BCJ2:BCJ3 BCN2:BCN3 BCR2:BCR3 BCV2:BCV3 BCZ2:BCZ3 BDD2:BDD3 BDH2:BDH3 BDL2:BDL3 BDP2:BDP3 BDT2:BDT3 BDX2:BDX3 BEB2:BEB3 BEF2:BEF3 BEJ2:BEJ3 BEN2:BEN3 BER2:BER3 BEV2:BEV3 BEZ2:BEZ3 BFD2:BFD3 BFH2:BFH3 BFL2:BFL3 BFP2:BFP3 BFT2:BFT3 BFX2:BFX3 BGB2:BGB3 BGF2:BGF3 BGJ2:BGJ3 BGN2:BGN3 BGR2:BGR3 BGV2:BGV3 BGZ2:BGZ3 BHD2:BHD3 BHH2:BHH3 BHL2:BHL3 BHP2:BHP3 BHT2:BHT3 BHX2:BHX3 BIB2:BIB3 BIF2:BIF3 BIJ2:BIJ3 BIN2:BIN3 BIR2:BIR3 BIV2:BIV3 BIZ2:BIZ3 BJD2:BJD3 BJH2:BJH3 BJL2:BJL3 BJP2:BJP3 BJT2:BJT3 BJX2:BJX3 BKB2:BKB3 BKF2:BKF3 BKJ2:BKJ3 BKN2:BKN3 BKR2:BKR3 BKV2:BKV3 BKZ2:BKZ3 BLD2:BLD3 BLH2:BLH3 BLL2:BLL3 BLP2:BLP3 BLT2:BLT3 BLX2:BLX3 BMB2:BMB3 BMF2:BMF3 BMJ2:BMJ3 BMN2:BMN3 BMR2:BMR3 BMV2:BMV3 BMZ2:BMZ3 BND2:BND3 BNH2:BNH3 BNL2:BNL3 BNP2:BNP3 BNT2:BNT3 BNX2:BNX3 BOB2:BOB3 BOF2:BOF3 BOJ2:BOJ3 BON2:BON3 BOR2:BOR3 BOV2:BOV3 BOZ2:BOZ3 BPD2:BPD3 BPH2:BPH3 BPL2:BPL3 BPP2:BPP3 BPT2:BPT3 BPX2:BPX3 BQB2:BQB3 BQF2:BQF3 BQJ2:BQJ3 BQN2:BQN3 BQR2:BQR3 BQV2:BQV3 BQZ2:BQZ3 BRD2:BRD3 BRH2:BRH3 BRL2:BRL3 BRP2:BRP3 BRT2:BRT3 BRX2:BRX3 BSB2:BSB3 BSF2:BSF3 BSJ2:BSJ3 BSN2:BSN3 BSR2:BSR3 BSV2:BSV3 BSZ2:BSZ3 BTD2:BTD3 BTH2:BTH3 BTL2:BTL3 BTP2:BTP3 BTT2:BTT3 BTX2:BTX3 BUB2:BUB3 BUF2:BUF3 BUJ2:BUJ3 BUN2:BUN3 BUR2:BUR3 BUV2:BUV3 BUZ2:BUZ3 BVD2:BVD3 BVH2:BVH3 BVL2:BVL3 BVP2:BVP3 BVT2:BVT3 BVX2:BVX3 BWB2:BWB3 BWF2:BWF3 BWJ2:BWJ3 BWN2:BWN3 BWR2:BWR3 BWV2:BWV3 BWZ2:BWZ3 BXD2:BXD3 BXH2:BXH3 BXL2:BXL3 BXP2:BXP3 BXT2:BXT3 BXX2:BXX3 BYB2:BYB3 BYF2:BYF3 BYJ2:BYJ3 BYN2:BYN3 BYR2:BYR3 BYV2:BYV3 BYZ2:BYZ3 BZD2:BZD3 BZH2:BZH3 BZL2:BZL3 BZP2:BZP3 BZT2:BZT3 BZX2:BZX3 CAB2:CAB3 CAF2:CAF3 CAJ2:CAJ3 CAN2:CAN3 CAR2:CAR3 CAV2:CAV3 CAZ2:CAZ3 CBD2:CBD3 CBH2:CBH3 CBL2:CBL3 CBP2:CBP3 CBT2:CBT3 CBX2:CBX3 CCB2:CCB3 CCF2:CCF3 CCJ2:CCJ3 CCN2:CCN3 CCR2:CCR3 CCV2:CCV3 CCZ2:CCZ3 CDD2:CDD3 CDH2:CDH3 CDL2:CDL3 CDP2:CDP3 CDT2:CDT3 CDX2:CDX3 CEB2:CEB3 CEF2:CEF3 CEJ2:CEJ3 CEN2:CEN3 CER2:CER3 CEV2:CEV3 CEZ2:CEZ3 CFD2:CFD3 CFH2:CFH3 CFL2:CFL3 CFP2:CFP3 CFT2:CFT3 CFX2:CFX3 CGB2:CGB3 CGF2:CGF3 CGJ2:CGJ3 CGN2:CGN3 CGR2:CGR3 CGV2:CGV3 CGZ2:CGZ3 CHD2:CHD3 CHH2:CHH3 CHL2:CHL3 CHP2:CHP3 CHT2:CHT3 CHX2:CHX3 CIB2:CIB3 CIF2:CIF3 CIJ2:CIJ3 CIN2:CIN3 CIR2:CIR3 CIV2:CIV3 CIZ2:CIZ3 CJD2:CJD3 CJH2:CJH3 CJL2:CJL3 CJP2:CJP3 CJT2:CJT3 CJX2:CJX3 CKB2:CKB3 CKF2:CKF3 CKJ2:CKJ3 CKN2:CKN3 CKR2:CKR3 CKV2:CKV3 CKZ2:CKZ3 CLD2:CLD3 CLH2:CLH3 CLL2:CLL3 CLP2:CLP3 CLT2:CLT3 CLX2:CLX3 CMB2:CMB3 CMF2:CMF3 CMJ2:CMJ3 CMN2:CMN3 CMR2:CMR3 CMV2:CMV3 CMZ2:CMZ3 CND2:CND3 CNH2:CNH3 CNL2:CNL3 CNP2:CNP3 CNT2:CNT3 CNX2:CNX3 COB2:COB3 COF2:COF3 COJ2:COJ3 CON2:CON3 COR2:COR3 COV2:COV3 COZ2:COZ3 CPD2:CPD3 CPH2:CPH3 CPL2:CPL3 CPP2:CPP3 CPT2:CPT3 CPX2:CPX3 CQB2:CQB3 CQF2:CQF3 CQJ2:CQJ3 CQN2:CQN3 CQR2:CQR3 CQV2:CQV3 CQZ2:CQZ3 CRD2:CRD3 CRH2:CRH3 CRL2:CRL3 CRP2:CRP3 CRT2:CRT3 CRX2:CRX3 CSB2:CSB3 CSF2:CSF3 CSJ2:CSJ3 CSN2:CSN3 CSR2:CSR3 CSV2:CSV3 CSZ2:CSZ3 CTD2:CTD3 CTH2:CTH3 CTL2:CTL3 CTP2:CTP3 CTT2:CTT3 CTX2:CTX3 CUB2:CUB3 CUF2:CUF3 CUJ2:CUJ3 CUN2:CUN3 CUR2:CUR3 CUV2:CUV3 CUZ2:CUZ3 CVD2:CVD3 CVH2:CVH3 CVL2:CVL3 CVP2:CVP3 CVT2:CVT3 CVX2:CVX3 CWB2:CWB3 CWF2:CWF3 CWJ2:CWJ3 CWN2:CWN3 CWR2:CWR3 CWV2:CWV3 CWZ2:CWZ3 CXD2:CXD3 CXH2:CXH3 CXL2:CXL3 CXP2:CXP3 CXT2:CXT3 CXX2:CXX3 CYB2:CYB3 CYF2:CYF3 CYJ2:CYJ3 CYN2:CYN3 CYR2:CYR3 CYV2:CYV3 CYZ2:CYZ3 CZD2:CZD3 CZH2:CZH3 CZL2:CZL3 CZP2:CZP3 CZT2:CZT3 CZX2:CZX3 DAB2:DAB3 DAF2:DAF3 DAJ2:DAJ3 DAN2:DAN3 DAR2:DAR3 DAV2:DAV3 DAZ2:DAZ3 DBD2:DBD3 DBH2:DBH3 DBL2:DBL3 DBP2:DBP3 DBT2:DBT3 DBX2:DBX3 DCB2:DCB3 DCF2:DCF3 DCJ2:DCJ3 DCN2:DCN3 DCR2:DCR3 DCV2:DCV3 DCZ2:DCZ3 DDD2:DDD3 DDH2:DDH3 DDL2:DDL3 DDP2:DDP3 DDT2:DDT3 DDX2:DDX3 DEB2:DEB3 DEF2:DEF3 DEJ2:DEJ3 DEN2:DEN3 DER2:DER3 DEV2:DEV3 DEZ2:DEZ3 DFD2:DFD3 DFH2:DFH3 DFL2:DFL3 DFP2:DFP3 DFT2:DFT3 DFX2:DFX3 DGB2:DGB3 DGF2:DGF3 DGJ2:DGJ3 DGN2:DGN3 DGR2:DGR3 DGV2:DGV3 DGZ2:DGZ3 DHD2:DHD3 DHH2:DHH3 DHL2:DHL3 DHP2:DHP3 DHT2:DHT3 DHX2:DHX3 DIB2:DIB3 DIF2:DIF3 DIJ2:DIJ3 DIN2:DIN3 DIR2:DIR3 DIV2:DIV3 DIZ2:DIZ3 DJD2:DJD3 DJH2:DJH3 DJL2:DJL3 DJP2:DJP3 DJT2:DJT3 DJX2:DJX3 DKB2:DKB3 DKF2:DKF3 DKJ2:DKJ3 DKN2:DKN3 DKR2:DKR3 DKV2:DKV3 DKZ2:DKZ3 DLD2:DLD3 DLH2:DLH3 DLL2:DLL3 DLP2:DLP3 DLT2:DLT3 DLX2:DLX3 DMB2:DMB3 DMF2:DMF3 DMJ2:DMJ3 DMN2:DMN3 DMR2:DMR3 DMV2:DMV3 DMZ2:DMZ3 DND2:DND3 DNH2:DNH3 DNL2:DNL3 DNP2:DNP3 DNT2:DNT3 DNX2:DNX3 DOB2:DOB3 DOF2:DOF3 DOJ2:DOJ3 DON2:DON3 DOR2:DOR3 DOV2:DOV3 DOZ2:DOZ3 DPD2:DPD3 DPH2:DPH3 DPL2:DPL3 DPP2:DPP3 DPT2:DPT3 DPX2:DPX3 DQB2:DQB3 DQF2:DQF3 DQJ2:DQJ3 DQN2:DQN3 DQR2:DQR3 DQV2:DQV3 DQZ2:DQZ3 DRD2:DRD3 DRH2:DRH3 DRL2:DRL3 DRP2:DRP3 DRT2:DRT3 DRX2:DRX3 DSB2:DSB3 DSF2:DSF3 DSJ2:DSJ3 DSN2:DSN3 DSR2:DSR3 DSV2:DSV3 DSZ2:DSZ3 DTD2:DTD3 DTH2:DTH3 DTL2:DTL3 DTP2:DTP3 DTT2:DTT3 DTX2:DTX3 DUB2:DUB3 DUF2:DUF3 DUJ2:DUJ3 DUN2:DUN3 DUR2:DUR3 DUV2:DUV3 DUZ2:DUZ3 DVD2:DVD3 DVH2:DVH3 DVL2:DVL3 DVP2:DVP3 DVT2:DVT3 DVX2:DVX3 DWB2:DWB3 DWF2:DWF3 DWJ2:DWJ3 DWN2:DWN3 DWR2:DWR3 DWV2:DWV3 DWZ2:DWZ3 DXD2:DXD3 DXH2:DXH3 DXL2:DXL3 DXP2:DXP3 DXT2:DXT3 DXX2:DXX3 DYB2:DYB3 DYF2:DYF3 DYJ2:DYJ3 DYN2:DYN3 DYR2:DYR3 DYV2:DYV3 DYZ2:DYZ3 DZD2:DZD3 DZH2:DZH3 DZL2:DZL3 DZP2:DZP3 DZT2:DZT3 DZX2:DZX3 EAB2:EAB3 EAF2:EAF3 EAJ2:EAJ3 EAN2:EAN3 EAR2:EAR3 EAV2:EAV3 EAZ2:EAZ3 EBD2:EBD3 EBH2:EBH3 EBL2:EBL3 EBP2:EBP3 EBT2:EBT3 EBX2:EBX3 ECB2:ECB3 ECF2:ECF3 ECJ2:ECJ3 ECN2:ECN3 ECR2:ECR3 ECV2:ECV3 ECZ2:ECZ3 EDD2:EDD3 EDH2:EDH3 EDL2:EDL3 EDP2:EDP3 EDT2:EDT3 EDX2:EDX3 EEB2:EEB3 EEF2:EEF3 EEJ2:EEJ3 EEN2:EEN3 EER2:EER3 EEV2:EEV3 EEZ2:EEZ3 EFD2:EFD3 EFH2:EFH3 EFL2:EFL3 EFP2:EFP3 EFT2:EFT3 EFX2:EFX3 EGB2:EGB3 EGF2:EGF3 EGJ2:EGJ3 EGN2:EGN3 EGR2:EGR3 EGV2:EGV3 EGZ2:EGZ3 EHD2:EHD3 EHH2:EHH3 EHL2:EHL3 EHP2:EHP3 EHT2:EHT3 EHX2:EHX3 EIB2:EIB3 EIF2:EIF3 EIJ2:EIJ3 EIN2:EIN3 EIR2:EIR3 EIV2:EIV3 EIZ2:EIZ3 EJD2:EJD3 EJH2:EJH3 EJL2:EJL3 EJP2:EJP3 EJT2:EJT3 EJX2:EJX3 EKB2:EKB3 EKF2:EKF3 EKJ2:EKJ3 EKN2:EKN3 EKR2:EKR3 EKV2:EKV3 EKZ2:EKZ3 ELD2:ELD3 ELH2:ELH3 ELL2:ELL3 ELP2:ELP3 ELT2:ELT3 ELX2:ELX3 EMB2:EMB3 EMF2:EMF3 EMJ2:EMJ3 EMN2:EMN3 EMR2:EMR3 EMV2:EMV3 EMZ2:EMZ3 END2:END3 ENH2:ENH3 ENL2:ENL3 ENP2:ENP3 ENT2:ENT3 ENX2:ENX3 EOB2:EOB3 EOF2:EOF3 EOJ2:EOJ3 EON2:EON3 EOR2:EOR3 EOV2:EOV3 EOZ2:EOZ3 EPD2:EPD3 EPH2:EPH3 EPL2:EPL3 EPP2:EPP3 EPT2:EPT3 EPX2:EPX3 EQB2:EQB3 EQF2:EQF3 EQJ2:EQJ3 EQN2:EQN3 EQR2:EQR3 EQV2:EQV3 EQZ2:EQZ3 ERD2:ERD3 ERH2:ERH3 ERL2:ERL3 ERP2:ERP3 ERT2:ERT3 ERX2:ERX3 ESB2:ESB3 ESF2:ESF3 ESJ2:ESJ3 ESN2:ESN3 ESR2:ESR3 ESV2:ESV3 ESZ2:ESZ3 ETD2:ETD3 ETH2:ETH3 ETL2:ETL3 ETP2:ETP3 ETT2:ETT3 ETX2:ETX3 EUB2:EUB3 EUF2:EUF3 EUJ2:EUJ3 EUN2:EUN3 EUR2:EUR3 EUV2:EUV3 EUZ2:EUZ3 EVD2:EVD3 EVH2:EVH3 EVL2:EVL3 EVP2:EVP3 EVT2:EVT3 EVX2:EVX3 EWB2:EWB3 EWF2:EWF3 EWJ2:EWJ3 EWN2:EWN3 EWR2:EWR3 EWV2:EWV3 EWZ2:EWZ3 EXD2:EXD3 EXH2:EXH3 EXL2:EXL3 EXP2:EXP3 EXT2:EXT3 EXX2:EXX3 EYB2:EYB3 EYF2:EYF3 EYJ2:EYJ3 EYN2:EYN3 EYR2:EYR3 EYV2:EYV3 EYZ2:EYZ3 EZD2:EZD3 EZH2:EZH3 EZL2:EZL3 EZP2:EZP3 EZT2:EZT3 EZX2:EZX3 FAB2:FAB3 FAF2:FAF3 FAJ2:FAJ3 FAN2:FAN3 FAR2:FAR3 FAV2:FAV3 FAZ2:FAZ3 FBD2:FBD3 FBH2:FBH3 FBL2:FBL3 FBP2:FBP3 FBT2:FBT3 FBX2:FBX3 FCB2:FCB3 FCF2:FCF3 FCJ2:FCJ3 FCN2:FCN3 FCR2:FCR3 FCV2:FCV3 FCZ2:FCZ3 FDD2:FDD3 FDH2:FDH3 FDL2:FDL3 FDP2:FDP3 FDT2:FDT3 FDX2:FDX3 FEB2:FEB3 FEF2:FEF3 FEJ2:FEJ3 FEN2:FEN3 FER2:FER3 FEV2:FEV3 FEZ2:FEZ3 FFD2:FFD3 FFH2:FFH3 FFL2:FFL3 FFP2:FFP3 FFT2:FFT3 FFX2:FFX3 FGB2:FGB3 FGF2:FGF3 FGJ2:FGJ3 FGN2:FGN3 FGR2:FGR3 FGV2:FGV3 FGZ2:FGZ3 FHD2:FHD3 FHH2:FHH3 FHL2:FHL3 FHP2:FHP3 FHT2:FHT3 FHX2:FHX3 FIB2:FIB3 FIF2:FIF3 FIJ2:FIJ3 FIN2:FIN3 FIR2:FIR3 FIV2:FIV3 FIZ2:FIZ3 FJD2:FJD3 FJH2:FJH3 FJL2:FJL3 FJP2:FJP3 FJT2:FJT3 FJX2:FJX3 FKB2:FKB3 FKF2:FKF3 FKJ2:FKJ3 FKN2:FKN3 FKR2:FKR3 FKV2:FKV3 FKZ2:FKZ3 FLD2:FLD3 FLH2:FLH3 FLL2:FLL3 FLP2:FLP3 FLT2:FLT3 FLX2:FLX3 FMB2:FMB3 FMF2:FMF3 FMJ2:FMJ3 FMN2:FMN3 FMR2:FMR3 FMV2:FMV3 FMZ2:FMZ3 FND2:FND3 FNH2:FNH3 FNL2:FNL3 FNP2:FNP3 FNT2:FNT3 FNX2:FNX3 FOB2:FOB3 FOF2:FOF3 FOJ2:FOJ3 FON2:FON3 FOR2:FOR3 FOV2:FOV3 FOZ2:FOZ3 FPD2:FPD3 FPH2:FPH3 FPL2:FPL3 FPP2:FPP3 FPT2:FPT3 FPX2:FPX3 FQB2:FQB3 FQF2:FQF3 FQJ2:FQJ3 FQN2:FQN3 FQR2:FQR3 FQV2:FQV3 FQZ2:FQZ3 FRD2:FRD3 FRH2:FRH3 FRL2:FRL3 FRP2:FRP3 FRT2:FRT3 FRX2:FRX3 FSB2:FSB3 FSF2:FSF3 FSJ2:FSJ3 FSN2:FSN3 FSR2:FSR3 FSV2:FSV3 FSZ2:FSZ3 FTD2:FTD3 FTH2:FTH3 FTL2:FTL3 FTP2:FTP3 FTT2:FTT3 FTX2:FTX3 FUB2:FUB3 FUF2:FUF3 FUJ2:FUJ3 FUN2:FUN3 FUR2:FUR3 FUV2:FUV3 FUZ2:FUZ3 FVD2:FVD3 FVH2:FVH3 FVL2:FVL3 FVP2:FVP3 FVT2:FVT3 FVX2:FVX3 FWB2:FWB3 FWF2:FWF3 FWJ2:FWJ3 FWN2:FWN3 FWR2:FWR3 FWV2:FWV3 FWZ2:FWZ3 FXD2:FXD3 FXH2:FXH3 FXL2:FXL3 FXP2:FXP3 FXT2:FXT3 FXX2:FXX3 FYB2:FYB3 FYF2:FYF3 FYJ2:FYJ3 FYN2:FYN3 FYR2:FYR3 FYV2:FYV3 FYZ2:FYZ3 FZD2:FZD3 FZH2:FZH3 FZL2:FZL3 FZP2:FZP3 FZT2:FZT3 FZX2:FZX3 GAB2:GAB3 GAF2:GAF3 GAJ2:GAJ3 GAN2:GAN3 GAR2:GAR3 GAV2:GAV3 GAZ2:GAZ3 GBD2:GBD3 GBH2:GBH3 GBL2:GBL3 GBP2:GBP3 GBT2:GBT3 GBX2:GBX3 GCB2:GCB3 GCF2:GCF3 GCJ2:GCJ3 GCN2:GCN3 GCR2:GCR3 GCV2:GCV3 GCZ2:GCZ3 GDD2:GDD3 GDH2:GDH3 GDL2:GDL3 GDP2:GDP3 GDT2:GDT3 GDX2:GDX3 GEB2:GEB3 GEF2:GEF3 GEJ2:GEJ3 GEN2:GEN3 GER2:GER3 GEV2:GEV3 GEZ2:GEZ3 GFD2:GFD3 GFH2:GFH3 GFL2:GFL3 GFP2:GFP3 GFT2:GFT3 GFX2:GFX3 GGB2:GGB3 GGF2:GGF3 GGJ2:GGJ3 GGN2:GGN3 GGR2:GGR3 GGV2:GGV3 GGZ2:GGZ3 GHD2:GHD3 GHH2:GHH3 GHL2:GHL3 GHP2:GHP3 GHT2:GHT3 GHX2:GHX3 GIB2:GIB3 GIF2:GIF3 GIJ2:GIJ3 GIN2:GIN3 GIR2:GIR3 GIV2:GIV3 GIZ2:GIZ3 GJD2:GJD3 GJH2:GJH3 GJL2:GJL3 GJP2:GJP3 GJT2:GJT3 GJX2:GJX3 GKB2:GKB3 GKF2:GKF3 GKJ2:GKJ3 GKN2:GKN3 GKR2:GKR3 GKV2:GKV3 GKZ2:GKZ3 GLD2:GLD3 GLH2:GLH3 GLL2:GLL3 GLP2:GLP3 GLT2:GLT3 GLX2:GLX3 GMB2:GMB3 GMF2:GMF3 GMJ2:GMJ3 GMN2:GMN3 GMR2:GMR3 GMV2:GMV3 GMZ2:GMZ3 GND2:GND3 GNH2:GNH3 GNL2:GNL3 GNP2:GNP3 GNT2:GNT3 GNX2:GNX3 GOB2:GOB3 GOF2:GOF3 GOJ2:GOJ3 GON2:GON3 GOR2:GOR3 GOV2:GOV3 GOZ2:GOZ3 GPD2:GPD3 GPH2:GPH3 GPL2:GPL3 GPP2:GPP3 GPT2:GPT3 GPX2:GPX3 GQB2:GQB3 GQF2:GQF3 GQJ2:GQJ3 GQN2:GQN3 GQR2:GQR3 GQV2:GQV3 GQZ2:GQZ3 GRD2:GRD3 GRH2:GRH3 GRL2:GRL3 GRP2:GRP3 GRT2:GRT3 GRX2:GRX3 GSB2:GSB3 GSF2:GSF3 GSJ2:GSJ3 GSN2:GSN3 GSR2:GSR3 GSV2:GSV3 GSZ2:GSZ3 GTD2:GTD3 GTH2:GTH3 GTL2:GTL3 GTP2:GTP3 GTT2:GTT3 GTX2:GTX3 GUB2:GUB3 GUF2:GUF3 GUJ2:GUJ3 GUN2:GUN3 GUR2:GUR3 GUV2:GUV3 GUZ2:GUZ3 GVD2:GVD3 GVH2:GVH3 GVL2:GVL3 GVP2:GVP3 GVT2:GVT3 GVX2:GVX3 GWB2:GWB3 GWF2:GWF3 GWJ2:GWJ3 GWN2:GWN3 GWR2:GWR3 GWV2:GWV3 GWZ2:GWZ3 GXD2:GXD3 GXH2:GXH3 GXL2:GXL3 GXP2:GXP3 GXT2:GXT3 GXX2:GXX3 GYB2:GYB3 GYF2:GYF3 GYJ2:GYJ3 GYN2:GYN3 GYR2:GYR3 GYV2:GYV3 GYZ2:GYZ3 GZD2:GZD3 GZH2:GZH3 GZL2:GZL3 GZP2:GZP3 GZT2:GZT3 GZX2:GZX3 HAB2:HAB3 HAF2:HAF3 HAJ2:HAJ3 HAN2:HAN3 HAR2:HAR3 HAV2:HAV3 HAZ2:HAZ3 HBD2:HBD3 HBH2:HBH3 HBL2:HBL3 HBP2:HBP3 HBT2:HBT3 HBX2:HBX3 HCB2:HCB3 HCF2:HCF3 HCJ2:HCJ3 HCN2:HCN3 HCR2:HCR3 HCV2:HCV3 HCZ2:HCZ3 HDD2:HDD3 HDH2:HDH3 HDL2:HDL3 HDP2:HDP3 HDT2:HDT3 HDX2:HDX3 HEB2:HEB3 HEF2:HEF3 HEJ2:HEJ3 HEN2:HEN3 HER2:HER3 HEV2:HEV3 HEZ2:HEZ3 HFD2:HFD3 HFH2:HFH3 HFL2:HFL3 HFP2:HFP3 HFT2:HFT3 HFX2:HFX3 HGB2:HGB3 HGF2:HGF3 HGJ2:HGJ3 HGN2:HGN3 HGR2:HGR3 HGV2:HGV3 HGZ2:HGZ3 HHD2:HHD3 HHH2:HHH3 HHL2:HHL3 HHP2:HHP3 HHT2:HHT3 HHX2:HHX3 HIB2:HIB3 HIF2:HIF3 HIJ2:HIJ3 HIN2:HIN3 HIR2:HIR3 HIV2:HIV3 HIZ2:HIZ3 HJD2:HJD3 HJH2:HJH3 HJL2:HJL3 HJP2:HJP3 HJT2:HJT3 HJX2:HJX3 HKB2:HKB3 HKF2:HKF3 HKJ2:HKJ3 HKN2:HKN3 HKR2:HKR3 HKV2:HKV3 HKZ2:HKZ3 HLD2:HLD3 HLH2:HLH3 HLL2:HLL3 HLP2:HLP3 HLT2:HLT3 HLX2:HLX3 HMB2:HMB3 HMF2:HMF3 HMJ2:HMJ3 HMN2:HMN3 HMR2:HMR3 HMV2:HMV3 HMZ2:HMZ3 HND2:HND3 HNH2:HNH3 HNL2:HNL3 HNP2:HNP3 HNT2:HNT3 HNX2:HNX3 HOB2:HOB3 HOF2:HOF3 HOJ2:HOJ3 HON2:HON3 HOR2:HOR3 HOV2:HOV3 HOZ2:HOZ3 HPD2:HPD3 HPH2:HPH3 HPL2:HPL3 HPP2:HPP3 HPT2:HPT3 HPX2:HPX3 HQB2:HQB3 HQF2:HQF3 HQJ2:HQJ3 HQN2:HQN3 HQR2:HQR3 HQV2:HQV3 HQZ2:HQZ3 HRD2:HRD3 HRH2:HRH3 HRL2:HRL3 HRP2:HRP3 HRT2:HRT3 HRX2:HRX3 HSB2:HSB3 HSF2:HSF3 HSJ2:HSJ3 HSN2:HSN3 HSR2:HSR3 HSV2:HSV3 HSZ2:HSZ3 HTD2:HTD3 HTH2:HTH3 HTL2:HTL3 HTP2:HTP3 HTT2:HTT3 HTX2:HTX3 HUB2:HUB3 HUF2:HUF3 HUJ2:HUJ3 HUN2:HUN3 HUR2:HUR3 HUV2:HUV3 HUZ2:HUZ3 HVD2:HVD3 HVH2:HVH3 HVL2:HVL3 HVP2:HVP3 HVT2:HVT3 HVX2:HVX3 HWB2:HWB3 HWF2:HWF3 HWJ2:HWJ3 HWN2:HWN3 HWR2:HWR3 HWV2:HWV3 HWZ2:HWZ3 HXD2:HXD3 HXH2:HXH3 HXL2:HXL3 HXP2:HXP3 HXT2:HXT3 HXX2:HXX3 HYB2:HYB3 HYF2:HYF3 HYJ2:HYJ3 HYN2:HYN3 HYR2:HYR3 HYV2:HYV3 HYZ2:HYZ3 HZD2:HZD3 HZH2:HZH3 HZL2:HZL3 HZP2:HZP3 HZT2:HZT3 HZX2:HZX3 IAB2:IAB3 IAF2:IAF3 IAJ2:IAJ3 IAN2:IAN3 IAR2:IAR3 IAV2:IAV3 IAZ2:IAZ3 IBD2:IBD3 IBH2:IBH3 IBL2:IBL3 IBP2:IBP3 IBT2:IBT3 IBX2:IBX3 ICB2:ICB3 ICF2:ICF3 ICJ2:ICJ3 ICN2:ICN3 ICR2:ICR3 ICV2:ICV3 ICZ2:ICZ3 IDD2:IDD3 IDH2:IDH3 IDL2:IDL3 IDP2:IDP3 IDT2:IDT3 IDX2:IDX3 IEB2:IEB3 IEF2:IEF3 IEJ2:IEJ3 IEN2:IEN3 IER2:IER3 IEV2:IEV3 IEZ2:IEZ3 IFD2:IFD3 IFH2:IFH3 IFL2:IFL3 IFP2:IFP3 IFT2:IFT3 IFX2:IFX3 IGB2:IGB3 IGF2:IGF3 IGJ2:IGJ3 IGN2:IGN3 IGR2:IGR3 IGV2:IGV3 IGZ2:IGZ3 IHD2:IHD3 IHH2:IHH3 IHL2:IHL3 IHP2:IHP3 IHT2:IHT3 IHX2:IHX3 IIB2:IIB3 IIF2:IIF3 IIJ2:IIJ3 IIN2:IIN3 IIR2:IIR3 IIV2:IIV3 IIZ2:IIZ3 IJD2:IJD3 IJH2:IJH3 IJL2:IJL3 IJP2:IJP3 IJT2:IJT3 IJX2:IJX3 IKB2:IKB3 IKF2:IKF3 IKJ2:IKJ3 IKN2:IKN3 IKR2:IKR3 IKV2:IKV3 IKZ2:IKZ3 ILD2:ILD3 ILH2:ILH3 ILL2:ILL3 ILP2:ILP3 ILT2:ILT3 ILX2:ILX3 IMB2:IMB3 IMF2:IMF3 IMJ2:IMJ3 IMN2:IMN3 IMR2:IMR3 IMV2:IMV3 IMZ2:IMZ3 IND2:IND3 INH2:INH3 INL2:INL3 INP2:INP3 INT2:INT3 INX2:INX3 IOB2:IOB3 IOF2:IOF3 IOJ2:IOJ3 ION2:ION3 IOR2:IOR3 IOV2:IOV3 IOZ2:IOZ3 IPD2:IPD3 IPH2:IPH3 IPL2:IPL3 IPP2:IPP3 IPT2:IPT3 IPX2:IPX3 IQB2:IQB3 IQF2:IQF3 IQJ2:IQJ3 IQN2:IQN3 IQR2:IQR3 IQV2:IQV3 IQZ2:IQZ3 IRD2:IRD3 IRH2:IRH3 IRL2:IRL3 IRP2:IRP3 IRT2:IRT3 IRX2:IRX3 ISB2:ISB3 ISF2:ISF3 ISJ2:ISJ3 ISN2:ISN3 ISR2:ISR3 ISV2:ISV3 ISZ2:ISZ3 ITD2:ITD3 ITH2:ITH3 ITL2:ITL3 ITP2:ITP3 ITT2:ITT3 ITX2:ITX3 IUB2:IUB3 IUF2:IUF3 IUJ2:IUJ3 IUN2:IUN3 IUR2:IUR3 IUV2:IUV3 IUZ2:IUZ3 IVD2:IVD3 IVH2:IVH3 IVL2:IVL3 IVP2:IVP3 IVT2:IVT3 IVX2:IVX3 IWB2:IWB3 IWF2:IWF3 IWJ2:IWJ3 IWN2:IWN3 IWR2:IWR3 IWV2:IWV3 IWZ2:IWZ3 IXD2:IXD3 IXH2:IXH3 IXL2:IXL3 IXP2:IXP3 IXT2:IXT3 IXX2:IXX3 IYB2:IYB3 IYF2:IYF3 IYJ2:IYJ3 IYN2:IYN3 IYR2:IYR3 IYV2:IYV3 IYZ2:IYZ3 IZD2:IZD3 IZH2:IZH3 IZL2:IZL3 IZP2:IZP3 IZT2:IZT3 IZX2:IZX3 JAB2:JAB3 JAF2:JAF3 JAJ2:JAJ3 JAN2:JAN3 JAR2:JAR3 JAV2:JAV3 JAZ2:JAZ3 JBD2:JBD3 JBH2:JBH3 JBL2:JBL3 JBP2:JBP3 JBT2:JBT3 JBX2:JBX3 JCB2:JCB3 JCF2:JCF3 JCJ2:JCJ3 JCN2:JCN3 JCR2:JCR3 JCV2:JCV3 JCZ2:JCZ3 JDD2:JDD3 JDH2:JDH3 JDL2:JDL3 JDP2:JDP3 JDT2:JDT3 JDX2:JDX3 JEB2:JEB3 JEF2:JEF3 JEJ2:JEJ3 JEN2:JEN3 JER2:JER3 JEV2:JEV3 JEZ2:JEZ3 JFD2:JFD3 JFH2:JFH3 JFL2:JFL3 JFP2:JFP3 JFT2:JFT3 JFX2:JFX3 JGB2:JGB3 JGF2:JGF3 JGJ2:JGJ3 JGN2:JGN3 JGR2:JGR3 JGV2:JGV3 JGZ2:JGZ3 JHD2:JHD3 JHH2:JHH3 JHL2:JHL3 JHP2:JHP3 JHT2:JHT3 JHX2:JHX3 JIB2:JIB3 JIF2:JIF3 JIJ2:JIJ3 JIN2:JIN3 JIR2:JIR3 JIV2:JIV3 JIZ2:JIZ3 JJD2:JJD3 JJH2:JJH3 JJL2:JJL3 JJP2:JJP3 JJT2:JJT3 JJX2:JJX3 JKB2:JKB3 JKF2:JKF3 JKJ2:JKJ3 JKN2:JKN3 JKR2:JKR3 JKV2:JKV3 JKZ2:JKZ3 JLD2:JLD3 JLH2:JLH3 JLL2:JLL3 JLP2:JLP3 JLT2:JLT3 JLX2:JLX3 JMB2:JMB3 JMF2:JMF3 JMJ2:JMJ3 JMN2:JMN3 JMR2:JMR3 JMV2:JMV3 JMZ2:JMZ3 JND2:JND3 JNH2:JNH3 JNL2:JNL3 JNP2:JNP3 JNT2:JNT3 JNX2:JNX3 JOB2:JOB3 JOF2:JOF3 JOJ2:JOJ3 JON2:JON3 JOR2:JOR3 JOV2:JOV3 JOZ2:JOZ3 JPD2:JPD3 JPH2:JPH3 JPL2:JPL3 JPP2:JPP3 JPT2:JPT3 JPX2:JPX3 JQB2:JQB3 JQF2:JQF3 JQJ2:JQJ3 JQN2:JQN3 JQR2:JQR3 JQV2:JQV3 JQZ2:JQZ3 JRD2:JRD3 JRH2:JRH3 JRL2:JRL3 JRP2:JRP3 JRT2:JRT3 JRX2:JRX3 JSB2:JSB3 JSF2:JSF3 JSJ2:JSJ3 JSN2:JSN3 JSR2:JSR3 JSV2:JSV3 JSZ2:JSZ3 JTD2:JTD3 JTH2:JTH3 JTL2:JTL3 JTP2:JTP3 JTT2:JTT3 JTX2:JTX3 JUB2:JUB3 JUF2:JUF3 JUJ2:JUJ3 JUN2:JUN3 JUR2:JUR3 JUV2:JUV3 JUZ2:JUZ3 JVD2:JVD3 JVH2:JVH3 JVL2:JVL3 JVP2:JVP3 JVT2:JVT3 JVX2:JVX3 JWB2:JWB3 JWF2:JWF3 JWJ2:JWJ3 JWN2:JWN3 JWR2:JWR3 JWV2:JWV3 JWZ2:JWZ3 JXD2:JXD3 JXH2:JXH3 JXL2:JXL3 JXP2:JXP3 JXT2:JXT3 JXX2:JXX3 JYB2:JYB3 JYF2:JYF3 JYJ2:JYJ3 JYN2:JYN3 JYR2:JYR3 JYV2:JYV3 JYZ2:JYZ3 JZD2:JZD3 JZH2:JZH3 JZL2:JZL3 JZP2:JZP3 JZT2:JZT3 JZX2:JZX3 KAB2:KAB3 KAF2:KAF3 KAJ2:KAJ3 KAN2:KAN3 KAR2:KAR3 KAV2:KAV3 KAZ2:KAZ3 KBD2:KBD3 KBH2:KBH3 KBL2:KBL3 KBP2:KBP3 KBT2:KBT3 KBX2:KBX3 KCB2:KCB3 KCF2:KCF3 KCJ2:KCJ3 KCN2:KCN3 KCR2:KCR3 KCV2:KCV3 KCZ2:KCZ3 KDD2:KDD3 KDH2:KDH3 KDL2:KDL3 KDP2:KDP3 KDT2:KDT3 KDX2:KDX3 KEB2:KEB3 KEF2:KEF3 KEJ2:KEJ3 KEN2:KEN3 KER2:KER3 KEV2:KEV3 KEZ2:KEZ3 KFD2:KFD3 KFH2:KFH3 KFL2:KFL3 KFP2:KFP3 KFT2:KFT3 KFX2:KFX3 KGB2:KGB3 KGF2:KGF3 KGJ2:KGJ3 KGN2:KGN3 KGR2:KGR3 KGV2:KGV3 KGZ2:KGZ3 KHD2:KHD3 KHH2:KHH3 KHL2:KHL3 KHP2:KHP3 KHT2:KHT3 KHX2:KHX3 KIB2:KIB3 KIF2:KIF3 KIJ2:KIJ3 KIN2:KIN3 KIR2:KIR3 KIV2:KIV3 KIZ2:KIZ3 KJD2:KJD3 KJH2:KJH3 KJL2:KJL3 KJP2:KJP3 KJT2:KJT3 KJX2:KJX3 KKB2:KKB3 KKF2:KKF3 KKJ2:KKJ3 KKN2:KKN3 KKR2:KKR3 KKV2:KKV3 KKZ2:KKZ3 KLD2:KLD3 KLH2:KLH3 KLL2:KLL3 KLP2:KLP3 KLT2:KLT3 KLX2:KLX3 KMB2:KMB3 KMF2:KMF3 KMJ2:KMJ3 KMN2:KMN3 KMR2:KMR3 KMV2:KMV3 KMZ2:KMZ3 KND2:KND3 KNH2:KNH3 KNL2:KNL3 KNP2:KNP3 KNT2:KNT3 KNX2:KNX3 KOB2:KOB3 KOF2:KOF3 KOJ2:KOJ3 KON2:KON3 KOR2:KOR3 KOV2:KOV3 KOZ2:KOZ3 KPD2:KPD3 KPH2:KPH3 KPL2:KPL3 KPP2:KPP3 KPT2:KPT3 KPX2:KPX3 KQB2:KQB3 KQF2:KQF3 KQJ2:KQJ3 KQN2:KQN3 KQR2:KQR3 KQV2:KQV3 KQZ2:KQZ3 KRD2:KRD3 KRH2:KRH3 KRL2:KRL3 KRP2:KRP3 KRT2:KRT3 KRX2:KRX3 KSB2:KSB3 KSF2:KSF3 KSJ2:KSJ3 KSN2:KSN3 KSR2:KSR3 KSV2:KSV3 KSZ2:KSZ3 KTD2:KTD3 KTH2:KTH3 KTL2:KTL3 KTP2:KTP3 KTT2:KTT3 KTX2:KTX3 KUB2:KUB3 KUF2:KUF3 KUJ2:KUJ3 KUN2:KUN3 KUR2:KUR3 KUV2:KUV3 KUZ2:KUZ3 KVD2:KVD3 KVH2:KVH3 KVL2:KVL3 KVP2:KVP3 KVT2:KVT3 KVX2:KVX3 KWB2:KWB3 KWF2:KWF3 KWJ2:KWJ3 KWN2:KWN3 KWR2:KWR3 KWV2:KWV3 KWZ2:KWZ3 KXD2:KXD3 KXH2:KXH3 KXL2:KXL3 KXP2:KXP3 KXT2:KXT3 KXX2:KXX3 KYB2:KYB3 KYF2:KYF3 KYJ2:KYJ3 KYN2:KYN3 KYR2:KYR3 KYV2:KYV3 KYZ2:KYZ3 KZD2:KZD3 KZH2:KZH3 KZL2:KZL3 KZP2:KZP3 KZT2:KZT3 KZX2:KZX3 LAB2:LAB3 LAF2:LAF3 LAJ2:LAJ3 LAN2:LAN3 LAR2:LAR3 LAV2:LAV3 LAZ2:LAZ3 LBD2:LBD3 LBH2:LBH3 LBL2:LBL3 LBP2:LBP3 LBT2:LBT3 LBX2:LBX3 LCB2:LCB3 LCF2:LCF3 LCJ2:LCJ3 LCN2:LCN3 LCR2:LCR3 LCV2:LCV3 LCZ2:LCZ3 LDD2:LDD3 LDH2:LDH3 LDL2:LDL3 LDP2:LDP3 LDT2:LDT3 LDX2:LDX3 LEB2:LEB3 LEF2:LEF3 LEJ2:LEJ3 LEN2:LEN3 LER2:LER3 LEV2:LEV3 LEZ2:LEZ3 LFD2:LFD3 LFH2:LFH3 LFL2:LFL3 LFP2:LFP3 LFT2:LFT3 LFX2:LFX3 LGB2:LGB3 LGF2:LGF3 LGJ2:LGJ3 LGN2:LGN3 LGR2:LGR3 LGV2:LGV3 LGZ2:LGZ3 LHD2:LHD3 LHH2:LHH3 LHL2:LHL3 LHP2:LHP3 LHT2:LHT3 LHX2:LHX3 LIB2:LIB3 LIF2:LIF3 LIJ2:LIJ3 LIN2:LIN3 LIR2:LIR3 LIV2:LIV3 LIZ2:LIZ3 LJD2:LJD3 LJH2:LJH3 LJL2:LJL3 LJP2:LJP3 LJT2:LJT3 LJX2:LJX3 LKB2:LKB3 LKF2:LKF3 LKJ2:LKJ3 LKN2:LKN3 LKR2:LKR3 LKV2:LKV3 LKZ2:LKZ3 LLD2:LLD3 LLH2:LLH3 LLL2:LLL3 LLP2:LLP3 LLT2:LLT3 LLX2:LLX3 LMB2:LMB3 LMF2:LMF3 LMJ2:LMJ3 LMN2:LMN3 LMR2:LMR3 LMV2:LMV3 LMZ2:LMZ3 LND2:LND3 LNH2:LNH3 LNL2:LNL3 LNP2:LNP3 LNT2:LNT3 LNX2:LNX3 LOB2:LOB3 LOF2:LOF3 LOJ2:LOJ3 LON2:LON3 LOR2:LOR3 LOV2:LOV3 LOZ2:LOZ3 LPD2:LPD3 LPH2:LPH3 LPL2:LPL3 LPP2:LPP3 LPT2:LPT3 LPX2:LPX3 LQB2:LQB3 LQF2:LQF3 LQJ2:LQJ3 LQN2:LQN3 LQR2:LQR3 LQV2:LQV3 LQZ2:LQZ3 LRD2:LRD3 LRH2:LRH3 LRL2:LRL3 LRP2:LRP3 LRT2:LRT3 LRX2:LRX3 LSB2:LSB3 LSF2:LSF3 LSJ2:LSJ3 LSN2:LSN3 LSR2:LSR3 LSV2:LSV3 LSZ2:LSZ3 LTD2:LTD3 LTH2:LTH3 LTL2:LTL3 LTP2:LTP3 LTT2:LTT3 LTX2:LTX3 LUB2:LUB3 LUF2:LUF3 LUJ2:LUJ3 LUN2:LUN3 LUR2:LUR3 LUV2:LUV3 LUZ2:LUZ3 LVD2:LVD3 LVH2:LVH3 LVL2:LVL3 LVP2:LVP3 LVT2:LVT3 LVX2:LVX3 LWB2:LWB3 LWF2:LWF3 LWJ2:LWJ3 LWN2:LWN3 LWR2:LWR3 LWV2:LWV3 LWZ2:LWZ3 LXD2:LXD3 LXH2:LXH3 LXL2:LXL3 LXP2:LXP3 LXT2:LXT3 LXX2:LXX3 LYB2:LYB3 LYF2:LYF3 LYJ2:LYJ3 LYN2:LYN3 LYR2:LYR3 LYV2:LYV3 LYZ2:LYZ3 LZD2:LZD3 LZH2:LZH3 LZL2:LZL3 LZP2:LZP3 LZT2:LZT3 LZX2:LZX3 MAB2:MAB3 MAF2:MAF3 MAJ2:MAJ3 MAN2:MAN3 MAR2:MAR3 MAV2:MAV3 MAZ2:MAZ3 MBD2:MBD3 MBH2:MBH3 MBL2:MBL3 MBP2:MBP3 MBT2:MBT3 MBX2:MBX3 MCB2:MCB3 MCF2:MCF3 MCJ2:MCJ3 MCN2:MCN3 MCR2:MCR3 MCV2:MCV3 MCZ2:MCZ3 MDD2:MDD3 MDH2:MDH3 MDL2:MDL3 MDP2:MDP3 MDT2:MDT3 MDX2:MDX3 MEB2:MEB3 MEF2:MEF3 MEJ2:MEJ3 MEN2:MEN3 MER2:MER3 MEV2:MEV3 MEZ2:MEZ3 MFD2:MFD3 MFH2:MFH3 MFL2:MFL3 MFP2:MFP3 MFT2:MFT3 MFX2:MFX3 MGB2:MGB3 MGF2:MGF3 MGJ2:MGJ3 MGN2:MGN3 MGR2:MGR3 MGV2:MGV3 MGZ2:MGZ3 MHD2:MHD3 MHH2:MHH3 MHL2:MHL3 MHP2:MHP3 MHT2:MHT3 MHX2:MHX3 MIB2:MIB3 MIF2:MIF3 MIJ2:MIJ3 MIN2:MIN3 MIR2:MIR3 MIV2:MIV3 MIZ2:MIZ3 MJD2:MJD3 MJH2:MJH3 MJL2:MJL3 MJP2:MJP3 MJT2:MJT3 MJX2:MJX3 MKB2:MKB3 MKF2:MKF3 MKJ2:MKJ3 MKN2:MKN3 MKR2:MKR3 MKV2:MKV3 MKZ2:MKZ3 MLD2:MLD3 MLH2:MLH3 MLL2:MLL3 MLP2:MLP3 MLT2:MLT3 MLX2:MLX3 MMB2:MMB3 MMF2:MMF3 MMJ2:MMJ3 MMN2:MMN3 MMR2:MMR3 MMV2:MMV3 MMZ2:MMZ3 MND2:MND3 MNH2:MNH3 MNL2:MNL3 MNP2:MNP3 MNT2:MNT3 MNX2:MNX3 MOB2:MOB3 MOF2:MOF3 MOJ2:MOJ3 MON2:MON3 MOR2:MOR3 MOV2:MOV3 MOZ2:MOZ3 MPD2:MPD3 MPH2:MPH3 MPL2:MPL3 MPP2:MPP3 MPT2:MPT3 MPX2:MPX3 MQB2:MQB3 MQF2:MQF3 MQJ2:MQJ3 MQN2:MQN3 MQR2:MQR3 MQV2:MQV3 MQZ2:MQZ3 MRD2:MRD3 MRH2:MRH3 MRL2:MRL3 MRP2:MRP3 MRT2:MRT3 MRX2:MRX3 MSB2:MSB3 MSF2:MSF3 MSJ2:MSJ3 MSN2:MSN3 MSR2:MSR3 MSV2:MSV3 MSZ2:MSZ3 MTD2:MTD3 MTH2:MTH3 MTL2:MTL3 MTP2:MTP3 MTT2:MTT3 MTX2:MTX3 MUB2:MUB3 MUF2:MUF3 MUJ2:MUJ3 MUN2:MUN3 MUR2:MUR3 MUV2:MUV3 MUZ2:MUZ3 MVD2:MVD3 MVH2:MVH3 MVL2:MVL3 MVP2:MVP3 MVT2:MVT3 MVX2:MVX3 MWB2:MWB3 MWF2:MWF3 MWJ2:MWJ3 MWN2:MWN3 MWR2:MWR3 MWV2:MWV3 MWZ2:MWZ3 MXD2:MXD3 MXH2:MXH3 MXL2:MXL3 MXP2:MXP3 MXT2:MXT3 MXX2:MXX3 MYB2:MYB3 MYF2:MYF3 MYJ2:MYJ3 MYN2:MYN3 MYR2:MYR3 MYV2:MYV3 MYZ2:MYZ3 MZD2:MZD3 MZH2:MZH3 MZL2:MZL3 MZP2:MZP3 MZT2:MZT3 MZX2:MZX3 NAB2:NAB3 NAF2:NAF3 NAJ2:NAJ3 NAN2:NAN3 NAR2:NAR3 NAV2:NAV3 NAZ2:NAZ3 NBD2:NBD3 NBH2:NBH3 NBL2:NBL3 NBP2:NBP3 NBT2:NBT3 NBX2:NBX3 NCB2:NCB3 NCF2:NCF3 NCJ2:NCJ3 NCN2:NCN3 NCR2:NCR3 NCV2:NCV3 NCZ2:NCZ3 NDD2:NDD3 NDH2:NDH3 NDL2:NDL3 NDP2:NDP3 NDT2:NDT3 NDX2:NDX3 NEB2:NEB3 NEF2:NEF3 NEJ2:NEJ3 NEN2:NEN3 NER2:NER3 NEV2:NEV3 NEZ2:NEZ3 NFD2:NFD3 NFH2:NFH3 NFL2:NFL3 NFP2:NFP3 NFT2:NFT3 NFX2:NFX3 NGB2:NGB3 NGF2:NGF3 NGJ2:NGJ3 NGN2:NGN3 NGR2:NGR3 NGV2:NGV3 NGZ2:NGZ3 NHD2:NHD3 NHH2:NHH3 NHL2:NHL3 NHP2:NHP3 NHT2:NHT3 NHX2:NHX3 NIB2:NIB3 NIF2:NIF3 NIJ2:NIJ3 NIN2:NIN3 NIR2:NIR3 NIV2:NIV3 NIZ2:NIZ3 NJD2:NJD3 NJH2:NJH3 NJL2:NJL3 NJP2:NJP3 NJT2:NJT3 NJX2:NJX3 NKB2:NKB3 NKF2:NKF3 NKJ2:NKJ3 NKN2:NKN3 NKR2:NKR3 NKV2:NKV3 NKZ2:NKZ3 NLD2:NLD3 NLH2:NLH3 NLL2:NLL3 NLP2:NLP3 NLT2:NLT3 NLX2:NLX3 NMB2:NMB3 NMF2:NMF3 NMJ2:NMJ3 NMN2:NMN3 NMR2:NMR3 NMV2:NMV3 NMZ2:NMZ3 NND2:NND3 NNH2:NNH3 NNL2:NNL3 NNP2:NNP3 NNT2:NNT3 NNX2:NNX3 NOB2:NOB3 NOF2:NOF3 NOJ2:NOJ3 NON2:NON3 NOR2:NOR3 NOV2:NOV3 NOZ2:NOZ3 NPD2:NPD3 NPH2:NPH3 NPL2:NPL3 NPP2:NPP3 NPT2:NPT3 NPX2:NPX3 NQB2:NQB3 NQF2:NQF3 NQJ2:NQJ3 NQN2:NQN3 NQR2:NQR3 NQV2:NQV3 NQZ2:NQZ3 NRD2:NRD3 NRH2:NRH3 NRL2:NRL3 NRP2:NRP3 NRT2:NRT3 NRX2:NRX3 NSB2:NSB3 NSF2:NSF3 NSJ2:NSJ3 NSN2:NSN3 NSR2:NSR3 NSV2:NSV3 NSZ2:NSZ3 NTD2:NTD3 NTH2:NTH3 NTL2:NTL3 NTP2:NTP3 NTT2:NTT3 NTX2:NTX3 NUB2:NUB3 NUF2:NUF3 NUJ2:NUJ3 NUN2:NUN3 NUR2:NUR3 NUV2:NUV3 NUZ2:NUZ3 NVD2:NVD3 NVH2:NVH3 NVL2:NVL3 NVP2:NVP3 NVT2:NVT3 NVX2:NVX3 NWB2:NWB3 NWF2:NWF3 NWJ2:NWJ3 NWN2:NWN3 NWR2:NWR3 NWV2:NWV3 NWZ2:NWZ3 NXD2:NXD3 NXH2:NXH3 NXL2:NXL3 NXP2:NXP3 NXT2:NXT3 NXX2:NXX3 NYB2:NYB3 NYF2:NYF3 NYJ2:NYJ3 NYN2:NYN3 NYR2:NYR3 NYV2:NYV3 NYZ2:NYZ3 NZD2:NZD3 NZH2:NZH3 NZL2:NZL3 NZP2:NZP3 NZT2:NZT3 NZX2:NZX3 OAB2:OAB3 OAF2:OAF3 OAJ2:OAJ3 OAN2:OAN3 OAR2:OAR3 OAV2:OAV3 OAZ2:OAZ3 OBD2:OBD3 OBH2:OBH3 OBL2:OBL3 OBP2:OBP3 OBT2:OBT3 OBX2:OBX3 OCB2:OCB3 OCF2:OCF3 OCJ2:OCJ3 OCN2:OCN3 OCR2:OCR3 OCV2:OCV3 OCZ2:OCZ3 ODD2:ODD3 ODH2:ODH3 ODL2:ODL3 ODP2:ODP3 ODT2:ODT3 ODX2:ODX3 OEB2:OEB3 OEF2:OEF3 OEJ2:OEJ3 OEN2:OEN3 OER2:OER3 OEV2:OEV3 OEZ2:OEZ3 OFD2:OFD3 OFH2:OFH3 OFL2:OFL3 OFP2:OFP3 OFT2:OFT3 OFX2:OFX3 OGB2:OGB3 OGF2:OGF3 OGJ2:OGJ3 OGN2:OGN3 OGR2:OGR3 OGV2:OGV3 OGZ2:OGZ3 OHD2:OHD3 OHH2:OHH3 OHL2:OHL3 OHP2:OHP3 OHT2:OHT3 OHX2:OHX3 OIB2:OIB3 OIF2:OIF3 OIJ2:OIJ3 OIN2:OIN3 OIR2:OIR3 OIV2:OIV3 OIZ2:OIZ3 OJD2:OJD3 OJH2:OJH3 OJL2:OJL3 OJP2:OJP3 OJT2:OJT3 OJX2:OJX3 OKB2:OKB3 OKF2:OKF3 OKJ2:OKJ3 OKN2:OKN3 OKR2:OKR3 OKV2:OKV3 OKZ2:OKZ3 OLD2:OLD3 OLH2:OLH3 OLL2:OLL3 OLP2:OLP3 OLT2:OLT3 OLX2:OLX3 OMB2:OMB3 OMF2:OMF3 OMJ2:OMJ3 OMN2:OMN3 OMR2:OMR3 OMV2:OMV3 OMZ2:OMZ3 OND2:OND3 ONH2:ONH3 ONL2:ONL3 ONP2:ONP3 ONT2:ONT3 ONX2:ONX3 OOB2:OOB3 OOF2:OOF3 OOJ2:OOJ3 OON2:OON3 OOR2:OOR3 OOV2:OOV3 OOZ2:OOZ3 OPD2:OPD3 OPH2:OPH3 OPL2:OPL3 OPP2:OPP3 OPT2:OPT3 OPX2:OPX3 OQB2:OQB3 OQF2:OQF3 OQJ2:OQJ3 OQN2:OQN3 OQR2:OQR3 OQV2:OQV3 OQZ2:OQZ3 ORD2:ORD3 ORH2:ORH3 ORL2:ORL3 ORP2:ORP3 ORT2:ORT3 ORX2:ORX3 OSB2:OSB3 OSF2:OSF3 OSJ2:OSJ3 OSN2:OSN3 OSR2:OSR3 OSV2:OSV3 OSZ2:OSZ3 OTD2:OTD3 OTH2:OTH3 OTL2:OTL3 OTP2:OTP3 OTT2:OTT3 OTX2:OTX3 OUB2:OUB3 OUF2:OUF3 OUJ2:OUJ3 OUN2:OUN3 OUR2:OUR3 OUV2:OUV3 OUZ2:OUZ3 OVD2:OVD3 OVH2:OVH3 OVL2:OVL3 OVP2:OVP3 OVT2:OVT3 OVX2:OVX3 OWB2:OWB3 OWF2:OWF3 OWJ2:OWJ3 OWN2:OWN3 OWR2:OWR3 OWV2:OWV3 OWZ2:OWZ3 OXD2:OXD3 OXH2:OXH3 OXL2:OXL3 OXP2:OXP3 OXT2:OXT3 OXX2:OXX3 OYB2:OYB3 OYF2:OYF3 OYJ2:OYJ3 OYN2:OYN3 OYR2:OYR3 OYV2:OYV3 OYZ2:OYZ3 OZD2:OZD3 OZH2:OZH3 OZL2:OZL3 OZP2:OZP3 OZT2:OZT3 OZX2:OZX3 PAB2:PAB3 PAF2:PAF3 PAJ2:PAJ3 PAN2:PAN3 PAR2:PAR3 PAV2:PAV3 PAZ2:PAZ3 PBD2:PBD3 PBH2:PBH3 PBL2:PBL3 PBP2:PBP3 PBT2:PBT3 PBX2:PBX3 PCB2:PCB3 PCF2:PCF3 PCJ2:PCJ3 PCN2:PCN3 PCR2:PCR3 PCV2:PCV3 PCZ2:PCZ3 PDD2:PDD3 PDH2:PDH3 PDL2:PDL3 PDP2:PDP3 PDT2:PDT3 PDX2:PDX3 PEB2:PEB3 PEF2:PEF3 PEJ2:PEJ3 PEN2:PEN3 PER2:PER3 PEV2:PEV3 PEZ2:PEZ3 PFD2:PFD3 PFH2:PFH3 PFL2:PFL3 PFP2:PFP3 PFT2:PFT3 PFX2:PFX3 PGB2:PGB3 PGF2:PGF3 PGJ2:PGJ3 PGN2:PGN3 PGR2:PGR3 PGV2:PGV3 PGZ2:PGZ3 PHD2:PHD3 PHH2:PHH3 PHL2:PHL3 PHP2:PHP3 PHT2:PHT3 PHX2:PHX3 PIB2:PIB3 PIF2:PIF3 PIJ2:PIJ3 PIN2:PIN3 PIR2:PIR3 PIV2:PIV3 PIZ2:PIZ3 PJD2:PJD3 PJH2:PJH3 PJL2:PJL3 PJP2:PJP3 PJT2:PJT3 PJX2:PJX3 PKB2:PKB3 PKF2:PKF3 PKJ2:PKJ3 PKN2:PKN3 PKR2:PKR3 PKV2:PKV3 PKZ2:PKZ3 PLD2:PLD3 PLH2:PLH3 PLL2:PLL3 PLP2:PLP3 PLT2:PLT3 PLX2:PLX3 PMB2:PMB3 PMF2:PMF3 PMJ2:PMJ3 PMN2:PMN3 PMR2:PMR3 PMV2:PMV3 PMZ2:PMZ3 PND2:PND3 PNH2:PNH3 PNL2:PNL3 PNP2:PNP3 PNT2:PNT3 PNX2:PNX3 POB2:POB3 POF2:POF3 POJ2:POJ3 PON2:PON3 POR2:POR3 POV2:POV3 POZ2:POZ3 PPD2:PPD3 PPH2:PPH3 PPL2:PPL3 PPP2:PPP3 PPT2:PPT3 PPX2:PPX3 PQB2:PQB3 PQF2:PQF3 PQJ2:PQJ3 PQN2:PQN3 PQR2:PQR3 PQV2:PQV3 PQZ2:PQZ3 PRD2:PRD3 PRH2:PRH3 PRL2:PRL3 PRP2:PRP3 PRT2:PRT3 PRX2:PRX3 PSB2:PSB3 PSF2:PSF3 PSJ2:PSJ3 PSN2:PSN3 PSR2:PSR3 PSV2:PSV3 PSZ2:PSZ3 PTD2:PTD3 PTH2:PTH3 PTL2:PTL3 PTP2:PTP3 PTT2:PTT3 PTX2:PTX3 PUB2:PUB3 PUF2:PUF3 PUJ2:PUJ3 PUN2:PUN3 PUR2:PUR3 PUV2:PUV3 PUZ2:PUZ3 PVD2:PVD3 PVH2:PVH3 PVL2:PVL3 PVP2:PVP3 PVT2:PVT3 PVX2:PVX3 PWB2:PWB3 PWF2:PWF3 PWJ2:PWJ3 PWN2:PWN3 PWR2:PWR3 PWV2:PWV3 PWZ2:PWZ3 PXD2:PXD3 PXH2:PXH3 PXL2:PXL3 PXP2:PXP3 PXT2:PXT3 PXX2:PXX3 PYB2:PYB3 PYF2:PYF3 PYJ2:PYJ3 PYN2:PYN3 PYR2:PYR3 PYV2:PYV3 PYZ2:PYZ3 PZD2:PZD3 PZH2:PZH3 PZL2:PZL3 PZP2:PZP3 PZT2:PZT3 PZX2:PZX3 QAB2:QAB3 QAF2:QAF3 QAJ2:QAJ3 QAN2:QAN3 QAR2:QAR3 QAV2:QAV3 QAZ2:QAZ3 QBD2:QBD3 QBH2:QBH3 QBL2:QBL3 QBP2:QBP3 QBT2:QBT3 QBX2:QBX3 QCB2:QCB3 QCF2:QCF3 QCJ2:QCJ3 QCN2:QCN3 QCR2:QCR3 QCV2:QCV3 QCZ2:QCZ3 QDD2:QDD3 QDH2:QDH3 QDL2:QDL3 QDP2:QDP3 QDT2:QDT3 QDX2:QDX3 QEB2:QEB3 QEF2:QEF3 QEJ2:QEJ3 QEN2:QEN3 QER2:QER3 QEV2:QEV3 QEZ2:QEZ3 QFD2:QFD3 QFH2:QFH3 QFL2:QFL3 QFP2:QFP3 QFT2:QFT3 QFX2:QFX3 QGB2:QGB3 QGF2:QGF3 QGJ2:QGJ3 QGN2:QGN3 QGR2:QGR3 QGV2:QGV3 QGZ2:QGZ3 QHD2:QHD3 QHH2:QHH3 QHL2:QHL3 QHP2:QHP3 QHT2:QHT3 QHX2:QHX3 QIB2:QIB3 QIF2:QIF3 QIJ2:QIJ3 QIN2:QIN3 QIR2:QIR3 QIV2:QIV3 QIZ2:QIZ3 QJD2:QJD3 QJH2:QJH3 QJL2:QJL3 QJP2:QJP3 QJT2:QJT3 QJX2:QJX3 QKB2:QKB3 QKF2:QKF3 QKJ2:QKJ3 QKN2:QKN3 QKR2:QKR3 QKV2:QKV3 QKZ2:QKZ3 QLD2:QLD3 QLH2:QLH3 QLL2:QLL3 QLP2:QLP3 QLT2:QLT3 QLX2:QLX3 QMB2:QMB3 QMF2:QMF3 QMJ2:QMJ3 QMN2:QMN3 QMR2:QMR3 QMV2:QMV3 QMZ2:QMZ3 QND2:QND3 QNH2:QNH3 QNL2:QNL3 QNP2:QNP3 QNT2:QNT3 QNX2:QNX3 QOB2:QOB3 QOF2:QOF3 QOJ2:QOJ3 QON2:QON3 QOR2:QOR3 QOV2:QOV3 QOZ2:QOZ3 QPD2:QPD3 QPH2:QPH3 QPL2:QPL3 QPP2:QPP3 QPT2:QPT3 QPX2:QPX3 QQB2:QQB3 QQF2:QQF3 QQJ2:QQJ3 QQN2:QQN3 QQR2:QQR3 QQV2:QQV3 QQZ2:QQZ3 QRD2:QRD3 QRH2:QRH3 QRL2:QRL3 QRP2:QRP3 QRT2:QRT3 QRX2:QRX3 QSB2:QSB3 QSF2:QSF3 QSJ2:QSJ3 QSN2:QSN3 QSR2:QSR3 QSV2:QSV3 QSZ2:QSZ3 QTD2:QTD3 QTH2:QTH3 QTL2:QTL3 QTP2:QTP3 QTT2:QTT3 QTX2:QTX3 QUB2:QUB3 QUF2:QUF3 QUJ2:QUJ3 QUN2:QUN3 QUR2:QUR3 QUV2:QUV3 QUZ2:QUZ3 QVD2:QVD3 QVH2:QVH3 QVL2:QVL3 QVP2:QVP3 QVT2:QVT3 QVX2:QVX3 QWB2:QWB3 QWF2:QWF3 QWJ2:QWJ3 QWN2:QWN3 QWR2:QWR3 QWV2:QWV3 QWZ2:QWZ3 QXD2:QXD3 QXH2:QXH3 QXL2:QXL3 QXP2:QXP3 QXT2:QXT3 QXX2:QXX3 QYB2:QYB3 QYF2:QYF3 QYJ2:QYJ3 QYN2:QYN3 QYR2:QYR3 QYV2:QYV3 QYZ2:QYZ3 QZD2:QZD3 QZH2:QZH3 QZL2:QZL3 QZP2:QZP3 QZT2:QZT3 QZX2:QZX3 RAB2:RAB3 RAF2:RAF3 RAJ2:RAJ3 RAN2:RAN3 RAR2:RAR3 RAV2:RAV3 RAZ2:RAZ3 RBD2:RBD3 RBH2:RBH3 RBL2:RBL3 RBP2:RBP3 RBT2:RBT3 RBX2:RBX3 RCB2:RCB3 RCF2:RCF3 RCJ2:RCJ3 RCN2:RCN3 RCR2:RCR3 RCV2:RCV3 RCZ2:RCZ3 RDD2:RDD3 RDH2:RDH3 RDL2:RDL3 RDP2:RDP3 RDT2:RDT3 RDX2:RDX3 REB2:REB3 REF2:REF3 REJ2:REJ3 REN2:REN3 RER2:RER3 REV2:REV3 REZ2:REZ3 RFD2:RFD3 RFH2:RFH3 RFL2:RFL3 RFP2:RFP3 RFT2:RFT3 RFX2:RFX3 RGB2:RGB3 RGF2:RGF3 RGJ2:RGJ3 RGN2:RGN3 RGR2:RGR3 RGV2:RGV3 RGZ2:RGZ3 RHD2:RHD3 RHH2:RHH3 RHL2:RHL3 RHP2:RHP3 RHT2:RHT3 RHX2:RHX3 RIB2:RIB3 RIF2:RIF3 RIJ2:RIJ3 RIN2:RIN3 RIR2:RIR3 RIV2:RIV3 RIZ2:RIZ3 RJD2:RJD3 RJH2:RJH3 RJL2:RJL3 RJP2:RJP3 RJT2:RJT3 RJX2:RJX3 RKB2:RKB3 RKF2:RKF3 RKJ2:RKJ3 RKN2:RKN3 RKR2:RKR3 RKV2:RKV3 RKZ2:RKZ3 RLD2:RLD3 RLH2:RLH3 RLL2:RLL3 RLP2:RLP3 RLT2:RLT3 RLX2:RLX3 RMB2:RMB3 RMF2:RMF3 RMJ2:RMJ3 RMN2:RMN3 RMR2:RMR3 RMV2:RMV3 RMZ2:RMZ3 RND2:RND3 RNH2:RNH3 RNL2:RNL3 RNP2:RNP3 RNT2:RNT3 RNX2:RNX3 ROB2:ROB3 ROF2:ROF3 ROJ2:ROJ3 RON2:RON3 ROR2:ROR3 ROV2:ROV3 ROZ2:ROZ3 RPD2:RPD3 RPH2:RPH3 RPL2:RPL3 RPP2:RPP3 RPT2:RPT3 RPX2:RPX3 RQB2:RQB3 RQF2:RQF3 RQJ2:RQJ3 RQN2:RQN3 RQR2:RQR3 RQV2:RQV3 RQZ2:RQZ3 RRD2:RRD3 RRH2:RRH3 RRL2:RRL3 RRP2:RRP3 RRT2:RRT3 RRX2:RRX3 RSB2:RSB3 RSF2:RSF3 RSJ2:RSJ3 RSN2:RSN3 RSR2:RSR3 RSV2:RSV3 RSZ2:RSZ3 RTD2:RTD3 RTH2:RTH3 RTL2:RTL3 RTP2:RTP3 RTT2:RTT3 RTX2:RTX3 RUB2:RUB3 RUF2:RUF3 RUJ2:RUJ3 RUN2:RUN3 RUR2:RUR3 RUV2:RUV3 RUZ2:RUZ3 RVD2:RVD3 RVH2:RVH3 RVL2:RVL3 RVP2:RVP3 RVT2:RVT3 RVX2:RVX3 RWB2:RWB3 RWF2:RWF3 RWJ2:RWJ3 RWN2:RWN3 RWR2:RWR3 RWV2:RWV3 RWZ2:RWZ3 RXD2:RXD3 RXH2:RXH3 RXL2:RXL3 RXP2:RXP3 RXT2:RXT3 RXX2:RXX3 RYB2:RYB3 RYF2:RYF3 RYJ2:RYJ3 RYN2:RYN3 RYR2:RYR3 RYV2:RYV3 RYZ2:RYZ3 RZD2:RZD3 RZH2:RZH3 RZL2:RZL3 RZP2:RZP3 RZT2:RZT3 RZX2:RZX3 SAB2:SAB3 SAF2:SAF3 SAJ2:SAJ3 SAN2:SAN3 SAR2:SAR3 SAV2:SAV3 SAZ2:SAZ3 SBD2:SBD3 SBH2:SBH3 SBL2:SBL3 SBP2:SBP3 SBT2:SBT3 SBX2:SBX3 SCB2:SCB3 SCF2:SCF3 SCJ2:SCJ3 SCN2:SCN3 SCR2:SCR3 SCV2:SCV3 SCZ2:SCZ3 SDD2:SDD3 SDH2:SDH3 SDL2:SDL3 SDP2:SDP3 SDT2:SDT3 SDX2:SDX3 SEB2:SEB3 SEF2:SEF3 SEJ2:SEJ3 SEN2:SEN3 SER2:SER3 SEV2:SEV3 SEZ2:SEZ3 SFD2:SFD3 SFH2:SFH3 SFL2:SFL3 SFP2:SFP3 SFT2:SFT3 SFX2:SFX3 SGB2:SGB3 SGF2:SGF3 SGJ2:SGJ3 SGN2:SGN3 SGR2:SGR3 SGV2:SGV3 SGZ2:SGZ3 SHD2:SHD3 SHH2:SHH3 SHL2:SHL3 SHP2:SHP3 SHT2:SHT3 SHX2:SHX3 SIB2:SIB3 SIF2:SIF3 SIJ2:SIJ3 SIN2:SIN3 SIR2:SIR3 SIV2:SIV3 SIZ2:SIZ3 SJD2:SJD3 SJH2:SJH3 SJL2:SJL3 SJP2:SJP3 SJT2:SJT3 SJX2:SJX3 SKB2:SKB3 SKF2:SKF3 SKJ2:SKJ3 SKN2:SKN3 SKR2:SKR3 SKV2:SKV3 SKZ2:SKZ3 SLD2:SLD3 SLH2:SLH3 SLL2:SLL3 SLP2:SLP3 SLT2:SLT3 SLX2:SLX3 SMB2:SMB3 SMF2:SMF3 SMJ2:SMJ3 SMN2:SMN3 SMR2:SMR3 SMV2:SMV3 SMZ2:SMZ3 SND2:SND3 SNH2:SNH3 SNL2:SNL3 SNP2:SNP3 SNT2:SNT3 SNX2:SNX3 SOB2:SOB3 SOF2:SOF3 SOJ2:SOJ3 SON2:SON3 SOR2:SOR3 SOV2:SOV3 SOZ2:SOZ3 SPD2:SPD3 SPH2:SPH3 SPL2:SPL3 SPP2:SPP3 SPT2:SPT3 SPX2:SPX3 SQB2:SQB3 SQF2:SQF3 SQJ2:SQJ3 SQN2:SQN3 SQR2:SQR3 SQV2:SQV3 SQZ2:SQZ3 SRD2:SRD3 SRH2:SRH3 SRL2:SRL3 SRP2:SRP3 SRT2:SRT3 SRX2:SRX3 SSB2:SSB3 SSF2:SSF3 SSJ2:SSJ3 SSN2:SSN3 SSR2:SSR3 SSV2:SSV3 SSZ2:SSZ3 STD2:STD3 STH2:STH3 STL2:STL3 STP2:STP3 STT2:STT3 STX2:STX3 SUB2:SUB3 SUF2:SUF3 SUJ2:SUJ3 SUN2:SUN3 SUR2:SUR3 SUV2:SUV3 SUZ2:SUZ3 SVD2:SVD3 SVH2:SVH3 SVL2:SVL3 SVP2:SVP3 SVT2:SVT3 SVX2:SVX3 SWB2:SWB3 SWF2:SWF3 SWJ2:SWJ3 SWN2:SWN3 SWR2:SWR3 SWV2:SWV3 SWZ2:SWZ3 SXD2:SXD3 SXH2:SXH3 SXL2:SXL3 SXP2:SXP3 SXT2:SXT3 SXX2:SXX3 SYB2:SYB3 SYF2:SYF3 SYJ2:SYJ3 SYN2:SYN3 SYR2:SYR3 SYV2:SYV3 SYZ2:SYZ3 SZD2:SZD3 SZH2:SZH3 SZL2:SZL3 SZP2:SZP3 SZT2:SZT3 SZX2:SZX3 TAB2:TAB3 TAF2:TAF3 TAJ2:TAJ3 TAN2:TAN3 TAR2:TAR3 TAV2:TAV3 TAZ2:TAZ3 TBD2:TBD3 TBH2:TBH3 TBL2:TBL3 TBP2:TBP3 TBT2:TBT3 TBX2:TBX3 TCB2:TCB3 TCF2:TCF3 TCJ2:TCJ3 TCN2:TCN3 TCR2:TCR3 TCV2:TCV3 TCZ2:TCZ3 TDD2:TDD3 TDH2:TDH3 TDL2:TDL3 TDP2:TDP3 TDT2:TDT3 TDX2:TDX3 TEB2:TEB3 TEF2:TEF3 TEJ2:TEJ3 TEN2:TEN3 TER2:TER3 TEV2:TEV3 TEZ2:TEZ3 TFD2:TFD3 TFH2:TFH3 TFL2:TFL3 TFP2:TFP3 TFT2:TFT3 TFX2:TFX3 TGB2:TGB3 TGF2:TGF3 TGJ2:TGJ3 TGN2:TGN3 TGR2:TGR3 TGV2:TGV3 TGZ2:TGZ3 THD2:THD3 THH2:THH3 THL2:THL3 THP2:THP3 THT2:THT3 THX2:THX3 TIB2:TIB3 TIF2:TIF3 TIJ2:TIJ3 TIN2:TIN3 TIR2:TIR3 TIV2:TIV3 TIZ2:TIZ3 TJD2:TJD3 TJH2:TJH3 TJL2:TJL3 TJP2:TJP3 TJT2:TJT3 TJX2:TJX3 TKB2:TKB3 TKF2:TKF3 TKJ2:TKJ3 TKN2:TKN3 TKR2:TKR3 TKV2:TKV3 TKZ2:TKZ3 TLD2:TLD3 TLH2:TLH3 TLL2:TLL3 TLP2:TLP3 TLT2:TLT3 TLX2:TLX3 TMB2:TMB3 TMF2:TMF3 TMJ2:TMJ3 TMN2:TMN3 TMR2:TMR3 TMV2:TMV3 TMZ2:TMZ3 TND2:TND3 TNH2:TNH3 TNL2:TNL3 TNP2:TNP3 TNT2:TNT3 TNX2:TNX3 TOB2:TOB3 TOF2:TOF3 TOJ2:TOJ3 TON2:TON3 TOR2:TOR3 TOV2:TOV3 TOZ2:TOZ3 TPD2:TPD3 TPH2:TPH3 TPL2:TPL3 TPP2:TPP3 TPT2:TPT3 TPX2:TPX3 TQB2:TQB3 TQF2:TQF3 TQJ2:TQJ3 TQN2:TQN3 TQR2:TQR3 TQV2:TQV3 TQZ2:TQZ3 TRD2:TRD3 TRH2:TRH3 TRL2:TRL3 TRP2:TRP3 TRT2:TRT3 TRX2:TRX3 TSB2:TSB3 TSF2:TSF3 TSJ2:TSJ3 TSN2:TSN3 TSR2:TSR3 TSV2:TSV3 TSZ2:TSZ3 TTD2:TTD3 TTH2:TTH3 TTL2:TTL3 TTP2:TTP3 TTT2:TTT3 TTX2:TTX3 TUB2:TUB3 TUF2:TUF3 TUJ2:TUJ3 TUN2:TUN3 TUR2:TUR3 TUV2:TUV3 TUZ2:TUZ3 TVD2:TVD3 TVH2:TVH3 TVL2:TVL3 TVP2:TVP3 TVT2:TVT3 TVX2:TVX3 TWB2:TWB3 TWF2:TWF3 TWJ2:TWJ3 TWN2:TWN3 TWR2:TWR3 TWV2:TWV3 TWZ2:TWZ3 TXD2:TXD3 TXH2:TXH3 TXL2:TXL3 TXP2:TXP3 TXT2:TXT3 TXX2:TXX3 TYB2:TYB3 TYF2:TYF3 TYJ2:TYJ3 TYN2:TYN3 TYR2:TYR3 TYV2:TYV3 TYZ2:TYZ3 TZD2:TZD3 TZH2:TZH3 TZL2:TZL3 TZP2:TZP3 TZT2:TZT3 TZX2:TZX3 UAB2:UAB3 UAF2:UAF3 UAJ2:UAJ3 UAN2:UAN3 UAR2:UAR3 UAV2:UAV3 UAZ2:UAZ3 UBD2:UBD3 UBH2:UBH3 UBL2:UBL3 UBP2:UBP3 UBT2:UBT3 UBX2:UBX3 UCB2:UCB3 UCF2:UCF3 UCJ2:UCJ3 UCN2:UCN3 UCR2:UCR3 UCV2:UCV3 UCZ2:UCZ3 UDD2:UDD3 UDH2:UDH3 UDL2:UDL3 UDP2:UDP3 UDT2:UDT3 UDX2:UDX3 UEB2:UEB3 UEF2:UEF3 UEJ2:UEJ3 UEN2:UEN3 UER2:UER3 UEV2:UEV3 UEZ2:UEZ3 UFD2:UFD3 UFH2:UFH3 UFL2:UFL3 UFP2:UFP3 UFT2:UFT3 UFX2:UFX3 UGB2:UGB3 UGF2:UGF3 UGJ2:UGJ3 UGN2:UGN3 UGR2:UGR3 UGV2:UGV3 UGZ2:UGZ3 UHD2:UHD3 UHH2:UHH3 UHL2:UHL3 UHP2:UHP3 UHT2:UHT3 UHX2:UHX3 UIB2:UIB3 UIF2:UIF3 UIJ2:UIJ3 UIN2:UIN3 UIR2:UIR3 UIV2:UIV3 UIZ2:UIZ3 UJD2:UJD3 UJH2:UJH3 UJL2:UJL3 UJP2:UJP3 UJT2:UJT3 UJX2:UJX3 UKB2:UKB3 UKF2:UKF3 UKJ2:UKJ3 UKN2:UKN3 UKR2:UKR3 UKV2:UKV3 UKZ2:UKZ3 ULD2:ULD3 ULH2:ULH3 ULL2:ULL3 ULP2:ULP3 ULT2:ULT3 ULX2:ULX3 UMB2:UMB3 UMF2:UMF3 UMJ2:UMJ3 UMN2:UMN3 UMR2:UMR3 UMV2:UMV3 UMZ2:UMZ3 UND2:UND3 UNH2:UNH3 UNL2:UNL3 UNP2:UNP3 UNT2:UNT3 UNX2:UNX3 UOB2:UOB3 UOF2:UOF3 UOJ2:UOJ3 UON2:UON3 UOR2:UOR3 UOV2:UOV3 UOZ2:UOZ3 UPD2:UPD3 UPH2:UPH3 UPL2:UPL3 UPP2:UPP3 UPT2:UPT3 UPX2:UPX3 UQB2:UQB3 UQF2:UQF3 UQJ2:UQJ3 UQN2:UQN3 UQR2:UQR3 UQV2:UQV3 UQZ2:UQZ3 URD2:URD3 URH2:URH3 URL2:URL3 URP2:URP3 URT2:URT3 URX2:URX3 USB2:USB3 USF2:USF3 USJ2:USJ3 USN2:USN3 USR2:USR3 USV2:USV3 USZ2:USZ3 UTD2:UTD3 UTH2:UTH3 UTL2:UTL3 UTP2:UTP3 UTT2:UTT3 UTX2:UTX3 UUB2:UUB3 UUF2:UUF3 UUJ2:UUJ3 UUN2:UUN3 UUR2:UUR3 UUV2:UUV3 UUZ2:UUZ3 UVD2:UVD3 UVH2:UVH3 UVL2:UVL3 UVP2:UVP3 UVT2:UVT3 UVX2:UVX3 UWB2:UWB3 UWF2:UWF3 UWJ2:UWJ3 UWN2:UWN3 UWR2:UWR3 UWV2:UWV3 UWZ2:UWZ3 UXD2:UXD3 UXH2:UXH3 UXL2:UXL3 UXP2:UXP3 UXT2:UXT3 UXX2:UXX3 UYB2:UYB3 UYF2:UYF3 UYJ2:UYJ3 UYN2:UYN3 UYR2:UYR3 UYV2:UYV3 UYZ2:UYZ3 UZD2:UZD3 UZH2:UZH3 UZL2:UZL3 UZP2:UZP3 UZT2:UZT3 UZX2:UZX3 VAB2:VAB3 VAF2:VAF3 VAJ2:VAJ3 VAN2:VAN3 VAR2:VAR3 VAV2:VAV3 VAZ2:VAZ3 VBD2:VBD3 VBH2:VBH3 VBL2:VBL3 VBP2:VBP3 VBT2:VBT3 VBX2:VBX3 VCB2:VCB3 VCF2:VCF3 VCJ2:VCJ3 VCN2:VCN3 VCR2:VCR3 VCV2:VCV3 VCZ2:VCZ3 VDD2:VDD3 VDH2:VDH3 VDL2:VDL3 VDP2:VDP3 VDT2:VDT3 VDX2:VDX3 VEB2:VEB3 VEF2:VEF3 VEJ2:VEJ3 VEN2:VEN3 VER2:VER3 VEV2:VEV3 VEZ2:VEZ3 VFD2:VFD3 VFH2:VFH3 VFL2:VFL3 VFP2:VFP3 VFT2:VFT3 VFX2:VFX3 VGB2:VGB3 VGF2:VGF3 VGJ2:VGJ3 VGN2:VGN3 VGR2:VGR3 VGV2:VGV3 VGZ2:VGZ3 VHD2:VHD3 VHH2:VHH3 VHL2:VHL3 VHP2:VHP3 VHT2:VHT3 VHX2:VHX3 VIB2:VIB3 VIF2:VIF3 VIJ2:VIJ3 VIN2:VIN3 VIR2:VIR3 VIV2:VIV3 VIZ2:VIZ3 VJD2:VJD3 VJH2:VJH3 VJL2:VJL3 VJP2:VJP3 VJT2:VJT3 VJX2:VJX3 VKB2:VKB3 VKF2:VKF3 VKJ2:VKJ3 VKN2:VKN3 VKR2:VKR3 VKV2:VKV3 VKZ2:VKZ3 VLD2:VLD3 VLH2:VLH3 VLL2:VLL3 VLP2:VLP3 VLT2:VLT3 VLX2:VLX3 VMB2:VMB3 VMF2:VMF3 VMJ2:VMJ3 VMN2:VMN3 VMR2:VMR3 VMV2:VMV3 VMZ2:VMZ3 VND2:VND3 VNH2:VNH3 VNL2:VNL3 VNP2:VNP3 VNT2:VNT3 VNX2:VNX3 VOB2:VOB3 VOF2:VOF3 VOJ2:VOJ3 VON2:VON3 VOR2:VOR3 VOV2:VOV3 VOZ2:VOZ3 VPD2:VPD3 VPH2:VPH3 VPL2:VPL3 VPP2:VPP3 VPT2:VPT3 VPX2:VPX3 VQB2:VQB3 VQF2:VQF3 VQJ2:VQJ3 VQN2:VQN3 VQR2:VQR3 VQV2:VQV3 VQZ2:VQZ3 VRD2:VRD3 VRH2:VRH3 VRL2:VRL3 VRP2:VRP3 VRT2:VRT3 VRX2:VRX3 VSB2:VSB3 VSF2:VSF3 VSJ2:VSJ3 VSN2:VSN3 VSR2:VSR3 VSV2:VSV3 VSZ2:VSZ3 VTD2:VTD3 VTH2:VTH3 VTL2:VTL3 VTP2:VTP3 VTT2:VTT3 VTX2:VTX3 VUB2:VUB3 VUF2:VUF3 VUJ2:VUJ3 VUN2:VUN3 VUR2:VUR3 VUV2:VUV3 VUZ2:VUZ3 VVD2:VVD3 VVH2:VVH3 VVL2:VVL3 VVP2:VVP3 VVT2:VVT3 VVX2:VVX3 VWB2:VWB3 VWF2:VWF3 VWJ2:VWJ3 VWN2:VWN3 VWR2:VWR3 VWV2:VWV3 VWZ2:VWZ3 VXD2:VXD3 VXH2:VXH3 VXL2:VXL3 VXP2:VXP3 VXT2:VXT3 VXX2:VXX3 VYB2:VYB3 VYF2:VYF3 VYJ2:VYJ3 VYN2:VYN3 VYR2:VYR3 VYV2:VYV3 VYZ2:VYZ3 VZD2:VZD3 VZH2:VZH3 VZL2:VZL3 VZP2:VZP3 VZT2:VZT3 VZX2:VZX3 WAB2:WAB3 WAF2:WAF3 WAJ2:WAJ3 WAN2:WAN3 WAR2:WAR3 WAV2:WAV3 WAZ2:WAZ3 WBD2:WBD3 WBH2:WBH3 WBL2:WBL3 WBP2:WBP3 WBT2:WBT3 WBX2:WBX3 WCB2:WCB3 WCF2:WCF3 WCJ2:WCJ3 WCN2:WCN3 WCR2:WCR3 WCV2:WCV3 WCZ2:WCZ3 WDD2:WDD3 WDH2:WDH3 WDL2:WDL3 WDP2:WDP3 WDT2:WDT3 WDX2:WDX3 WEB2:WEB3 WEF2:WEF3 WEJ2:WEJ3 WEN2:WEN3 WER2:WER3 WEV2:WEV3 WEZ2:WEZ3 WFD2:WFD3 WFH2:WFH3 WFL2:WFL3 WFP2:WFP3 WFT2:WFT3 WFX2:WFX3 WGB2:WGB3 WGF2:WGF3 WGJ2:WGJ3 WGN2:WGN3 WGR2:WGR3 WGV2:WGV3 WGZ2:WGZ3 WHD2:WHD3 WHH2:WHH3 WHL2:WHL3 WHP2:WHP3 WHT2:WHT3 WHX2:WHX3 WIB2:WIB3 WIF2:WIF3 WIJ2:WIJ3 WIN2:WIN3 WIR2:WIR3 WIV2:WIV3 WIZ2:WIZ3 WJD2:WJD3 WJH2:WJH3 WJL2:WJL3 WJP2:WJP3 WJT2:WJT3 WJX2:WJX3 WKB2:WKB3 WKF2:WKF3 WKJ2:WKJ3 WKN2:WKN3 WKR2:WKR3 WKV2:WKV3 WKZ2:WKZ3 WLD2:WLD3 WLH2:WLH3 WLL2:WLL3 WLP2:WLP3 WLT2:WLT3 WLX2:WLX3 WMB2:WMB3 WMF2:WMF3 WMJ2:WMJ3 WMN2:WMN3 WMR2:WMR3 WMV2:WMV3 WMZ2:WMZ3 WND2:WND3 WNH2:WNH3 WNL2:WNL3 WNP2:WNP3 WNT2:WNT3 WNX2:WNX3 WOB2:WOB3 WOF2:WOF3 WOJ2:WOJ3 WON2:WON3 WOR2:WOR3 WOV2:WOV3 WOZ2:WOZ3 WPD2:WPD3 WPH2:WPH3 WPL2:WPL3 WPP2:WPP3 WPT2:WPT3 WPX2:WPX3 WQB2:WQB3 WQF2:WQF3 WQJ2:WQJ3 WQN2:WQN3 WQR2:WQR3 WQV2:WQV3 WQZ2:WQZ3 WRD2:WRD3 WRH2:WRH3 WRL2:WRL3 WRP2:WRP3 WRT2:WRT3 WRX2:WRX3 WSB2:WSB3 WSF2:WSF3 WSJ2:WSJ3 WSN2:WSN3 WSR2:WSR3 WSV2:WSV3 WSZ2:WSZ3 WTD2:WTD3 WTH2:WTH3 WTL2:WTL3 WTP2:WTP3 WTT2:WTT3 WTX2:WTX3 WUB2:WUB3 WUF2:WUF3 WUJ2:WUJ3 WUN2:WUN3 WUR2:WUR3 WUV2:WUV3 WUZ2:WUZ3 WVD2:WVD3 WVH2:WVH3 WVL2:WVL3 WVP2:WVP3 WVT2:WVT3 WVX2:WVX3 WWB2:WWB3 WWF2:WWF3 WWJ2:WWJ3 WWN2:WWN3 WWR2:WWR3 WWV2:WWV3 WWZ2:WWZ3 WXD2:WXD3 WXH2:WXH3 WXL2:WXL3 WXP2:WXP3 WXT2:WXT3 WXX2:WXX3 WYB2:WYB3 WYF2:WYF3 WYJ2:WYJ3 WYN2:WYN3 WYR2:WYR3 WYV2:WYV3 WYZ2:WYZ3 WZD2:WZD3 WZH2:WZH3 WZL2:WZL3 WZP2:WZP3 WZT2:WZT3 WZX2:WZX3 XAB2:XAB3 XAF2:XAF3 XAJ2:XAJ3 XAN2:XAN3 XAR2:XAR3 XAV2:XAV3 XAZ2:XAZ3 XBD2:XBD3 XBH2:XBH3 XBL2:XBL3 XBP2:XBP3 XBT2:XBT3 XBX2:XBX3 XCB2:XCB3 XCF2:XCF3 XCJ2:XCJ3 XCN2:XCN3 XCR2:XCR3 XCV2:XCV3 XCZ2:XCZ3 XDD2:XDD3 XDH2:XDH3 XDL2:XDL3 XDP2:XDP3 XDT2:XDT3 XDX2:XDX3 XEB2:XEB3 XEF2:XEF3 XEJ2:XEJ3 XEN2:XEN3 XER2:XER3 XEV2:XEV3 XEZ2:XEZ3 XFD2:XFD3 D2:D123">
+  <conditionalFormatting sqref="H2 L2 P2 T2 X2 AB2 AF2 AJ2 AN2 AR2 AV2 AZ2 BD2 BH2 BL2 BP2 BT2 BX2 CB2 CF2 CJ2 CN2 CR2 CV2 CZ2 DD2 DH2 DL2 DP2 DT2 DX2 EB2 EF2 EJ2 EN2 ER2 EV2 EZ2 FD2 FH2 FL2 FP2 FT2 FX2 GB2 GF2 GJ2 GN2 GR2 GV2 GZ2 HD2 HH2 HL2 HP2 HT2 HX2 IB2 IF2 IJ2 IN2 IR2 IV2 IZ2 JD2 JH2 JL2 JP2 JT2 JX2 KB2 KF2 KJ2 KN2 KR2 KV2 KZ2 LD2 LH2 LL2 LP2 LT2 LX2 MB2 MF2 MJ2 MN2 MR2 MV2 MZ2 ND2 NH2 NL2 NP2 NT2 NX2 OB2 OF2 OJ2 ON2 OR2 OV2 OZ2 PD2 PH2 PL2 PP2 PT2 PX2 QB2 QF2 QJ2 QN2 QR2 QV2 QZ2 RD2 RH2 RL2 RP2 RT2 RX2 SB2 SF2 SJ2 SN2 SR2 SV2 SZ2 TD2 TH2 TL2 TP2 TT2 TX2 UB2 UF2 UJ2 UN2 UR2 UV2 UZ2 VD2 VH2 VL2 VP2 VT2 VX2 WB2 WF2 WJ2 WN2 WR2 WV2 WZ2 XD2 XH2 XL2 XP2 XT2 XX2 YB2 YF2 YJ2 YN2 YR2 YV2 YZ2 ZD2 ZH2 ZL2 ZP2 ZT2 ZX2 AAB2 AAF2 AAJ2 AAN2 AAR2 AAV2 AAZ2 ABD2 ABH2 ABL2 ABP2 ABT2 ABX2 ACB2 ACF2 ACJ2 ACN2 ACR2 ACV2 ACZ2 ADD2 ADH2 ADL2 ADP2 ADT2 ADX2 AEB2 AEF2 AEJ2 AEN2 AER2 AEV2 AEZ2 AFD2 AFH2 AFL2 AFP2 AFT2 AFX2 AGB2 AGF2 AGJ2 AGN2 AGR2 AGV2 AGZ2 AHD2 AHH2 AHL2 AHP2 AHT2 AHX2 AIB2 AIF2 AIJ2 AIN2 AIR2 AIV2 AIZ2 AJD2 AJH2 AJL2 AJP2 AJT2 AJX2 AKB2 AKF2 AKJ2 AKN2 AKR2 AKV2 AKZ2 ALD2 ALH2 ALL2 ALP2 ALT2 ALX2 AMB2 AMF2 AMJ2 AMN2 AMR2 AMV2 AMZ2 AND2 ANH2 ANL2 ANP2 ANT2 ANX2 AOB2 AOF2 AOJ2 AON2 AOR2 AOV2 AOZ2 APD2 APH2 APL2 APP2 APT2 APX2 AQB2 AQF2 AQJ2 AQN2 AQR2 AQV2 AQZ2 ARD2 ARH2 ARL2 ARP2 ART2 ARX2 ASB2 ASF2 ASJ2 ASN2 ASR2 ASV2 ASZ2 ATD2 ATH2 ATL2 ATP2 ATT2 ATX2 AUB2 AUF2 AUJ2 AUN2 AUR2 AUV2 AUZ2 AVD2 AVH2 AVL2 AVP2 AVT2 AVX2 AWB2 AWF2 AWJ2 AWN2 AWR2 AWV2 AWZ2 AXD2 AXH2 AXL2 AXP2 AXT2 AXX2 AYB2 AYF2 AYJ2 AYN2 AYR2 AYV2 AYZ2 AZD2 AZH2 AZL2 AZP2 AZT2 AZX2 BAB2 BAF2 BAJ2 BAN2 BAR2 BAV2 BAZ2 BBD2 BBH2 BBL2 BBP2 BBT2 BBX2 BCB2 BCF2 BCJ2 BCN2 BCR2 BCV2 BCZ2 BDD2 BDH2 BDL2 BDP2 BDT2 BDX2 BEB2 BEF2 BEJ2 BEN2 BER2 BEV2 BEZ2 BFD2 BFH2 BFL2 BFP2 BFT2 BFX2 BGB2 BGF2 BGJ2 BGN2 BGR2 BGV2 BGZ2 BHD2 BHH2 BHL2 BHP2 BHT2 BHX2 BIB2 BIF2 BIJ2 BIN2 BIR2 BIV2 BIZ2 BJD2 BJH2 BJL2 BJP2 BJT2 BJX2 BKB2 BKF2 BKJ2 BKN2 BKR2 BKV2 BKZ2 BLD2 BLH2 BLL2 BLP2 BLT2 BLX2 BMB2 BMF2 BMJ2 BMN2 BMR2 BMV2 BMZ2 BND2 BNH2 BNL2 BNP2 BNT2 BNX2 BOB2 BOF2 BOJ2 BON2 BOR2 BOV2 BOZ2 BPD2 BPH2 BPL2 BPP2 BPT2 BPX2 BQB2 BQF2 BQJ2 BQN2 BQR2 BQV2 BQZ2 BRD2 BRH2 BRL2 BRP2 BRT2 BRX2 BSB2 BSF2 BSJ2 BSN2 BSR2 BSV2 BSZ2 BTD2 BTH2 BTL2 BTP2 BTT2 BTX2 BUB2 BUF2 BUJ2 BUN2 BUR2 BUV2 BUZ2 BVD2 BVH2 BVL2 BVP2 BVT2 BVX2 BWB2 BWF2 BWJ2 BWN2 BWR2 BWV2 BWZ2 BXD2 BXH2 BXL2 BXP2 BXT2 BXX2 BYB2 BYF2 BYJ2 BYN2 BYR2 BYV2 BYZ2 BZD2 BZH2 BZL2 BZP2 BZT2 BZX2 CAB2 CAF2 CAJ2 CAN2 CAR2 CAV2 CAZ2 CBD2 CBH2 CBL2 CBP2 CBT2 CBX2 CCB2 CCF2 CCJ2 CCN2 CCR2 CCV2 CCZ2 CDD2 CDH2 CDL2 CDP2 CDT2 CDX2 CEB2 CEF2 CEJ2 CEN2 CER2 CEV2 CEZ2 CFD2 CFH2 CFL2 CFP2 CFT2 CFX2 CGB2 CGF2 CGJ2 CGN2 CGR2 CGV2 CGZ2 CHD2 CHH2 CHL2 CHP2 CHT2 CHX2 CIB2 CIF2 CIJ2 CIN2 CIR2 CIV2 CIZ2 CJD2 CJH2 CJL2 CJP2 CJT2 CJX2 CKB2 CKF2 CKJ2 CKN2 CKR2 CKV2 CKZ2 CLD2 CLH2 CLL2 CLP2 CLT2 CLX2 CMB2 CMF2 CMJ2 CMN2 CMR2 CMV2 CMZ2 CND2 CNH2 CNL2 CNP2 CNT2 CNX2 COB2 COF2 COJ2 CON2 COR2 COV2 COZ2 CPD2 CPH2 CPL2 CPP2 CPT2 CPX2 CQB2 CQF2 CQJ2 CQN2 CQR2 CQV2 CQZ2 CRD2 CRH2 CRL2 CRP2 CRT2 CRX2 CSB2 CSF2 CSJ2 CSN2 CSR2 CSV2 CSZ2 CTD2 CTH2 CTL2 CTP2 CTT2 CTX2 CUB2 CUF2 CUJ2 CUN2 CUR2 CUV2 CUZ2 CVD2 CVH2 CVL2 CVP2 CVT2 CVX2 CWB2 CWF2 CWJ2 CWN2 CWR2 CWV2 CWZ2 CXD2 CXH2 CXL2 CXP2 CXT2 CXX2 CYB2 CYF2 CYJ2 CYN2 CYR2 CYV2 CYZ2 CZD2 CZH2 CZL2 CZP2 CZT2 CZX2 DAB2 DAF2 DAJ2 DAN2 DAR2 DAV2 DAZ2 DBD2 DBH2 DBL2 DBP2 DBT2 DBX2 DCB2 DCF2 DCJ2 DCN2 DCR2 DCV2 DCZ2 DDD2 DDH2 DDL2 DDP2 DDT2 DDX2 DEB2 DEF2 DEJ2 DEN2 DER2 DEV2 DEZ2 DFD2 DFH2 DFL2 DFP2 DFT2 DFX2 DGB2 DGF2 DGJ2 DGN2 DGR2 DGV2 DGZ2 DHD2 DHH2 DHL2 DHP2 DHT2 DHX2 DIB2 DIF2 DIJ2 DIN2 DIR2 DIV2 DIZ2 DJD2 DJH2 DJL2 DJP2 DJT2 DJX2 DKB2 DKF2 DKJ2 DKN2 DKR2 DKV2 DKZ2 DLD2 DLH2 DLL2 DLP2 DLT2 DLX2 DMB2 DMF2 DMJ2 DMN2 DMR2 DMV2 DMZ2 DND2 DNH2 DNL2 DNP2 DNT2 DNX2 DOB2 DOF2 DOJ2 DON2 DOR2 DOV2 DOZ2 DPD2 DPH2 DPL2 DPP2 DPT2 DPX2 DQB2 DQF2 DQJ2 DQN2 DQR2 DQV2 DQZ2 DRD2 DRH2 DRL2 DRP2 DRT2 DRX2 DSB2 DSF2 DSJ2 DSN2 DSR2 DSV2 DSZ2 DTD2 DTH2 DTL2 DTP2 DTT2 DTX2 DUB2 DUF2 DUJ2 DUN2 DUR2 DUV2 DUZ2 DVD2 DVH2 DVL2 DVP2 DVT2 DVX2 DWB2 DWF2 DWJ2 DWN2 DWR2 DWV2 DWZ2 DXD2 DXH2 DXL2 DXP2 DXT2 DXX2 DYB2 DYF2 DYJ2 DYN2 DYR2 DYV2 DYZ2 DZD2 DZH2 DZL2 DZP2 DZT2 DZX2 EAB2 EAF2 EAJ2 EAN2 EAR2 EAV2 EAZ2 EBD2 EBH2 EBL2 EBP2 EBT2 EBX2 ECB2 ECF2 ECJ2 ECN2 ECR2 ECV2 ECZ2 EDD2 EDH2 EDL2 EDP2 EDT2 EDX2 EEB2 EEF2 EEJ2 EEN2 EER2 EEV2 EEZ2 EFD2 EFH2 EFL2 EFP2 EFT2 EFX2 EGB2 EGF2 EGJ2 EGN2 EGR2 EGV2 EGZ2 EHD2 EHH2 EHL2 EHP2 EHT2 EHX2 EIB2 EIF2 EIJ2 EIN2 EIR2 EIV2 EIZ2 EJD2 EJH2 EJL2 EJP2 EJT2 EJX2 EKB2 EKF2 EKJ2 EKN2 EKR2 EKV2 EKZ2 ELD2 ELH2 ELL2 ELP2 ELT2 ELX2 EMB2 EMF2 EMJ2 EMN2 EMR2 EMV2 EMZ2 END2 ENH2 ENL2 ENP2 ENT2 ENX2 EOB2 EOF2 EOJ2 EON2 EOR2 EOV2 EOZ2 EPD2 EPH2 EPL2 EPP2 EPT2 EPX2 EQB2 EQF2 EQJ2 EQN2 EQR2 EQV2 EQZ2 ERD2 ERH2 ERL2 ERP2 ERT2 ERX2 ESB2 ESF2 ESJ2 ESN2 ESR2 ESV2 ESZ2 ETD2 ETH2 ETL2 ETP2 ETT2 ETX2 EUB2 EUF2 EUJ2 EUN2 EUR2 EUV2 EUZ2 EVD2 EVH2 EVL2 EVP2 EVT2 EVX2 EWB2 EWF2 EWJ2 EWN2 EWR2 EWV2 EWZ2 EXD2 EXH2 EXL2 EXP2 EXT2 EXX2 EYB2 EYF2 EYJ2 EYN2 EYR2 EYV2 EYZ2 EZD2 EZH2 EZL2 EZP2 EZT2 EZX2 FAB2 FAF2 FAJ2 FAN2 FAR2 FAV2 FAZ2 FBD2 FBH2 FBL2 FBP2 FBT2 FBX2 FCB2 FCF2 FCJ2 FCN2 FCR2 FCV2 FCZ2 FDD2 FDH2 FDL2 FDP2 FDT2 FDX2 FEB2 FEF2 FEJ2 FEN2 FER2 FEV2 FEZ2 FFD2 FFH2 FFL2 FFP2 FFT2 FFX2 FGB2 FGF2 FGJ2 FGN2 FGR2 FGV2 FGZ2 FHD2 FHH2 FHL2 FHP2 FHT2 FHX2 FIB2 FIF2 FIJ2 FIN2 FIR2 FIV2 FIZ2 FJD2 FJH2 FJL2 FJP2 FJT2 FJX2 FKB2 FKF2 FKJ2 FKN2 FKR2 FKV2 FKZ2 FLD2 FLH2 FLL2 FLP2 FLT2 FLX2 FMB2 FMF2 FMJ2 FMN2 FMR2 FMV2 FMZ2 FND2 FNH2 FNL2 FNP2 FNT2 FNX2 FOB2 FOF2 FOJ2 FON2 FOR2 FOV2 FOZ2 FPD2 FPH2 FPL2 FPP2 FPT2 FPX2 FQB2 FQF2 FQJ2 FQN2 FQR2 FQV2 FQZ2 FRD2 FRH2 FRL2 FRP2 FRT2 FRX2 FSB2 FSF2 FSJ2 FSN2 FSR2 FSV2 FSZ2 FTD2 FTH2 FTL2 FTP2 FTT2 FTX2 FUB2 FUF2 FUJ2 FUN2 FUR2 FUV2 FUZ2 FVD2 FVH2 FVL2 FVP2 FVT2 FVX2 FWB2 FWF2 FWJ2 FWN2 FWR2 FWV2 FWZ2 FXD2 FXH2 FXL2 FXP2 FXT2 FXX2 FYB2 FYF2 FYJ2 FYN2 FYR2 FYV2 FYZ2 FZD2 FZH2 FZL2 FZP2 FZT2 FZX2 GAB2 GAF2 GAJ2 GAN2 GAR2 GAV2 GAZ2 GBD2 GBH2 GBL2 GBP2 GBT2 GBX2 GCB2 GCF2 GCJ2 GCN2 GCR2 GCV2 GCZ2 GDD2 GDH2 GDL2 GDP2 GDT2 GDX2 GEB2 GEF2 GEJ2 GEN2 GER2 GEV2 GEZ2 GFD2 GFH2 GFL2 GFP2 GFT2 GFX2 GGB2 GGF2 GGJ2 GGN2 GGR2 GGV2 GGZ2 GHD2 GHH2 GHL2 GHP2 GHT2 GHX2 GIB2 GIF2 GIJ2 GIN2 GIR2 GIV2 GIZ2 GJD2 GJH2 GJL2 GJP2 GJT2 GJX2 GKB2 GKF2 GKJ2 GKN2 GKR2 GKV2 GKZ2 GLD2 GLH2 GLL2 GLP2 GLT2 GLX2 GMB2 GMF2 GMJ2 GMN2 GMR2 GMV2 GMZ2 GND2 GNH2 GNL2 GNP2 GNT2 GNX2 GOB2 GOF2 GOJ2 GON2 GOR2 GOV2 GOZ2 GPD2 GPH2 GPL2 GPP2 GPT2 GPX2 GQB2 GQF2 GQJ2 GQN2 GQR2 GQV2 GQZ2 GRD2 GRH2 GRL2 GRP2 GRT2 GRX2 GSB2 GSF2 GSJ2 GSN2 GSR2 GSV2 GSZ2 GTD2 GTH2 GTL2 GTP2 GTT2 GTX2 GUB2 GUF2 GUJ2 GUN2 GUR2 GUV2 GUZ2 GVD2 GVH2 GVL2 GVP2 GVT2 GVX2 GWB2 GWF2 GWJ2 GWN2 GWR2 GWV2 GWZ2 GXD2 GXH2 GXL2 GXP2 GXT2 GXX2 GYB2 GYF2 GYJ2 GYN2 GYR2 GYV2 GYZ2 GZD2 GZH2 GZL2 GZP2 GZT2 GZX2 HAB2 HAF2 HAJ2 HAN2 HAR2 HAV2 HAZ2 HBD2 HBH2 HBL2 HBP2 HBT2 HBX2 HCB2 HCF2 HCJ2 HCN2 HCR2 HCV2 HCZ2 HDD2 HDH2 HDL2 HDP2 HDT2 HDX2 HEB2 HEF2 HEJ2 HEN2 HER2 HEV2 HEZ2 HFD2 HFH2 HFL2 HFP2 HFT2 HFX2 HGB2 HGF2 HGJ2 HGN2 HGR2 HGV2 HGZ2 HHD2 HHH2 HHL2 HHP2 HHT2 HHX2 HIB2 HIF2 HIJ2 HIN2 HIR2 HIV2 HIZ2 HJD2 HJH2 HJL2 HJP2 HJT2 HJX2 HKB2 HKF2 HKJ2 HKN2 HKR2 HKV2 HKZ2 HLD2 HLH2 HLL2 HLP2 HLT2 HLX2 HMB2 HMF2 HMJ2 HMN2 HMR2 HMV2 HMZ2 HND2 HNH2 HNL2 HNP2 HNT2 HNX2 HOB2 HOF2 HOJ2 HON2 HOR2 HOV2 HOZ2 HPD2 HPH2 HPL2 HPP2 HPT2 HPX2 HQB2 HQF2 HQJ2 HQN2 HQR2 HQV2 HQZ2 HRD2 HRH2 HRL2 HRP2 HRT2 HRX2 HSB2 HSF2 HSJ2 HSN2 HSR2 HSV2 HSZ2 HTD2 HTH2 HTL2 HTP2 HTT2 HTX2 HUB2 HUF2 HUJ2 HUN2 HUR2 HUV2 HUZ2 HVD2 HVH2 HVL2 HVP2 HVT2 HVX2 HWB2 HWF2 HWJ2 HWN2 HWR2 HWV2 HWZ2 HXD2 HXH2 HXL2 HXP2 HXT2 HXX2 HYB2 HYF2 HYJ2 HYN2 HYR2 HYV2 HYZ2 HZD2 HZH2 HZL2 HZP2 HZT2 HZX2 IAB2 IAF2 IAJ2 IAN2 IAR2 IAV2 IAZ2 IBD2 IBH2 IBL2 IBP2 IBT2 IBX2 ICB2 ICF2 ICJ2 ICN2 ICR2 ICV2 ICZ2 IDD2 IDH2 IDL2 IDP2 IDT2 IDX2 IEB2 IEF2 IEJ2 IEN2 IER2 IEV2 IEZ2 IFD2 IFH2 IFL2 IFP2 IFT2 IFX2 IGB2 IGF2 IGJ2 IGN2 IGR2 IGV2 IGZ2 IHD2 IHH2 IHL2 IHP2 IHT2 IHX2 IIB2 IIF2 IIJ2 IIN2 IIR2 IIV2 IIZ2 IJD2 IJH2 IJL2 IJP2 IJT2 IJX2 IKB2 IKF2 IKJ2 IKN2 IKR2 IKV2 IKZ2 ILD2 ILH2 ILL2 ILP2 ILT2 ILX2 IMB2 IMF2 IMJ2 IMN2 IMR2 IMV2 IMZ2 IND2 INH2 INL2 INP2 INT2 INX2 IOB2 IOF2 IOJ2 ION2 IOR2 IOV2 IOZ2 IPD2 IPH2 IPL2 IPP2 IPT2 IPX2 IQB2 IQF2 IQJ2 IQN2 IQR2 IQV2 IQZ2 IRD2 IRH2 IRL2 IRP2 IRT2 IRX2 ISB2 ISF2 ISJ2 ISN2 ISR2 ISV2 ISZ2 ITD2 ITH2 ITL2 ITP2 ITT2 ITX2 IUB2 IUF2 IUJ2 IUN2 IUR2 IUV2 IUZ2 IVD2 IVH2 IVL2 IVP2 IVT2 IVX2 IWB2 IWF2 IWJ2 IWN2 IWR2 IWV2 IWZ2 IXD2 IXH2 IXL2 IXP2 IXT2 IXX2 IYB2 IYF2 IYJ2 IYN2 IYR2 IYV2 IYZ2 IZD2 IZH2 IZL2 IZP2 IZT2 IZX2 JAB2 JAF2 JAJ2 JAN2 JAR2 JAV2 JAZ2 JBD2 JBH2 JBL2 JBP2 JBT2 JBX2 JCB2 JCF2 JCJ2 JCN2 JCR2 JCV2 JCZ2 JDD2 JDH2 JDL2 JDP2 JDT2 JDX2 JEB2 JEF2 JEJ2 JEN2 JER2 JEV2 JEZ2 JFD2 JFH2 JFL2 JFP2 JFT2 JFX2 JGB2 JGF2 JGJ2 JGN2 JGR2 JGV2 JGZ2 JHD2 JHH2 JHL2 JHP2 JHT2 JHX2 JIB2 JIF2 JIJ2 JIN2 JIR2 JIV2 JIZ2 JJD2 JJH2 JJL2 JJP2 JJT2 JJX2 JKB2 JKF2 JKJ2 JKN2 JKR2 JKV2 JKZ2 JLD2 JLH2 JLL2 JLP2 JLT2 JLX2 JMB2 JMF2 JMJ2 JMN2 JMR2 JMV2 JMZ2 JND2 JNH2 JNL2 JNP2 JNT2 JNX2 JOB2 JOF2 JOJ2 JON2 JOR2 JOV2 JOZ2 JPD2 JPH2 JPL2 JPP2 JPT2 JPX2 JQB2 JQF2 JQJ2 JQN2 JQR2 JQV2 JQZ2 JRD2 JRH2 JRL2 JRP2 JRT2 JRX2 JSB2 JSF2 JSJ2 JSN2 JSR2 JSV2 JSZ2 JTD2 JTH2 JTL2 JTP2 JTT2 JTX2 JUB2 JUF2 JUJ2 JUN2 JUR2 JUV2 JUZ2 JVD2 JVH2 JVL2 JVP2 JVT2 JVX2 JWB2 JWF2 JWJ2 JWN2 JWR2 JWV2 JWZ2 JXD2 JXH2 JXL2 JXP2 JXT2 JXX2 JYB2 JYF2 JYJ2 JYN2 JYR2 JYV2 JYZ2 JZD2 JZH2 JZL2 JZP2 JZT2 JZX2 KAB2 KAF2 KAJ2 KAN2 KAR2 KAV2 KAZ2 KBD2 KBH2 KBL2 KBP2 KBT2 KBX2 KCB2 KCF2 KCJ2 KCN2 KCR2 KCV2 KCZ2 KDD2 KDH2 KDL2 KDP2 KDT2 KDX2 KEB2 KEF2 KEJ2 KEN2 KER2 KEV2 KEZ2 KFD2 KFH2 KFL2 KFP2 KFT2 KFX2 KGB2 KGF2 KGJ2 KGN2 KGR2 KGV2 KGZ2 KHD2 KHH2 KHL2 KHP2 KHT2 KHX2 KIB2 KIF2 KIJ2 KIN2 KIR2 KIV2 KIZ2 KJD2 KJH2 KJL2 KJP2 KJT2 KJX2 KKB2 KKF2 KKJ2 KKN2 KKR2 KKV2 KKZ2 KLD2 KLH2 KLL2 KLP2 KLT2 KLX2 KMB2 KMF2 KMJ2 KMN2 KMR2 KMV2 KMZ2 KND2 KNH2 KNL2 KNP2 KNT2 KNX2 KOB2 KOF2 KOJ2 KON2 KOR2 KOV2 KOZ2 KPD2 KPH2 KPL2 KPP2 KPT2 KPX2 KQB2 KQF2 KQJ2 KQN2 KQR2 KQV2 KQZ2 KRD2 KRH2 KRL2 KRP2 KRT2 KRX2 KSB2 KSF2 KSJ2 KSN2 KSR2 KSV2 KSZ2 KTD2 KTH2 KTL2 KTP2 KTT2 KTX2 KUB2 KUF2 KUJ2 KUN2 KUR2 KUV2 KUZ2 KVD2 KVH2 KVL2 KVP2 KVT2 KVX2 KWB2 KWF2 KWJ2 KWN2 KWR2 KWV2 KWZ2 KXD2 KXH2 KXL2 KXP2 KXT2 KXX2 KYB2 KYF2 KYJ2 KYN2 KYR2 KYV2 KYZ2 KZD2 KZH2 KZL2 KZP2 KZT2 KZX2 LAB2 LAF2 LAJ2 LAN2 LAR2 LAV2 LAZ2 LBD2 LBH2 LBL2 LBP2 LBT2 LBX2 LCB2 LCF2 LCJ2 LCN2 LCR2 LCV2 LCZ2 LDD2 LDH2 LDL2 LDP2 LDT2 LDX2 LEB2 LEF2 LEJ2 LEN2 LER2 LEV2 LEZ2 LFD2 LFH2 LFL2 LFP2 LFT2 LFX2 LGB2 LGF2 LGJ2 LGN2 LGR2 LGV2 LGZ2 LHD2 LHH2 LHL2 LHP2 LHT2 LHX2 LIB2 LIF2 LIJ2 LIN2 LIR2 LIV2 LIZ2 LJD2 LJH2 LJL2 LJP2 LJT2 LJX2 LKB2 LKF2 LKJ2 LKN2 LKR2 LKV2 LKZ2 LLD2 LLH2 LLL2 LLP2 LLT2 LLX2 LMB2 LMF2 LMJ2 LMN2 LMR2 LMV2 LMZ2 LND2 LNH2 LNL2 LNP2 LNT2 LNX2 LOB2 LOF2 LOJ2 LON2 LOR2 LOV2 LOZ2 LPD2 LPH2 LPL2 LPP2 LPT2 LPX2 LQB2 LQF2 LQJ2 LQN2 LQR2 LQV2 LQZ2 LRD2 LRH2 LRL2 LRP2 LRT2 LRX2 LSB2 LSF2 LSJ2 LSN2 LSR2 LSV2 LSZ2 LTD2 LTH2 LTL2 LTP2 LTT2 LTX2 LUB2 LUF2 LUJ2 LUN2 LUR2 LUV2 LUZ2 LVD2 LVH2 LVL2 LVP2 LVT2 LVX2 LWB2 LWF2 LWJ2 LWN2 LWR2 LWV2 LWZ2 LXD2 LXH2 LXL2 LXP2 LXT2 LXX2 LYB2 LYF2 LYJ2 LYN2 LYR2 LYV2 LYZ2 LZD2 LZH2 LZL2 LZP2 LZT2 LZX2 MAB2 MAF2 MAJ2 MAN2 MAR2 MAV2 MAZ2 MBD2 MBH2 MBL2 MBP2 MBT2 MBX2 MCB2 MCF2 MCJ2 MCN2 MCR2 MCV2 MCZ2 MDD2 MDH2 MDL2 MDP2 MDT2 MDX2 MEB2 MEF2 MEJ2 MEN2 MER2 MEV2 MEZ2 MFD2 MFH2 MFL2 MFP2 MFT2 MFX2 MGB2 MGF2 MGJ2 MGN2 MGR2 MGV2 MGZ2 MHD2 MHH2 MHL2 MHP2 MHT2 MHX2 MIB2 MIF2 MIJ2 MIN2 MIR2 MIV2 MIZ2 MJD2 MJH2 MJL2 MJP2 MJT2 MJX2 MKB2 MKF2 MKJ2 MKN2 MKR2 MKV2 MKZ2 MLD2 MLH2 MLL2 MLP2 MLT2 MLX2 MMB2 MMF2 MMJ2 MMN2 MMR2 MMV2 MMZ2 MND2 MNH2 MNL2 MNP2 MNT2 MNX2 MOB2 MOF2 MOJ2 MON2 MOR2 MOV2 MOZ2 MPD2 MPH2 MPL2 MPP2 MPT2 MPX2 MQB2 MQF2 MQJ2 MQN2 MQR2 MQV2 MQZ2 MRD2 MRH2 MRL2 MRP2 MRT2 MRX2 MSB2 MSF2 MSJ2 MSN2 MSR2 MSV2 MSZ2 MTD2 MTH2 MTL2 MTP2 MTT2 MTX2 MUB2 MUF2 MUJ2 MUN2 MUR2 MUV2 MUZ2 MVD2 MVH2 MVL2 MVP2 MVT2 MVX2 MWB2 MWF2 MWJ2 MWN2 MWR2 MWV2 MWZ2 MXD2 MXH2 MXL2 MXP2 MXT2 MXX2 MYB2 MYF2 MYJ2 MYN2 MYR2 MYV2 MYZ2 MZD2 MZH2 MZL2 MZP2 MZT2 MZX2 NAB2 NAF2 NAJ2 NAN2 NAR2 NAV2 NAZ2 NBD2 NBH2 NBL2 NBP2 NBT2 NBX2 NCB2 NCF2 NCJ2 NCN2 NCR2 NCV2 NCZ2 NDD2 NDH2 NDL2 NDP2 NDT2 NDX2 NEB2 NEF2 NEJ2 NEN2 NER2 NEV2 NEZ2 NFD2 NFH2 NFL2 NFP2 NFT2 NFX2 NGB2 NGF2 NGJ2 NGN2 NGR2 NGV2 NGZ2 NHD2 NHH2 NHL2 NHP2 NHT2 NHX2 NIB2 NIF2 NIJ2 NIN2 NIR2 NIV2 NIZ2 NJD2 NJH2 NJL2 NJP2 NJT2 NJX2 NKB2 NKF2 NKJ2 NKN2 NKR2 NKV2 NKZ2 NLD2 NLH2 NLL2 NLP2 NLT2 NLX2 NMB2 NMF2 NMJ2 NMN2 NMR2 NMV2 NMZ2 NND2 NNH2 NNL2 NNP2 NNT2 NNX2 NOB2 NOF2 NOJ2 NON2 NOR2 NOV2 NOZ2 NPD2 NPH2 NPL2 NPP2 NPT2 NPX2 NQB2 NQF2 NQJ2 NQN2 NQR2 NQV2 NQZ2 NRD2 NRH2 NRL2 NRP2 NRT2 NRX2 NSB2 NSF2 NSJ2 NSN2 NSR2 NSV2 NSZ2 NTD2 NTH2 NTL2 NTP2 NTT2 NTX2 NUB2 NUF2 NUJ2 NUN2 NUR2 NUV2 NUZ2 NVD2 NVH2 NVL2 NVP2 NVT2 NVX2 NWB2 NWF2 NWJ2 NWN2 NWR2 NWV2 NWZ2 NXD2 NXH2 NXL2 NXP2 NXT2 NXX2 NYB2 NYF2 NYJ2 NYN2 NYR2 NYV2 NYZ2 NZD2 NZH2 NZL2 NZP2 NZT2 NZX2 OAB2 OAF2 OAJ2 OAN2 OAR2 OAV2 OAZ2 OBD2 OBH2 OBL2 OBP2 OBT2 OBX2 OCB2 OCF2 OCJ2 OCN2 OCR2 OCV2 OCZ2 ODD2 ODH2 ODL2 ODP2 ODT2 ODX2 OEB2 OEF2 OEJ2 OEN2 OER2 OEV2 OEZ2 OFD2 OFH2 OFL2 OFP2 OFT2 OFX2 OGB2 OGF2 OGJ2 OGN2 OGR2 OGV2 OGZ2 OHD2 OHH2 OHL2 OHP2 OHT2 OHX2 OIB2 OIF2 OIJ2 OIN2 OIR2 OIV2 OIZ2 OJD2 OJH2 OJL2 OJP2 OJT2 OJX2 OKB2 OKF2 OKJ2 OKN2 OKR2 OKV2 OKZ2 OLD2 OLH2 OLL2 OLP2 OLT2 OLX2 OMB2 OMF2 OMJ2 OMN2 OMR2 OMV2 OMZ2 OND2 ONH2 ONL2 ONP2 ONT2 ONX2 OOB2 OOF2 OOJ2 OON2 OOR2 OOV2 OOZ2 OPD2 OPH2 OPL2 OPP2 OPT2 OPX2 OQB2 OQF2 OQJ2 OQN2 OQR2 OQV2 OQZ2 ORD2 ORH2 ORL2 ORP2 ORT2 ORX2 OSB2 OSF2 OSJ2 OSN2 OSR2 OSV2 OSZ2 OTD2 OTH2 OTL2 OTP2 OTT2 OTX2 OUB2 OUF2 OUJ2 OUN2 OUR2 OUV2 OUZ2 OVD2 OVH2 OVL2 OVP2 OVT2 OVX2 OWB2 OWF2 OWJ2 OWN2 OWR2 OWV2 OWZ2 OXD2 OXH2 OXL2 OXP2 OXT2 OXX2 OYB2 OYF2 OYJ2 OYN2 OYR2 OYV2 OYZ2 OZD2 OZH2 OZL2 OZP2 OZT2 OZX2 PAB2 PAF2 PAJ2 PAN2 PAR2 PAV2 PAZ2 PBD2 PBH2 PBL2 PBP2 PBT2 PBX2 PCB2 PCF2 PCJ2 PCN2 PCR2 PCV2 PCZ2 PDD2 PDH2 PDL2 PDP2 PDT2 PDX2 PEB2 PEF2 PEJ2 PEN2 PER2 PEV2 PEZ2 PFD2 PFH2 PFL2 PFP2 PFT2 PFX2 PGB2 PGF2 PGJ2 PGN2 PGR2 PGV2 PGZ2 PHD2 PHH2 PHL2 PHP2 PHT2 PHX2 PIB2 PIF2 PIJ2 PIN2 PIR2 PIV2 PIZ2 PJD2 PJH2 PJL2 PJP2 PJT2 PJX2 PKB2 PKF2 PKJ2 PKN2 PKR2 PKV2 PKZ2 PLD2 PLH2 PLL2 PLP2 PLT2 PLX2 PMB2 PMF2 PMJ2 PMN2 PMR2 PMV2 PMZ2 PND2 PNH2 PNL2 PNP2 PNT2 PNX2 POB2 POF2 POJ2 PON2 POR2 POV2 POZ2 PPD2 PPH2 PPL2 PPP2 PPT2 PPX2 PQB2 PQF2 PQJ2 PQN2 PQR2 PQV2 PQZ2 PRD2 PRH2 PRL2 PRP2 PRT2 PRX2 PSB2 PSF2 PSJ2 PSN2 PSR2 PSV2 PSZ2 PTD2 PTH2 PTL2 PTP2 PTT2 PTX2 PUB2 PUF2 PUJ2 PUN2 PUR2 PUV2 PUZ2 PVD2 PVH2 PVL2 PVP2 PVT2 PVX2 PWB2 PWF2 PWJ2 PWN2 PWR2 PWV2 PWZ2 PXD2 PXH2 PXL2 PXP2 PXT2 PXX2 PYB2 PYF2 PYJ2 PYN2 PYR2 PYV2 PYZ2 PZD2 PZH2 PZL2 PZP2 PZT2 PZX2 QAB2 QAF2 QAJ2 QAN2 QAR2 QAV2 QAZ2 QBD2 QBH2 QBL2 QBP2 QBT2 QBX2 QCB2 QCF2 QCJ2 QCN2 QCR2 QCV2 QCZ2 QDD2 QDH2 QDL2 QDP2 QDT2 QDX2 QEB2 QEF2 QEJ2 QEN2 QER2 QEV2 QEZ2 QFD2 QFH2 QFL2 QFP2 QFT2 QFX2 QGB2 QGF2 QGJ2 QGN2 QGR2 QGV2 QGZ2 QHD2 QHH2 QHL2 QHP2 QHT2 QHX2 QIB2 QIF2 QIJ2 QIN2 QIR2 QIV2 QIZ2 QJD2 QJH2 QJL2 QJP2 QJT2 QJX2 QKB2 QKF2 QKJ2 QKN2 QKR2 QKV2 QKZ2 QLD2 QLH2 QLL2 QLP2 QLT2 QLX2 QMB2 QMF2 QMJ2 QMN2 QMR2 QMV2 QMZ2 QND2 QNH2 QNL2 QNP2 QNT2 QNX2 QOB2 QOF2 QOJ2 QON2 QOR2 QOV2 QOZ2 QPD2 QPH2 QPL2 QPP2 QPT2 QPX2 QQB2 QQF2 QQJ2 QQN2 QQR2 QQV2 QQZ2 QRD2 QRH2 QRL2 QRP2 QRT2 QRX2 QSB2 QSF2 QSJ2 QSN2 QSR2 QSV2 QSZ2 QTD2 QTH2 QTL2 QTP2 QTT2 QTX2 QUB2 QUF2 QUJ2 QUN2 QUR2 QUV2 QUZ2 QVD2 QVH2 QVL2 QVP2 QVT2 QVX2 QWB2 QWF2 QWJ2 QWN2 QWR2 QWV2 QWZ2 QXD2 QXH2 QXL2 QXP2 QXT2 QXX2 QYB2 QYF2 QYJ2 QYN2 QYR2 QYV2 QYZ2 QZD2 QZH2 QZL2 QZP2 QZT2 QZX2 RAB2 RAF2 RAJ2 RAN2 RAR2 RAV2 RAZ2 RBD2 RBH2 RBL2 RBP2 RBT2 RBX2 RCB2 RCF2 RCJ2 RCN2 RCR2 RCV2 RCZ2 RDD2 RDH2 RDL2 RDP2 RDT2 RDX2 REB2 REF2 REJ2 REN2 RER2 REV2 REZ2 RFD2 RFH2 RFL2 RFP2 RFT2 RFX2 RGB2 RGF2 RGJ2 RGN2 RGR2 RGV2 RGZ2 RHD2 RHH2 RHL2 RHP2 RHT2 RHX2 RIB2 RIF2 RIJ2 RIN2 RIR2 RIV2 RIZ2 RJD2 RJH2 RJL2 RJP2 RJT2 RJX2 RKB2 RKF2 RKJ2 RKN2 RKR2 RKV2 RKZ2 RLD2 RLH2 RLL2 RLP2 RLT2 RLX2 RMB2 RMF2 RMJ2 RMN2 RMR2 RMV2 RMZ2 RND2 RNH2 RNL2 RNP2 RNT2 RNX2 ROB2 ROF2 ROJ2 RON2 ROR2 ROV2 ROZ2 RPD2 RPH2 RPL2 RPP2 RPT2 RPX2 RQB2 RQF2 RQJ2 RQN2 RQR2 RQV2 RQZ2 RRD2 RRH2 RRL2 RRP2 RRT2 RRX2 RSB2 RSF2 RSJ2 RSN2 RSR2 RSV2 RSZ2 RTD2 RTH2 RTL2 RTP2 RTT2 RTX2 RUB2 RUF2 RUJ2 RUN2 RUR2 RUV2 RUZ2 RVD2 RVH2 RVL2 RVP2 RVT2 RVX2 RWB2 RWF2 RWJ2 RWN2 RWR2 RWV2 RWZ2 RXD2 RXH2 RXL2 RXP2 RXT2 RXX2 RYB2 RYF2 RYJ2 RYN2 RYR2 RYV2 RYZ2 RZD2 RZH2 RZL2 RZP2 RZT2 RZX2 SAB2 SAF2 SAJ2 SAN2 SAR2 SAV2 SAZ2 SBD2 SBH2 SBL2 SBP2 SBT2 SBX2 SCB2 SCF2 SCJ2 SCN2 SCR2 SCV2 SCZ2 SDD2 SDH2 SDL2 SDP2 SDT2 SDX2 SEB2 SEF2 SEJ2 SEN2 SER2 SEV2 SEZ2 SFD2 SFH2 SFL2 SFP2 SFT2 SFX2 SGB2 SGF2 SGJ2 SGN2 SGR2 SGV2 SGZ2 SHD2 SHH2 SHL2 SHP2 SHT2 SHX2 SIB2 SIF2 SIJ2 SIN2 SIR2 SIV2 SIZ2 SJD2 SJH2 SJL2 SJP2 SJT2 SJX2 SKB2 SKF2 SKJ2 SKN2 SKR2 SKV2 SKZ2 SLD2 SLH2 SLL2 SLP2 SLT2 SLX2 SMB2 SMF2 SMJ2 SMN2 SMR2 SMV2 SMZ2 SND2 SNH2 SNL2 SNP2 SNT2 SNX2 SOB2 SOF2 SOJ2 SON2 SOR2 SOV2 SOZ2 SPD2 SPH2 SPL2 SPP2 SPT2 SPX2 SQB2 SQF2 SQJ2 SQN2 SQR2 SQV2 SQZ2 SRD2 SRH2 SRL2 SRP2 SRT2 SRX2 SSB2 SSF2 SSJ2 SSN2 SSR2 SSV2 SSZ2 STD2 STH2 STL2 STP2 STT2 STX2 SUB2 SUF2 SUJ2 SUN2 SUR2 SUV2 SUZ2 SVD2 SVH2 SVL2 SVP2 SVT2 SVX2 SWB2 SWF2 SWJ2 SWN2 SWR2 SWV2 SWZ2 SXD2 SXH2 SXL2 SXP2 SXT2 SXX2 SYB2 SYF2 SYJ2 SYN2 SYR2 SYV2 SYZ2 SZD2 SZH2 SZL2 SZP2 SZT2 SZX2 TAB2 TAF2 TAJ2 TAN2 TAR2 TAV2 TAZ2 TBD2 TBH2 TBL2 TBP2 TBT2 TBX2 TCB2 TCF2 TCJ2 TCN2 TCR2 TCV2 TCZ2 TDD2 TDH2 TDL2 TDP2 TDT2 TDX2 TEB2 TEF2 TEJ2 TEN2 TER2 TEV2 TEZ2 TFD2 TFH2 TFL2 TFP2 TFT2 TFX2 TGB2 TGF2 TGJ2 TGN2 TGR2 TGV2 TGZ2 THD2 THH2 THL2 THP2 THT2 THX2 TIB2 TIF2 TIJ2 TIN2 TIR2 TIV2 TIZ2 TJD2 TJH2 TJL2 TJP2 TJT2 TJX2 TKB2 TKF2 TKJ2 TKN2 TKR2 TKV2 TKZ2 TLD2 TLH2 TLL2 TLP2 TLT2 TLX2 TMB2 TMF2 TMJ2 TMN2 TMR2 TMV2 TMZ2 TND2 TNH2 TNL2 TNP2 TNT2 TNX2 TOB2 TOF2 TOJ2 TON2 TOR2 TOV2 TOZ2 TPD2 TPH2 TPL2 TPP2 TPT2 TPX2 TQB2 TQF2 TQJ2 TQN2 TQR2 TQV2 TQZ2 TRD2 TRH2 TRL2 TRP2 TRT2 TRX2 TSB2 TSF2 TSJ2 TSN2 TSR2 TSV2 TSZ2 TTD2 TTH2 TTL2 TTP2 TTT2 TTX2 TUB2 TUF2 TUJ2 TUN2 TUR2 TUV2 TUZ2 TVD2 TVH2 TVL2 TVP2 TVT2 TVX2 TWB2 TWF2 TWJ2 TWN2 TWR2 TWV2 TWZ2 TXD2 TXH2 TXL2 TXP2 TXT2 TXX2 TYB2 TYF2 TYJ2 TYN2 TYR2 TYV2 TYZ2 TZD2 TZH2 TZL2 TZP2 TZT2 TZX2 UAB2 UAF2 UAJ2 UAN2 UAR2 UAV2 UAZ2 UBD2 UBH2 UBL2 UBP2 UBT2 UBX2 UCB2 UCF2 UCJ2 UCN2 UCR2 UCV2 UCZ2 UDD2 UDH2 UDL2 UDP2 UDT2 UDX2 UEB2 UEF2 UEJ2 UEN2 UER2 UEV2 UEZ2 UFD2 UFH2 UFL2 UFP2 UFT2 UFX2 UGB2 UGF2 UGJ2 UGN2 UGR2 UGV2 UGZ2 UHD2 UHH2 UHL2 UHP2 UHT2 UHX2 UIB2 UIF2 UIJ2 UIN2 UIR2 UIV2 UIZ2 UJD2 UJH2 UJL2 UJP2 UJT2 UJX2 UKB2 UKF2 UKJ2 UKN2 UKR2 UKV2 UKZ2 ULD2 ULH2 ULL2 ULP2 ULT2 ULX2 UMB2 UMF2 UMJ2 UMN2 UMR2 UMV2 UMZ2 UND2 UNH2 UNL2 UNP2 UNT2 UNX2 UOB2 UOF2 UOJ2 UON2 UOR2 UOV2 UOZ2 UPD2 UPH2 UPL2 UPP2 UPT2 UPX2 UQB2 UQF2 UQJ2 UQN2 UQR2 UQV2 UQZ2 URD2 URH2 URL2 URP2 URT2 URX2 USB2 USF2 USJ2 USN2 USR2 USV2 USZ2 UTD2 UTH2 UTL2 UTP2 UTT2 UTX2 UUB2 UUF2 UUJ2 UUN2 UUR2 UUV2 UUZ2 UVD2 UVH2 UVL2 UVP2 UVT2 UVX2 UWB2 UWF2 UWJ2 UWN2 UWR2 UWV2 UWZ2 UXD2 UXH2 UXL2 UXP2 UXT2 UXX2 UYB2 UYF2 UYJ2 UYN2 UYR2 UYV2 UYZ2 UZD2 UZH2 UZL2 UZP2 UZT2 UZX2 VAB2 VAF2 VAJ2 VAN2 VAR2 VAV2 VAZ2 VBD2 VBH2 VBL2 VBP2 VBT2 VBX2 VCB2 VCF2 VCJ2 VCN2 VCR2 VCV2 VCZ2 VDD2 VDH2 VDL2 VDP2 VDT2 VDX2 VEB2 VEF2 VEJ2 VEN2 VER2 VEV2 VEZ2 VFD2 VFH2 VFL2 VFP2 VFT2 VFX2 VGB2 VGF2 VGJ2 VGN2 VGR2 VGV2 VGZ2 VHD2 VHH2 VHL2 VHP2 VHT2 VHX2 VIB2 VIF2 VIJ2 VIN2 VIR2 VIV2 VIZ2 VJD2 VJH2 VJL2 VJP2 VJT2 VJX2 VKB2 VKF2 VKJ2 VKN2 VKR2 VKV2 VKZ2 VLD2 VLH2 VLL2 VLP2 VLT2 VLX2 VMB2 VMF2 VMJ2 VMN2 VMR2 VMV2 VMZ2 VND2 VNH2 VNL2 VNP2 VNT2 VNX2 VOB2 VOF2 VOJ2 VON2 VOR2 VOV2 VOZ2 VPD2 VPH2 VPL2 VPP2 VPT2 VPX2 VQB2 VQF2 VQJ2 VQN2 VQR2 VQV2 VQZ2 VRD2 VRH2 VRL2 VRP2 VRT2 VRX2 VSB2 VSF2 VSJ2 VSN2 VSR2 VSV2 VSZ2 VTD2 VTH2 VTL2 VTP2 VTT2 VTX2 VUB2 VUF2 VUJ2 VUN2 VUR2 VUV2 VUZ2 VVD2 VVH2 VVL2 VVP2 VVT2 VVX2 VWB2 VWF2 VWJ2 VWN2 VWR2 VWV2 VWZ2 VXD2 VXH2 VXL2 VXP2 VXT2 VXX2 VYB2 VYF2 VYJ2 VYN2 VYR2 VYV2 VYZ2 VZD2 VZH2 VZL2 VZP2 VZT2 VZX2 WAB2 WAF2 WAJ2 WAN2 WAR2 WAV2 WAZ2 WBD2 WBH2 WBL2 WBP2 WBT2 WBX2 WCB2 WCF2 WCJ2 WCN2 WCR2 WCV2 WCZ2 WDD2 WDH2 WDL2 WDP2 WDT2 WDX2 WEB2 WEF2 WEJ2 WEN2 WER2 WEV2 WEZ2 WFD2 WFH2 WFL2 WFP2 WFT2 WFX2 WGB2 WGF2 WGJ2 WGN2 WGR2 WGV2 WGZ2 WHD2 WHH2 WHL2 WHP2 WHT2 WHX2 WIB2 WIF2 WIJ2 WIN2 WIR2 WIV2 WIZ2 WJD2 WJH2 WJL2 WJP2 WJT2 WJX2 WKB2 WKF2 WKJ2 WKN2 WKR2 WKV2 WKZ2 WLD2 WLH2 WLL2 WLP2 WLT2 WLX2 WMB2 WMF2 WMJ2 WMN2 WMR2 WMV2 WMZ2 WND2 WNH2 WNL2 WNP2 WNT2 WNX2 WOB2 WOF2 WOJ2 WON2 WOR2 WOV2 WOZ2 WPD2 WPH2 WPL2 WPP2 WPT2 WPX2 WQB2 WQF2 WQJ2 WQN2 WQR2 WQV2 WQZ2 WRD2 WRH2 WRL2 WRP2 WRT2 WRX2 WSB2 WSF2 WSJ2 WSN2 WSR2 WSV2 WSZ2 WTD2 WTH2 WTL2 WTP2 WTT2 WTX2 WUB2 WUF2 WUJ2 WUN2 WUR2 WUV2 WUZ2 WVD2 WVH2 WVL2 WVP2 WVT2 WVX2 WWB2 WWF2 WWJ2 WWN2 WWR2 WWV2 WWZ2 WXD2 WXH2 WXL2 WXP2 WXT2 WXX2 WYB2 WYF2 WYJ2 WYN2 WYR2 WYV2 WYZ2 WZD2 WZH2 WZL2 WZP2 WZT2 WZX2 XAB2 XAF2 XAJ2 XAN2 XAR2 XAV2 XAZ2 XBD2 XBH2 XBL2 XBP2 XBT2 XBX2 XCB2 XCF2 XCJ2 XCN2 XCR2 XCV2 XCZ2 XDD2 XDH2 XDL2 XDP2 XDT2 XDX2 XEB2 XEF2 XEJ2 XEN2 XER2 XEV2 XEZ2 XFD2 D2:D111">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>D2=""</formula>
     </cfRule>
